--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -505,22 +505,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="H2" t="n">
-        <v>7.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>1.6</v>
@@ -529,7 +529,7 @@
         <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
@@ -540,39 +540,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="G3" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="H3" t="n">
         <v>7.4</v>
       </c>
       <c r="I3" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="J3" t="n">
         <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="4">
@@ -583,39 +583,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.7</v>
+        <v>22.1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="G4" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="H4" t="n">
-        <v>8.9</v>
+        <v>7.4</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -630,26 +630,26 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.3</v>
+        <v>22.8</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="H5" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="I5" t="n">
         <v>1.8</v>
@@ -658,7 +658,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="6">
@@ -673,23 +673,23 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.2</v>
+        <v>23.5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G6" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="H6" t="n">
         <v>8.1</v>
@@ -716,35 +716,35 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G7" t="n">
         <v>5.8</v>
       </c>
       <c r="H7" t="n">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
         <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
@@ -759,32 +759,32 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G8" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="H8" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="K8" t="n">
         <v>2.9</v>
@@ -802,29 +802,29 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.9</v>
+        <v>23.2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
         <v>0.5</v>
@@ -841,39 +841,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24.4</v>
+        <v>23.1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G10" t="n">
-        <v>6.9</v>
+        <v>6.1</v>
       </c>
       <c r="H10" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="11">
@@ -884,39 +884,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.5</v>
+        <v>24.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="H11" t="n">
-        <v>7.3</v>
+        <v>8.6</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="12">
@@ -927,39 +927,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>28.1</v>
+        <v>25</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="G12" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="H12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
         <v>0.4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="13">
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.4</v>
+        <v>23.9</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="H13" t="n">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="14">
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24.1</v>
+        <v>27.4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="15">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25.4</v>
+        <v>23.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="G15" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="16">
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24.1</v>
+        <v>23.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>3.1</v>
       </c>
       <c r="G16" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="H16" t="n">
-        <v>9.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K16" t="n">
         <v>2.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3.7</v>
       </c>
     </row>
     <row r="17">
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.8</v>
+        <v>23.5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="H17" t="n">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K17" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="18">
@@ -1189,26 +1189,26 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>25.3</v>
+        <v>24.9</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G18" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="H18" t="n">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I18" t="n">
         <v>1.9</v>
@@ -1217,7 +1217,7 @@
         <v>0.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="19">
@@ -1228,39 +1228,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="G19" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="H19" t="n">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>0.6</v>
       </c>
       <c r="K19" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="20">
@@ -1271,39 +1271,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="H20" t="n">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K20" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="21">
@@ -1318,35 +1318,35 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3.1</v>
       </c>
       <c r="G21" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="H21" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
         <v>0.5</v>
       </c>
       <c r="K21" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1365,31 +1365,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G22" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="H22" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="I22" t="n">
         <v>2.1</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="23">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1408,28 +1408,28 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="H23" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="I23" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K23" t="n">
         <v>3.2</v>
@@ -1443,39 +1443,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25.5</v>
+        <v>24.1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="H24" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="I24" t="n">
         <v>1.9</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K24" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="25">
@@ -1486,11 +1486,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.4</v>
+        <v>24.5</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1499,23 +1499,23 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>2.9</v>
       </c>
       <c r="G25" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="H25" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="I25" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K25" t="n">
         <v>2.9</v>
@@ -1529,39 +1529,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.5</v>
+        <v>26.4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G26" t="n">
         <v>6.7</v>
       </c>
       <c r="H26" t="n">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K26" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="27">
@@ -1572,39 +1572,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.8</v>
+        <v>23.7</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>2.9</v>
       </c>
       <c r="G27" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="H27" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="28">
@@ -1619,20 +1619,20 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.7</v>
+        <v>24.5</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G28" t="n">
         <v>6.9</v>
@@ -1644,10 +1644,10 @@
         <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K28" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="29">
@@ -1662,35 +1662,35 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.3</v>
+        <v>26.8</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G29" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="H29" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J29" t="n">
         <v>0.5</v>
       </c>
       <c r="K29" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="30">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1724,16 +1724,16 @@
         <v>6.6</v>
       </c>
       <c r="H30" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="J30" t="n">
         <v>0.7</v>
       </c>
       <c r="K30" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -1748,35 +1748,35 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>3.7</v>
       </c>
       <c r="G31" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H31" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J31" t="n">
         <v>0.6</v>
       </c>
       <c r="K31" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
   </sheetData>
@@ -1858,30 +1858,30 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G2" t="n">
         <v>6.4</v>
       </c>
       <c r="H2" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I2" t="n">
         <v>1.2</v>
@@ -1901,39 +1901,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.1</v>
+        <v>21.6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>6.5</v>
       </c>
       <c r="H3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="4">
@@ -1948,26 +1948,26 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.8</v>
+        <v>20.9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I4" t="n">
         <v>1.9</v>
@@ -1976,7 +1976,7 @@
         <v>0.6</v>
       </c>
       <c r="K4" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="5">
@@ -1987,39 +1987,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.9</v>
+        <v>23.3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="G5" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="H5" t="n">
         <v>5.2</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="6">
@@ -2030,39 +2030,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G6" t="n">
-        <v>5.6</v>
+        <v>6.9</v>
       </c>
       <c r="H6" t="n">
         <v>5.3</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K6" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7">
@@ -2073,15 +2073,15 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2090,22 +2090,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>5.9</v>
       </c>
       <c r="H7" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="I7" t="n">
         <v>1.7</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="8">
@@ -2120,26 +2120,26 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>3.1</v>
       </c>
       <c r="G8" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="H8" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I8" t="n">
         <v>1.5</v>
@@ -2148,7 +2148,7 @@
         <v>0.5</v>
       </c>
       <c r="K8" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9">
@@ -2159,39 +2159,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>3.5</v>
       </c>
       <c r="G9" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="H9" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K9" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="10">
@@ -2202,39 +2202,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="G10" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="H10" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0.6</v>
       </c>
       <c r="K10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="11">
@@ -2249,16 +2249,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.7</v>
+        <v>22.4</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -2268,7 +2268,7 @@
         <v>7</v>
       </c>
       <c r="H11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
         <v>1.5</v>
@@ -2288,39 +2288,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24.7</v>
+        <v>23.2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G12" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="H12" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
         <v>0.7</v>
       </c>
       <c r="K12" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13">
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -2357,7 +2357,7 @@
         <v>5.4</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>0.5</v>
@@ -2374,15 +2374,15 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.5</v>
+        <v>24.6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2391,22 +2391,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="G14" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="H14" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K14" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="15">
@@ -2421,23 +2421,23 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.3</v>
+        <v>23</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G15" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="H15" t="n">
         <v>5.3</v>
@@ -2460,39 +2460,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="G16" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="H16" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="17">
@@ -2503,39 +2503,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.8</v>
+        <v>22.3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G17" t="n">
         <v>6.8</v>
       </c>
       <c r="H17" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
         <v>0.6</v>
       </c>
       <c r="K17" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="18">
@@ -2546,39 +2546,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.7</v>
+        <v>23.4</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G18" t="n">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="H18" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="19">
@@ -2589,39 +2589,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.3</v>
+        <v>24.1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="G19" t="n">
         <v>6.5</v>
       </c>
       <c r="H19" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="20">
@@ -2632,39 +2632,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.6</v>
+        <v>23.1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="G20" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -2679,29 +2679,29 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.4</v>
+        <v>24.6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3.7</v>
       </c>
       <c r="G21" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="H21" t="n">
         <v>5.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0.6</v>
@@ -2722,26 +2722,26 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="G22" t="n">
         <v>6.6</v>
       </c>
       <c r="H22" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="I22" t="n">
         <v>1.6</v>
@@ -2750,7 +2750,7 @@
         <v>0.4</v>
       </c>
       <c r="K22" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -2761,39 +2761,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>3.1</v>
       </c>
       <c r="G23" t="n">
-        <v>7.3</v>
+        <v>6.3</v>
       </c>
       <c r="H23" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="24">
@@ -2808,7 +2808,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2817,26 +2817,26 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>3.5</v>
       </c>
       <c r="G24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H24" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
         <v>2</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K24" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="25">
@@ -2847,39 +2847,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.5</v>
+        <v>25</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="G25" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="H25" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
         <v>0.6</v>
       </c>
       <c r="K25" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="26">
@@ -2890,39 +2890,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.3</v>
+        <v>25</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="G26" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="H26" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0.7</v>
       </c>
       <c r="K26" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -2933,39 +2933,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>25.7</v>
+        <v>23.5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>84.1</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="G27" t="n">
-        <v>5.9</v>
+        <v>6.9</v>
       </c>
       <c r="H27" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="28">
@@ -2976,39 +2976,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>25.6</v>
+        <v>24.3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="G28" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="H28" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="29">
@@ -3019,39 +3019,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>23.7</v>
+        <v>24.1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="G29" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="H29" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="I29" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J29" t="n">
         <v>0.7</v>
       </c>
       <c r="K29" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="30">
@@ -3070,25 +3070,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>4.1</v>
       </c>
       <c r="G30" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="H30" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0.8</v>
@@ -3109,11 +3109,11 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3122,13 +3122,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G31" t="n">
         <v>7</v>
       </c>
       <c r="H31" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I31" t="n">
         <v>2</v>
@@ -3223,32 +3223,32 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I2" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>3.2</v>
@@ -3266,32 +3266,32 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>2.6</v>
       </c>
       <c r="G3" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I3" t="n">
         <v>1.6</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K3" t="n">
         <v>2.4</v>
@@ -3309,11 +3309,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3328,10 +3328,10 @@
         <v>8.300000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J4" t="n">
         <v>0.7</v>
@@ -3348,39 +3348,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23.6</v>
+        <v>20.6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K5" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="6">
@@ -3391,39 +3391,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.9</v>
+        <v>23.7</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="G6" t="n">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="7">
@@ -3434,39 +3434,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.3</v>
+        <v>22.3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="G7" t="n">
-        <v>8.300000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="H7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="8">
@@ -3477,39 +3477,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.6</v>
+        <v>21.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="G8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="H8" t="n">
         <v>4.6</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="9">
@@ -3520,27 +3520,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22</v>
+        <v>20.6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G9" t="n">
-        <v>7.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H9" t="n">
         <v>4.6</v>
@@ -3549,10 +3549,10 @@
         <v>1.7</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="10">
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20.9</v>
+        <v>22.4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G10" t="n">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="K10" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -3610,35 +3610,35 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G11" t="n">
         <v>7.5</v>
       </c>
       <c r="H11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
         <v>0.8</v>
       </c>
       <c r="K11" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12">
@@ -3649,39 +3649,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21.6</v>
+        <v>21.1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>2.8</v>
       </c>
       <c r="G12" t="n">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="K12" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="13">
@@ -3692,33 +3692,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="G13" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
         <v>0.6</v>
@@ -3735,36 +3735,36 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.3</v>
+        <v>22.6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="G14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="H14" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K14" t="n">
         <v>2.7</v>
@@ -3778,39 +3778,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.5</v>
+        <v>23.2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K15" t="n">
         <v>2.7</v>
-      </c>
-      <c r="G15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="16">
@@ -3825,35 +3825,35 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>2.8</v>
       </c>
       <c r="G16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="17">
@@ -3868,16 +3868,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -3887,10 +3887,10 @@
         <v>7.1</v>
       </c>
       <c r="H17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>1</v>
@@ -3907,39 +3907,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>2.6</v>
       </c>
       <c r="G18" t="n">
-        <v>9.1</v>
+        <v>6.9</v>
       </c>
       <c r="H18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="19">
@@ -3954,16 +3954,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.3</v>
+        <v>22.9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -3973,7 +3973,7 @@
         <v>6.7</v>
       </c>
       <c r="H19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
         <v>2.1</v>
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4006,26 +4006,26 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I20" t="n">
         <v>1.5</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="21">
@@ -4044,28 +4044,28 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="G21" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I21" t="n">
         <v>2.3</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>2.6</v>
@@ -4083,35 +4083,35 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G22" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I22" t="n">
         <v>1.8</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -4122,30 +4122,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>26.4</v>
+        <v>23.9</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>7.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="I23" t="n">
         <v>1.7</v>
@@ -4154,7 +4154,7 @@
         <v>0.8</v>
       </c>
       <c r="K23" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="24">
@@ -4165,36 +4165,36 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.6</v>
+        <v>26.6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="G24" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="H24" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K24" t="n">
         <v>2.7</v>
@@ -4208,39 +4208,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.2</v>
+        <v>23.7</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G25" t="n">
         <v>8.6</v>
       </c>
       <c r="H25" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="K25" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="26">
@@ -4251,39 +4251,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.5</v>
+        <v>24.6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="G26" t="n">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="H26" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="27">
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.9</v>
+        <v>24.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>7.5</v>
+        <v>8.9</v>
       </c>
       <c r="H27" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="28">
@@ -4337,39 +4337,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="G28" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="H28" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
         <v>0.8</v>
       </c>
       <c r="K28" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -4380,39 +4380,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="G29" t="n">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="I29" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0.9</v>
       </c>
       <c r="K29" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="30">
@@ -4423,39 +4423,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>25.2</v>
+        <v>23.7</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="G30" t="n">
         <v>7.8</v>
       </c>
       <c r="H30" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -4466,39 +4466,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.7</v>
+        <v>24.3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G31" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="H31" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
         <v>0.8</v>
       </c>
       <c r="K31" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>
@@ -4584,35 +4584,35 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20.8</v>
+        <v>21.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="G2" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
       <c r="H2" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
         <v>1.3</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="3">
@@ -4627,35 +4627,35 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1.9</v>
       </c>
       <c r="G3" t="n">
-        <v>9.9</v>
+        <v>10.2</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J3" t="n">
         <v>1.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="4">
@@ -4666,39 +4666,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19.9</v>
+        <v>21.7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>10.4</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -4709,39 +4709,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.8</v>
+        <v>20.6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="G5" t="n">
-        <v>10.7</v>
+        <v>8.4</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -4752,39 +4752,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="G6" t="n">
         <v>10.7</v>
       </c>
       <c r="H6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7">
@@ -4795,39 +4795,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="G7" t="n">
-        <v>10.1</v>
+        <v>10.8</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.7</v>
+        <v>22.1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="G8" t="n">
-        <v>9.300000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="H8" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="I8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J8" t="n">
         <v>1.4</v>
       </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
       <c r="K8" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="9">
@@ -4881,36 +4881,36 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G9" t="n">
-        <v>10.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H9" t="n">
         <v>4.3</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>2.9</v>
@@ -4924,39 +4924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.6</v>
+        <v>20.6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K10" t="n">
         <v>2.4</v>
-      </c>
-      <c r="G10" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2.9</v>
       </c>
     </row>
     <row r="11">
@@ -4967,39 +4967,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20.9</v>
+        <v>21.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="G11" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="H11" t="n">
         <v>3.9</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="G12" t="n">
-        <v>10.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
         <v>1.1</v>
       </c>
       <c r="K12" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="13">
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.3</v>
+        <v>22.2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="G13" t="n">
-        <v>9.800000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K13" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="14">
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="G14" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="H14" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="15">
@@ -5143,35 +5143,35 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>2.7</v>
       </c>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I15" t="n">
         <v>1.8</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="16">
@@ -5182,36 +5182,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.5</v>
+        <v>23.7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G16" t="n">
-        <v>11.6</v>
+        <v>10</v>
       </c>
       <c r="H16" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K16" t="n">
         <v>2.2</v>
@@ -5229,16 +5229,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -5257,7 +5257,7 @@
         <v>1.2</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="18">
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.5</v>
+        <v>23.2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G18" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="H18" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="19">
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.3</v>
+        <v>22.2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G19" t="n">
-        <v>10.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="20">
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22</v>
+        <v>22.4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="G20" t="n">
-        <v>10.5</v>
+        <v>11.3</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>1.3</v>
       </c>
       <c r="K20" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="21">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -5405,31 +5405,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>9.699999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="H21" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J21" t="n">
         <v>1.2</v>
       </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
       <c r="K21" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="22">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.7</v>
+        <v>22.9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="G22" t="n">
-        <v>9.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I22" t="n">
         <v>1.4</v>
       </c>
       <c r="J22" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="K22" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="23">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -5491,31 +5491,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="G23" t="n">
-        <v>9.4</v>
+        <v>10.9</v>
       </c>
       <c r="H23" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K23" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="24">
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.3</v>
+        <v>23.4</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="G24" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="25">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -5577,31 +5577,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G25" t="n">
-        <v>9.300000000000001</v>
+        <v>11.7</v>
       </c>
       <c r="H25" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
         <v>1.8</v>
       </c>
       <c r="J25" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="K25" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="26">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -5620,25 +5620,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>2.3</v>
       </c>
       <c r="G26" t="n">
-        <v>11.5</v>
+        <v>10.1</v>
       </c>
       <c r="H26" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
         <v>1</v>
@@ -5655,39 +5655,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="G27" t="n">
-        <v>10.1</v>
+        <v>9.4</v>
       </c>
       <c r="H27" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="I27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J27" t="n">
         <v>1.7</v>
       </c>
-      <c r="J27" t="n">
-        <v>1.3</v>
-      </c>
       <c r="K27" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="28">
@@ -5702,29 +5702,29 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.4</v>
+        <v>24</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="H28" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J28" t="n">
         <v>1.2</v>
@@ -5749,19 +5749,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G29" t="n">
-        <v>11.5</v>
+        <v>10.9</v>
       </c>
       <c r="H29" t="n">
         <v>4.5</v>
@@ -5770,7 +5770,7 @@
         <v>1.4</v>
       </c>
       <c r="J29" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="K29" t="n">
         <v>2.1</v>
@@ -5788,35 +5788,35 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>25.7</v>
+        <v>24.9</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>72.0</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="G30" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="H30" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>1.2</v>
       </c>
       <c r="K30" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="31">
@@ -5831,35 +5831,35 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.2</v>
+        <v>25.9</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>3</v>
       </c>
       <c r="G31" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="H31" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I31" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J31" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="K31" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
   </sheetData>
@@ -5941,39 +5941,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="3">
@@ -5984,36 +5984,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.5</v>
+        <v>21.1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="G3" t="n">
-        <v>15.2</v>
+        <v>14.7</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K3" t="n">
         <v>3.1</v>
@@ -6027,39 +6027,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19.5</v>
+        <v>21.3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="G4" t="n">
-        <v>14.6</v>
+        <v>15.2</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I4" t="n">
         <v>1.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="5">
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G5" t="n">
-        <v>14.5</v>
+        <v>13.6</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="6">
@@ -6113,36 +6113,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.5</v>
+        <v>18.8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G6" t="n">
-        <v>13.5</v>
+        <v>14.4</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="K6" t="n">
         <v>2.8</v>
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="G7" t="n">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
@@ -6203,32 +6203,32 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.1</v>
+        <v>19.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>0.9</v>
       </c>
       <c r="G8" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="H8" t="n">
         <v>3.7</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K8" t="n">
         <v>2.4</v>
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>13.9</v>
+        <v>13.5</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="K9" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="10">
@@ -6285,36 +6285,36 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.1</v>
+        <v>19.3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="G10" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J10" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>2.6</v>
@@ -6336,31 +6336,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1.4</v>
       </c>
       <c r="G11" t="n">
-        <v>14.7</v>
+        <v>14.4</v>
       </c>
       <c r="H11" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J11" t="n">
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.8</v>
+        <v>18</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="G12" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="H12" t="n">
         <v>3.6</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="K12" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.5</v>
+        <v>21.1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>68.2</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="G13" t="n">
-        <v>12.2</v>
+        <v>14.2</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="I13" t="n">
         <v>1.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="K13" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="14">
@@ -6461,26 +6461,26 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G14" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="H14" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="I14" t="n">
         <v>1.3</v>
@@ -6489,7 +6489,7 @@
         <v>1.9</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="15">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.3</v>
+        <v>22.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>68.1</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="G15" t="n">
-        <v>15.1</v>
+        <v>13.7</v>
       </c>
       <c r="H15" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="16">
@@ -6547,35 +6547,35 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1.5</v>
       </c>
       <c r="G16" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="H16" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J16" t="n">
         <v>1.9</v>
       </c>
-      <c r="J16" t="n">
-        <v>2</v>
-      </c>
       <c r="K16" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="17">
@@ -6586,39 +6586,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>19.4</v>
+        <v>21.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1.2</v>
       </c>
       <c r="G17" t="n">
-        <v>13.5</v>
+        <v>12.3</v>
       </c>
       <c r="H17" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="18">
@@ -6633,35 +6633,35 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21</v>
+        <v>20.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1.2</v>
       </c>
       <c r="G18" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="H18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J18" t="n">
         <v>1.8</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="19">
@@ -6672,39 +6672,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.8</v>
+        <v>22.2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="G19" t="n">
-        <v>14.3</v>
+        <v>13.9</v>
       </c>
       <c r="H19" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="K19" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="20">
@@ -6715,39 +6715,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.4</v>
+        <v>22.7</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G20" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="H20" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="K20" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="21">
@@ -6758,36 +6758,36 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>20.7</v>
+        <v>22.6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="G21" t="n">
-        <v>14.2</v>
+        <v>11.8</v>
       </c>
       <c r="H21" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="K21" t="n">
         <v>2.4</v>
@@ -6801,39 +6801,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.5</v>
+        <v>20.9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>58.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="H22" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="23">
@@ -6844,39 +6844,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.3</v>
+        <v>23.9</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="G23" t="n">
-        <v>12</v>
+        <v>14.2</v>
       </c>
       <c r="H23" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="K23" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="24">
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>18.2</v>
+        <v>21.9</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G24" t="n">
-        <v>12.8</v>
+        <v>15.6</v>
       </c>
       <c r="H24" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J24" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="25">
@@ -6930,39 +6930,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22.1</v>
+        <v>23.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>15.7</v>
+        <v>15.1</v>
       </c>
       <c r="H25" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="K25" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="26">
@@ -6973,20 +6973,20 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>20.9</v>
+        <v>21.8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -6996,13 +6996,13 @@
         <v>14.1</v>
       </c>
       <c r="H26" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
-        <v>1.7</v>
+        <v>2.7</v>
       </c>
       <c r="K26" t="n">
         <v>2.1</v>
@@ -7016,36 +7016,36 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>22.3</v>
+        <v>20.6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G27" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="H27" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="K27" t="n">
         <v>2.2</v>
@@ -7063,35 +7063,35 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1.3</v>
       </c>
       <c r="G28" t="n">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="H28" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I28" t="n">
         <v>1.3</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="K28" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="29">
@@ -7102,39 +7102,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24</v>
+        <v>24.3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>56.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>69.1</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G29" t="n">
-        <v>15.2</v>
+        <v>15.5</v>
       </c>
       <c r="H29" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="30">
@@ -7145,39 +7145,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G30" t="n">
-        <v>15.7</v>
+        <v>15.4</v>
       </c>
       <c r="H30" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="K30" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="31">
@@ -7192,16 +7192,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>59.2</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>67.6</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -7211,16 +7211,16 @@
         <v>16.1</v>
       </c>
       <c r="H31" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I31" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="K31" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
   </sheetData>

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -563,16 +563,16 @@
         <v>6.5</v>
       </c>
       <c r="H3" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J3" t="n">
         <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -587,26 +587,26 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G4" t="n">
         <v>5.8</v>
       </c>
       <c r="H4" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="I4" t="n">
         <v>2.5</v>
@@ -630,11 +630,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -646,7 +646,7 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H5" t="n">
         <v>7.9</v>
@@ -673,20 +673,20 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.5</v>
+        <v>23.8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G6" t="n">
         <v>6.2</v>
@@ -759,16 +759,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -798,7 +798,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -806,31 +806,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G9" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="H9" t="n">
-        <v>8.6</v>
+        <v>7.1</v>
       </c>
       <c r="I9" t="n">
         <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="10">
@@ -841,39 +841,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23.1</v>
+        <v>24.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G10" t="n">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="11">
@@ -884,39 +884,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24.6</v>
+        <v>23.3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G11" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="H11" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="12">
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.9</v>
+        <v>27.4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G13" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="14">
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>27.4</v>
+        <v>23.2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="H14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="15">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1064,31 +1064,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>2.9</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="H15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="16">
@@ -1099,15 +1099,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.6</v>
+        <v>23.3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1116,22 +1116,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G16" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="H16" t="n">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="17">
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.5</v>
+        <v>23.9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>5.4</v>
+        <v>6.3</v>
       </c>
       <c r="H17" t="n">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="I17" t="n">
         <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K17" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="18">
@@ -1185,39 +1185,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24.9</v>
+        <v>24.1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="H18" t="n">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="19">
@@ -1236,16 +1236,16 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G19" t="n">
         <v>6.2</v>
@@ -1271,39 +1271,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.1</v>
+        <v>24.4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G20" t="n">
-        <v>5.2</v>
+        <v>6.1</v>
       </c>
       <c r="H20" t="n">
-        <v>9.1</v>
+        <v>9.5</v>
       </c>
       <c r="I20" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K20" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="21">
@@ -1314,30 +1314,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.4</v>
+        <v>24.9</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="G21" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="H21" t="n">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I21" t="n">
         <v>1.9</v>
@@ -1346,7 +1346,7 @@
         <v>0.5</v>
       </c>
       <c r="K21" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="22">
@@ -1486,39 +1486,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.5</v>
+        <v>26.4</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="H25" t="n">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K25" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="26">
@@ -1529,39 +1529,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>26.4</v>
+        <v>24.5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="G26" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="H26" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="I26" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K26" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="27">
@@ -1572,39 +1572,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.7</v>
+        <v>24.6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G27" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="H27" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="28">
@@ -1615,39 +1615,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.5</v>
+        <v>24.1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="G28" t="n">
-        <v>6.9</v>
+        <v>5.7</v>
       </c>
       <c r="H28" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K28" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="29">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1684,7 +1684,7 @@
         <v>9</v>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0.5</v>
@@ -1705,11 +1705,11 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G30" t="n">
         <v>6.6</v>
@@ -1905,16 +1905,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -1924,7 +1924,7 @@
         <v>6.5</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I3" t="n">
         <v>1.3</v>
@@ -1948,26 +1948,26 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
         <v>1.9</v>
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -2010,7 +2010,7 @@
         <v>6.7</v>
       </c>
       <c r="H5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I5" t="n">
         <v>1.5</v>
@@ -2030,39 +2030,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.9</v>
+        <v>23.2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="H6" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="7">
@@ -2073,39 +2073,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G7" t="n">
-        <v>5.9</v>
+        <v>6.9</v>
       </c>
       <c r="H7" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
@@ -2116,39 +2116,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23.3</v>
+        <v>22.6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="H8" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9">
@@ -2159,39 +2159,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="G9" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="H9" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>0.5</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -2202,39 +2202,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23.6</v>
+        <v>22.8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="G10" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="H10" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="11">
@@ -2245,39 +2245,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.4</v>
+        <v>23.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G11" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="12">
@@ -2288,39 +2288,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="G12" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="H12" t="n">
         <v>5.4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="13">
@@ -2331,39 +2331,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="H13" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
         <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="14">
@@ -2374,39 +2374,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24.6</v>
+        <v>22.3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2</v>
+        <v>7.3</v>
       </c>
       <c r="H14" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I14" t="n">
         <v>1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="15">
@@ -2417,20 +2417,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -2440,16 +2440,16 @@
         <v>6.6</v>
       </c>
       <c r="H15" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="I15" t="n">
         <v>1.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -2460,39 +2460,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23</v>
+        <v>24.5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="G16" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="H16" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0.8</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="17">
@@ -2503,39 +2503,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.3</v>
+        <v>23</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="G17" t="n">
         <v>6.8</v>
       </c>
       <c r="H17" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="I17" t="n">
         <v>1.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="18">
@@ -2550,23 +2550,23 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>3.1</v>
       </c>
       <c r="G18" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="H18" t="n">
         <v>5.8</v>
@@ -2589,39 +2589,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.1</v>
+        <v>22.3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="H19" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K19" t="n">
-        <v>3.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -2632,39 +2632,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.1</v>
+        <v>24.1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="G20" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="H20" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="21">
@@ -2675,39 +2675,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.6</v>
+        <v>23.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="G21" t="n">
-        <v>6.9</v>
+        <v>6.3</v>
       </c>
       <c r="H21" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>0.6</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22">
@@ -2718,39 +2718,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.1</v>
+        <v>24.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>84.1</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="G22" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="H22" t="n">
-        <v>6.5</v>
+        <v>5.4</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23">
@@ -2761,39 +2761,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="G23" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="H23" t="n">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
       <c r="I23" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K23" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="24">
@@ -2804,39 +2804,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.5</v>
+        <v>23.9</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="G24" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="25">
@@ -2890,39 +2890,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25</v>
+        <v>24.1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="G26" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="H26" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="27">
@@ -2933,39 +2933,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.5</v>
+        <v>25</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="G27" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="H27" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="I27" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2976,39 +2976,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.3</v>
+        <v>23.5</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="G28" t="n">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K28" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="29">
@@ -3023,26 +3023,26 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="H29" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
         <v>2.2</v>
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.8</v>
+        <v>24.5</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3118,14 +3118,14 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>3.5</v>
       </c>
       <c r="G31" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="H31" t="n">
         <v>5.3</v>
@@ -3134,7 +3134,7 @@
         <v>2</v>
       </c>
       <c r="J31" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K31" t="n">
         <v>3.1</v>
@@ -3219,39 +3219,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.9</v>
+        <v>20.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>7.1</v>
+        <v>7.9</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="3">
@@ -3262,39 +3262,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.4</v>
+        <v>22.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -3313,31 +3313,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
         <v>3.1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K4" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="5">
@@ -3348,39 +3348,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20.6</v>
+        <v>22.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G5" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="H5" t="n">
         <v>4.5</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="6">
@@ -3434,39 +3434,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.3</v>
+        <v>20.6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="H7" t="n">
         <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
@@ -3524,32 +3524,32 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>2.4</v>
       </c>
       <c r="G9" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="H9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K9" t="n">
         <v>2.3</v>
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.4</v>
+        <v>21.1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G10" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="H10" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="11">
@@ -3606,20 +3606,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -3629,16 +3629,16 @@
         <v>7.5</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -3649,36 +3649,36 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21.1</v>
+        <v>22.9</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G12" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I12" t="n">
         <v>1.6</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="K12" t="n">
         <v>2.7</v>
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.5</v>
+        <v>21.7</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="G13" t="n">
-        <v>8.800000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="H13" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="14">
@@ -3735,39 +3735,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.6</v>
+        <v>23.6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="G14" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="15">
@@ -3778,36 +3778,36 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.2</v>
+        <v>22.7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G15" t="n">
-        <v>7.3</v>
+        <v>8.6</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K15" t="n">
         <v>2.7</v>
@@ -3821,36 +3821,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G16" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="H16" t="n">
-        <v>5.2</v>
+        <v>4.3</v>
       </c>
       <c r="I16" t="n">
         <v>1.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K16" t="n">
         <v>2.7</v>
@@ -3864,36 +3864,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="G17" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="H17" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K17" t="n">
         <v>2.5</v>
@@ -3907,39 +3907,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.6</v>
+        <v>22.9</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G18" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="H18" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K18" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="19">
@@ -3950,39 +3950,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.9</v>
+        <v>22.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="G19" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="20">
@@ -3993,39 +3993,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.2</v>
+        <v>22.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G20" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
         <v>0.8</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="21">
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.6</v>
+        <v>24.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="G22" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="H22" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -4126,26 +4126,26 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.9</v>
+        <v>23.6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G23" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I23" t="n">
         <v>1.7</v>
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26.6</v>
+        <v>23.7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="G24" t="n">
-        <v>7.3</v>
+        <v>8.6</v>
       </c>
       <c r="H24" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="K24" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="25">
@@ -4208,39 +4208,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.7</v>
+        <v>26.6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="G25" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
       <c r="H25" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="K25" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="26">
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4337,39 +4337,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.3</v>
+        <v>23.7</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H28" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="29">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -4388,31 +4388,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="G29" t="n">
-        <v>8.699999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="H29" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K29" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -4423,39 +4423,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>23.7</v>
+        <v>24.3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="G30" t="n">
-        <v>7.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I30" t="n">
         <v>1.9</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="31">
@@ -4584,26 +4584,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G2" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I2" t="n">
         <v>1.3</v>
@@ -4631,22 +4631,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1.9</v>
       </c>
       <c r="G3" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I3" t="n">
         <v>1.6</v>
@@ -4713,11 +4713,11 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4726,10 +4726,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="G5" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="H5" t="n">
         <v>3.4</v>
@@ -4738,7 +4738,7 @@
         <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K5" t="n">
         <v>2</v>
@@ -4799,11 +4799,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4815,7 +4815,7 @@
         <v>1.9</v>
       </c>
       <c r="G7" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="H7" t="n">
         <v>4.4</v>
@@ -5143,16 +5143,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -5186,11 +5186,11 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -5199,7 +5199,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G16" t="n">
         <v>10</v>
@@ -5245,7 +5245,7 @@
         <v>2.2</v>
       </c>
       <c r="G17" t="n">
-        <v>10.8</v>
+        <v>11.1</v>
       </c>
       <c r="H17" t="n">
         <v>4.1</v>
@@ -5311,36 +5311,36 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.2</v>
+        <v>23.2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>9.199999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="H19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K19" t="n">
         <v>2.2</v>
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="G20" t="n">
-        <v>11.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H20" t="n">
         <v>4.6</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="21">
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I21" t="n">
         <v>2</v>
-      </c>
-      <c r="G21" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="H21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.6</v>
       </c>
       <c r="J21" t="n">
         <v>1.2</v>
       </c>
       <c r="K21" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="22">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.9</v>
+        <v>22.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="G22" t="n">
-        <v>9.699999999999999</v>
+        <v>11.7</v>
       </c>
       <c r="H22" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="K22" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23">
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22.8</v>
+        <v>23.3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="G23" t="n">
-        <v>10.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="24">
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.4</v>
+        <v>23.7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="G24" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="H24" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="25">
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G25" t="n">
-        <v>11.7</v>
+        <v>11.3</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>1.4</v>
       </c>
       <c r="K25" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="26">
@@ -5612,39 +5612,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.9</v>
+        <v>23.3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="G26" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K26" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="27">
@@ -5702,23 +5702,23 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>2</v>
       </c>
       <c r="G28" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="H28" t="n">
         <v>4.5</v>
@@ -5788,16 +5788,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -5813,10 +5813,10 @@
         <v>1.9</v>
       </c>
       <c r="J30" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K30" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="31">
@@ -5984,39 +5984,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.1</v>
+        <v>20</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1.2</v>
       </c>
       <c r="G3" t="n">
-        <v>14.7</v>
+        <v>13.6</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J3" t="n">
         <v>1.9</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="4">
@@ -6027,30 +6027,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="G4" t="n">
-        <v>15.2</v>
+        <v>14.8</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I4" t="n">
         <v>1.4</v>
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>21.3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="G5" t="n">
-        <v>13.6</v>
+        <v>15.4</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I5" t="n">
         <v>1.3</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -6113,39 +6113,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18.8</v>
+        <v>17.8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G6" t="n">
-        <v>14.4</v>
+        <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="K6" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7">
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.9</v>
+        <v>19</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>13</v>
+        <v>14.4</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="I7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J7" t="n">
         <v>1.7</v>
       </c>
-      <c r="J7" t="n">
-        <v>2.1</v>
-      </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="8">
@@ -6418,11 +6418,11 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6431,22 +6431,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G13" t="n">
         <v>14.2</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
         <v>1.4</v>
       </c>
       <c r="J13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="14">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.1</v>
+        <v>22.6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>68.2</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I14" t="n">
         <v>1.2</v>
       </c>
-      <c r="G14" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.3</v>
-      </c>
       <c r="J14" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="15">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.9</v>
+        <v>21.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>68.1</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G15" t="n">
-        <v>13.7</v>
+        <v>12.3</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="16">
@@ -6586,39 +6586,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1.2</v>
       </c>
       <c r="G17" t="n">
-        <v>12.3</v>
+        <v>15.3</v>
       </c>
       <c r="H17" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J17" t="n">
         <v>1.8</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="18">
@@ -6629,36 +6629,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>20.6</v>
+        <v>22.2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="G18" t="n">
-        <v>15.3</v>
+        <v>11.7</v>
       </c>
       <c r="H18" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="K18" t="n">
         <v>2.4</v>
@@ -6672,39 +6672,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.2</v>
+        <v>21.1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G19" t="n">
-        <v>13.9</v>
+        <v>14.3</v>
       </c>
       <c r="H19" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="I19" t="n">
         <v>1.3</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="20">
@@ -6715,39 +6715,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="F20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G20" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J20" t="n">
         <v>1.5</v>
       </c>
-      <c r="G20" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="H20" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2.4</v>
-      </c>
       <c r="K20" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="21">
@@ -6758,39 +6758,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="G21" t="n">
-        <v>11.8</v>
+        <v>14.2</v>
       </c>
       <c r="H21" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="I21" t="n">
         <v>1.4</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="22">
@@ -6805,16 +6805,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>58.2</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -6891,16 +6891,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -6977,23 +6977,23 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>21.8</v>
+        <v>22.1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G26" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="H26" t="n">
         <v>4.5</v>
@@ -7002,7 +7002,7 @@
         <v>1.6</v>
       </c>
       <c r="J26" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="K26" t="n">
         <v>2.1</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -7082,13 +7082,13 @@
         <v>16.2</v>
       </c>
       <c r="H28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J28" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="K28" t="n">
         <v>2.6</v>
@@ -7106,7 +7106,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>69.1</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -7125,7 +7125,7 @@
         <v>15.5</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I29" t="n">
         <v>1.6</v>
@@ -7192,7 +7192,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.4</v>
+        <v>25.7</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -7201,17 +7201,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>67.6</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1.3</v>
       </c>
       <c r="G31" t="n">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
       <c r="H31" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I31" t="n">
         <v>1.8</v>

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -501,11 +501,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -523,13 +523,13 @@
         <v>8.699999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="n">
         <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="3">
@@ -626,39 +626,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.7</v>
+        <v>21</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="H5" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="6">
@@ -669,39 +669,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.8</v>
+        <v>22.7</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="H6" t="n">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="7">
@@ -712,39 +712,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.1</v>
+        <v>23.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="G7" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="H7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="8">
@@ -798,39 +798,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23.2</v>
+        <v>24.9</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="H9" t="n">
-        <v>7.1</v>
+        <v>8.6</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="10">
@@ -841,39 +841,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24.9</v>
+        <v>23.2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G10" t="n">
-        <v>6.8</v>
+        <v>6.1</v>
       </c>
       <c r="H10" t="n">
-        <v>8.6</v>
+        <v>7.1</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="11">
@@ -884,39 +884,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.3</v>
+        <v>24.9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="G11" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="H11" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="12">
@@ -927,39 +927,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25</v>
+        <v>23.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="G12" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="H12" t="n">
-        <v>8.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="13">
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>27.4</v>
+        <v>23.2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="H13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="K13" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14">
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.2</v>
+        <v>23.5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="H14" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="15">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>2.9</v>
       </c>
       <c r="G15" t="n">
-        <v>5.4</v>
+        <v>6.1</v>
       </c>
       <c r="H15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="16">
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.3</v>
+        <v>27.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G16" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="17">
@@ -1185,39 +1185,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24.1</v>
+        <v>24.9</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="G18" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="H18" t="n">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="19">
@@ -1271,39 +1271,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.4</v>
+        <v>24</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>3.1</v>
       </c>
       <c r="G20" t="n">
-        <v>6.1</v>
+        <v>5.2</v>
       </c>
       <c r="H20" t="n">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K20" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="21">
@@ -1314,30 +1314,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.9</v>
+        <v>24.4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="G21" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="H21" t="n">
-        <v>8.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="I21" t="n">
         <v>1.9</v>
@@ -1346,7 +1346,7 @@
         <v>0.5</v>
       </c>
       <c r="K21" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="22">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1426,7 +1426,7 @@
         <v>7.6</v>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J23" t="n">
         <v>0.8</v>
@@ -1529,39 +1529,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H26" t="n">
-        <v>7.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K26" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="27">
@@ -1572,39 +1572,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="H27" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K27" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="28">
@@ -1615,39 +1615,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.1</v>
+        <v>26.8</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="G28" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="H28" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="I28" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K28" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="29">
@@ -1658,39 +1658,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.8</v>
+        <v>24.4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="H29" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K29" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="30">
@@ -1705,26 +1705,26 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G30" t="n">
         <v>6.6</v>
       </c>
       <c r="H30" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I30" t="n">
         <v>2.4</v>
@@ -1733,7 +1733,7 @@
         <v>0.7</v>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="31">
@@ -1862,16 +1862,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -1887,7 +1887,7 @@
         <v>1.2</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K2" t="n">
         <v>2.5</v>
@@ -1987,39 +1987,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="H5" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="I5" t="n">
         <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="6">
@@ -2030,39 +2030,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="G6" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="H6" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="I6" t="n">
         <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="7">
@@ -2081,12 +2081,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -2159,39 +2159,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="G9" t="n">
-        <v>7.6</v>
+        <v>6.1</v>
       </c>
       <c r="H9" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J9" t="n">
         <v>0.5</v>
       </c>
       <c r="K9" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="10">
@@ -2202,39 +2202,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.8</v>
+        <v>23.3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="G10" t="n">
-        <v>6.1</v>
+        <v>7.6</v>
       </c>
       <c r="H10" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0.5</v>
       </c>
       <c r="K10" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11">
@@ -2288,39 +2288,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="H12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
         <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="13">
@@ -2331,39 +2331,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>3.3</v>
       </c>
       <c r="G13" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="14">
@@ -2460,39 +2460,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24.5</v>
+        <v>23.5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="H16" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="17">
@@ -2503,39 +2503,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23</v>
+        <v>24.5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="G17" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="H17" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0.8</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="18">
@@ -2546,11 +2546,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.5</v>
+        <v>23</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2559,23 +2559,23 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="G18" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="H18" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K18" t="n">
         <v>2.7</v>
@@ -2632,39 +2632,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.1</v>
+        <v>24.5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>84.1</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="G20" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="H20" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K20" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="21">
@@ -2675,39 +2675,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.1</v>
+        <v>24.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="G21" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="22">
@@ -2718,39 +2718,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.5</v>
+        <v>23.9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>84.1</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="G22" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="H22" t="n">
-        <v>5.4</v>
+        <v>6.3</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -2761,39 +2761,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.1</v>
+        <v>23.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G23" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="H23" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="24">
@@ -2808,11 +2808,11 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2851,16 +2851,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -2894,7 +2894,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2903,14 +2903,14 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>3.1</v>
       </c>
       <c r="G26" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="H26" t="n">
         <v>6</v>
@@ -2922,7 +2922,7 @@
         <v>0.5</v>
       </c>
       <c r="K26" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="27">
@@ -2933,39 +2933,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>25</v>
+        <v>23.5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="G27" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="H27" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
         <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="28">
@@ -2976,39 +2976,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.5</v>
+        <v>25</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="G28" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="H28" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J28" t="n">
         <v>0.7</v>
       </c>
       <c r="K28" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="29">
@@ -3266,11 +3266,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3282,7 +3282,7 @@
         <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H3" t="n">
         <v>3.8</v>
@@ -3294,7 +3294,7 @@
         <v>0.7</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="4">
@@ -3348,39 +3348,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.1</v>
+        <v>23.4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="6">
@@ -3391,39 +3391,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.7</v>
+        <v>20.6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>40.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>7.7</v>
+        <v>8.4</v>
       </c>
       <c r="H6" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K6" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7">
@@ -3434,39 +3434,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.6</v>
+        <v>22.1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G7" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="H7" t="n">
         <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="8">
@@ -3563,27 +3563,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.1</v>
+        <v>22.6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G10" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="H10" t="n">
         <v>4.1</v>
@@ -3592,10 +3592,10 @@
         <v>1.6</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="K10" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="11">
@@ -3649,39 +3649,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.9</v>
+        <v>22.1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="G12" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="H12" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="I12" t="n">
         <v>1.6</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="K12" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="13">
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.7</v>
+        <v>21</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G13" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="H13" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="I13" t="n">
         <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="K13" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="14">
@@ -3993,39 +3993,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.6</v>
+        <v>24.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="G20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="H20" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0.8</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -4036,39 +4036,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21.7</v>
+        <v>22.6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="G21" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="I21" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K21" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="22">
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.6</v>
+        <v>22</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="G22" t="n">
-        <v>8.1</v>
+        <v>9.1</v>
       </c>
       <c r="H22" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="23">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -4231,7 +4231,7 @@
         <v>7.3</v>
       </c>
       <c r="H25" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
         <v>1.7</v>
@@ -4255,16 +4255,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -4274,7 +4274,7 @@
         <v>7.7</v>
       </c>
       <c r="H26" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I26" t="n">
         <v>1.7</v>
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.2</v>
+        <v>23.7</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>8.9</v>
+        <v>7.8</v>
       </c>
       <c r="H27" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I27" t="n">
         <v>1.9</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="28">
@@ -4337,39 +4337,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>7.8</v>
+        <v>8.9</v>
       </c>
       <c r="H28" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I28" t="n">
         <v>1.9</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K28" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="29">
@@ -4423,39 +4423,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="G30" t="n">
-        <v>8.699999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="H30" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K30" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="31">
@@ -4466,11 +4466,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4479,26 +4479,26 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="G31" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="H31" t="n">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="I31" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K31" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>
@@ -4666,36 +4666,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="G4" t="n">
-        <v>10.4</v>
+        <v>10.9</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="I4" t="n">
         <v>1.3</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
@@ -4709,39 +4709,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20.4</v>
+        <v>21.5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="G5" t="n">
-        <v>8.5</v>
+        <v>10.7</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="I5" t="n">
         <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="6">
@@ -4752,39 +4752,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.5</v>
+        <v>20.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="G6" t="n">
-        <v>10.7</v>
+        <v>8.5</v>
       </c>
       <c r="H6" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="I6" t="n">
         <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.1</v>
+        <v>21.8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="G8" t="n">
-        <v>10.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9">
@@ -4881,39 +4881,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.8</v>
+        <v>22.1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="G9" t="n">
-        <v>9.300000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="H9" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="10">
@@ -4924,39 +4924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20.6</v>
+        <v>21.6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J10" t="n">
         <v>2</v>
       </c>
-      <c r="G10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1.2</v>
-      </c>
       <c r="K10" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -4967,39 +4967,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.6</v>
+        <v>20.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="H11" t="n">
         <v>3.9</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
         <v>1.2</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12">
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.6</v>
+        <v>22.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K12" t="n">
         <v>2.8</v>
-      </c>
-      <c r="G12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2.1</v>
       </c>
     </row>
     <row r="13">
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.2</v>
+        <v>23.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="G13" t="n">
-        <v>10.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="14">
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>21.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="G14" t="n">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
         <v>1.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="15">
@@ -5139,36 +5139,36 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.8</v>
+        <v>23.2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="G15" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="H15" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>2.8</v>
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G18" t="n">
-        <v>11.1</v>
+        <v>10.2</v>
       </c>
       <c r="H18" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="I18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J18" t="n">
         <v>1.5</v>
       </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
       <c r="K18" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="19">
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="G19" t="n">
-        <v>10.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="20">
@@ -5354,36 +5354,36 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.2</v>
+        <v>23.2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="G20" t="n">
-        <v>9.199999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="H20" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K20" t="n">
         <v>2.2</v>
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="G21" t="n">
-        <v>10.9</v>
+        <v>11.7</v>
       </c>
       <c r="H21" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K21" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="22">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.6</v>
+        <v>22.3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="G22" t="n">
-        <v>11.7</v>
+        <v>9.4</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="I22" t="n">
         <v>1.7</v>
       </c>
       <c r="J22" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="23">
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.3</v>
+        <v>23.7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="G23" t="n">
-        <v>9.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="H23" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="24">
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.7</v>
+        <v>22.7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="G24" t="n">
-        <v>10.1</v>
+        <v>11.3</v>
       </c>
       <c r="H24" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="K24" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="25">
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="G25" t="n">
-        <v>11.3</v>
+        <v>10.9</v>
       </c>
       <c r="H25" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="K25" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="26">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -5675,7 +5675,7 @@
         <v>2.3</v>
       </c>
       <c r="G27" t="n">
-        <v>9.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H27" t="n">
         <v>4.2</v>
@@ -5788,7 +5788,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>25</v>
+        <v>24.7</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5797,14 +5797,14 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>2</v>
       </c>
       <c r="G30" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="H30" t="n">
         <v>4.7</v>
@@ -5992,12 +5992,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -6007,7 +6007,7 @@
         <v>13.6</v>
       </c>
       <c r="H3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I3" t="n">
         <v>1.3</v>
@@ -6027,39 +6027,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="G4" t="n">
-        <v>14.8</v>
+        <v>15.4</v>
       </c>
       <c r="H4" t="n">
         <v>4.2</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.3</v>
+        <v>17.8</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="G5" t="n">
-        <v>15.4</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="6">
@@ -6113,36 +6113,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.8</v>
+        <v>21.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1.2</v>
       </c>
       <c r="G6" t="n">
-        <v>13</v>
+        <v>14.8</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="K6" t="n">
         <v>3.1</v>
@@ -6246,35 +6246,35 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G9" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I9" t="n">
         <v>1.1</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="K9" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="10">
@@ -6289,35 +6289,35 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="H10" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
         <v>1.2</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K10" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11">
@@ -6328,39 +6328,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="G11" t="n">
-        <v>14.4</v>
+        <v>13.6</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="K11" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="12">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="G12" t="n">
-        <v>13.6</v>
+        <v>14.5</v>
       </c>
       <c r="H12" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>68.2</t>
+          <t>67.1</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G14" t="n">
-        <v>13.7</v>
+        <v>12.3</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="15">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.5</v>
+        <v>22.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>68.2</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I15" t="n">
         <v>1.2</v>
       </c>
-      <c r="G15" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.4</v>
-      </c>
       <c r="J15" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="16">
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>21.8</v>
+        <v>20.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G16" t="n">
-        <v>14.5</v>
+        <v>15.3</v>
       </c>
       <c r="H16" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="I16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J16" t="n">
         <v>1.8</v>
       </c>
-      <c r="J16" t="n">
-        <v>1.9</v>
-      </c>
       <c r="K16" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="17">
@@ -6586,36 +6586,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.6</v>
+        <v>22.2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="G17" t="n">
-        <v>15.3</v>
+        <v>11.7</v>
       </c>
       <c r="H17" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="K17" t="n">
         <v>2.4</v>
@@ -6629,39 +6629,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.2</v>
+        <v>21.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="G18" t="n">
-        <v>11.7</v>
+        <v>14.5</v>
       </c>
       <c r="H18" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="19">
@@ -6758,39 +6758,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.7</v>
+        <v>23.7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G21" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="H21" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="22">
@@ -6844,39 +6844,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.9</v>
+        <v>22.7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="G23" t="n">
         <v>14.2</v>
       </c>
       <c r="H23" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="K23" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="24">
@@ -6973,39 +6973,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>22.1</v>
+        <v>20.6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="G26" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="H26" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="K26" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="27">
@@ -7016,39 +7016,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>20.6</v>
+        <v>22.1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="G27" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="H27" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="28">
@@ -7063,29 +7063,29 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.8</v>
+        <v>24.3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1.3</v>
       </c>
       <c r="G28" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="H28" t="n">
         <v>4.4</v>
       </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>3</v>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -7110,31 +7110,31 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G29" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="H29" t="n">
         <v>4.4</v>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="K29" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="30">
@@ -7145,39 +7145,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G30" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="H30" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="31">
@@ -7192,23 +7192,23 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.7</v>
+        <v>25.6</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>59.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>67.7</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1.3</v>
       </c>
       <c r="G31" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="H31" t="n">
         <v>4.2</v>

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>22.3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -596,11 +596,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G4" t="n">
         <v>5.8</v>
@@ -615,7 +615,7 @@
         <v>0.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="5">
@@ -626,39 +626,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>22.8</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="H5" t="n">
-        <v>9.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J5" t="n">
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="6">
@@ -669,39 +669,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.7</v>
+        <v>21</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="H6" t="n">
-        <v>7.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
         <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="7">
@@ -720,12 +720,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -735,10 +735,10 @@
         <v>6.2</v>
       </c>
       <c r="H7" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J7" t="n">
         <v>0.3</v>
@@ -759,20 +759,20 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G8" t="n">
         <v>5.9</v>
@@ -798,39 +798,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24.9</v>
+        <v>23</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G9" t="n">
-        <v>6.8</v>
+        <v>6.1</v>
       </c>
       <c r="H9" t="n">
-        <v>8.6</v>
+        <v>7.1</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="10">
@@ -841,39 +841,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G10" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="H10" t="n">
-        <v>7.1</v>
+        <v>8.6</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K10" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="11">
@@ -884,36 +884,36 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="G11" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="H11" t="n">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
         <v>3.4</v>
@@ -927,39 +927,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="H12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>0.6</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.2</v>
+        <v>24.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="G13" t="n">
-        <v>5.6</v>
+        <v>6.7</v>
       </c>
       <c r="H13" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="14">
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.5</v>
+        <v>27.1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G14" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
         <v>0.4</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="15">
@@ -1060,16 +1060,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1082,13 +1082,13 @@
         <v>8.9</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
         <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="16">
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>27.1</v>
+        <v>24.2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="17">
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G17" t="n">
-        <v>6.3</v>
+        <v>5.2</v>
       </c>
       <c r="H17" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="18">
@@ -1185,39 +1185,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24.9</v>
+        <v>23.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="G18" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="H18" t="n">
-        <v>8.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="19">
@@ -1228,15 +1228,15 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1245,22 +1245,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="H19" t="n">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="I19" t="n">
         <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="20">
@@ -1271,39 +1271,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>25.1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="G20" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="H20" t="n">
-        <v>9.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K20" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="21">
@@ -1318,7 +1318,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1331,13 +1331,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G21" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H21" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="I21" t="n">
         <v>1.9</v>
@@ -1346,7 +1346,7 @@
         <v>0.5</v>
       </c>
       <c r="K21" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="22">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1380,7 +1380,7 @@
         <v>6.2</v>
       </c>
       <c r="H22" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="I22" t="n">
         <v>2.1</v>
@@ -1389,7 +1389,7 @@
         <v>0.6</v>
       </c>
       <c r="K22" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="23">
@@ -1447,16 +1447,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1466,7 +1466,7 @@
         <v>6.8</v>
       </c>
       <c r="H24" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="I24" t="n">
         <v>1.9</v>
@@ -1490,23 +1490,23 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>26.4</v>
+        <v>26.2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G25" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="H25" t="n">
         <v>8.199999999999999</v>
@@ -1529,39 +1529,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.6</v>
+        <v>24.8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="H26" t="n">
-        <v>9.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K26" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="27">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1580,31 +1580,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G27" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="H27" t="n">
-        <v>7.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="28">
@@ -1748,29 +1748,29 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.4</v>
+        <v>26.1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>3.7</v>
       </c>
       <c r="G31" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H31" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="I31" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J31" t="n">
         <v>0.6</v>
@@ -1858,39 +1858,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>21.6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H2" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="3">
@@ -1901,39 +1901,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.5</v>
+        <v>20.6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="H3" t="n">
         <v>4.9</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="4">
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.8</v>
+        <v>22</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G4" t="n">
         <v>6.4</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="J4" t="n">
         <v>0.6</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5">
@@ -1987,39 +1987,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="G5" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="I5" t="n">
         <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="6">
@@ -2030,39 +2030,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.4</v>
+        <v>22.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="G6" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="7">
@@ -2116,39 +2116,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.6</v>
+        <v>23.2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G8" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="H8" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="9">
@@ -2159,39 +2159,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.8</v>
+        <v>23.4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="G9" t="n">
-        <v>6.1</v>
+        <v>7.6</v>
       </c>
       <c r="H9" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>0.5</v>
       </c>
       <c r="K9" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="10">
@@ -2202,39 +2202,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23.3</v>
+        <v>23</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="G10" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="H10" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K10" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="11">
@@ -2245,39 +2245,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G11" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="H11" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="12">
@@ -2288,39 +2288,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>3.3</v>
       </c>
       <c r="G12" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H12" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="13">
@@ -2331,39 +2331,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.1</v>
+        <v>22.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2</v>
+        <v>7.3</v>
       </c>
       <c r="H13" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="14">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2382,31 +2382,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="H14" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.9</v>
+        <v>24.3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G15" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="H15" t="n">
-        <v>5.9</v>
+        <v>4.8</v>
       </c>
       <c r="I15" t="n">
         <v>1.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K15" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="16">
@@ -2460,39 +2460,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.5</v>
+        <v>23</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="G16" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="H16" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="17">
@@ -2503,39 +2503,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.5</v>
+        <v>23.1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>3.2</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="H17" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="I17" t="n">
         <v>1.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K17" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
@@ -2546,39 +2546,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="G18" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H18" t="n">
         <v>5.2</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="19">
@@ -2589,39 +2589,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.3</v>
+        <v>23.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G19" t="n">
         <v>6.7</v>
       </c>
       <c r="H19" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J19" t="n">
         <v>0.6</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="20">
@@ -2632,39 +2632,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.5</v>
+        <v>23.4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>84.1</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>3.7</v>
       </c>
       <c r="G20" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="H20" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="21">
@@ -2675,39 +2675,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="G21" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="H21" t="n">
-        <v>5.3</v>
+        <v>6.3</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K21" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="22">
@@ -2718,39 +2718,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.9</v>
+        <v>24.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="G22" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="H22" t="n">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23">
@@ -2761,39 +2761,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.1</v>
+        <v>23.8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="G23" t="n">
         <v>6.3</v>
       </c>
       <c r="H23" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="n">
         <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="24">
@@ -2804,39 +2804,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.8</v>
+        <v>23.1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="G24" t="n">
         <v>6.3</v>
       </c>
       <c r="H24" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
         <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="25">
@@ -2933,39 +2933,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.5</v>
+        <v>24.9</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="G27" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="H27" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="I27" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="28">
@@ -2976,39 +2976,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>25</v>
+        <v>23.3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="G28" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="H28" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0.7</v>
       </c>
       <c r="K28" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="29">
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3036,13 +3036,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G29" t="n">
         <v>7.5</v>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I29" t="n">
         <v>2.2</v>
@@ -3051,7 +3051,7 @@
         <v>0.7</v>
       </c>
       <c r="K29" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="30">
@@ -3070,12 +3070,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -3131,10 +3131,10 @@
         <v>5.3</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K31" t="n">
         <v>3.1</v>
@@ -3223,20 +3223,20 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G2" t="n">
         <v>7.9</v>
@@ -3309,16 +3309,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -3328,7 +3328,7 @@
         <v>7.2</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I4" t="n">
         <v>1.8</v>
@@ -3438,16 +3438,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.1</v>
+        <v>22.4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -3460,7 +3460,7 @@
         <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J7" t="n">
         <v>0.4</v>
@@ -3477,39 +3477,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.5</v>
+        <v>22.3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="G8" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="H8" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="I8" t="n">
         <v>1.7</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K8" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -3520,39 +3520,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.8</v>
+        <v>21.6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="H9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K9" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="10">
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.6</v>
+        <v>20.8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="G10" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="I10" t="n">
         <v>1.6</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K10" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="11">
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.4</v>
+        <v>21</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G11" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="H11" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="12">
@@ -3692,27 +3692,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21</v>
+        <v>22.6</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G13" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="H13" t="n">
         <v>4.1</v>
@@ -3721,10 +3721,10 @@
         <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="14">
@@ -3782,11 +3782,11 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3798,7 +3798,7 @@
         <v>2.8</v>
       </c>
       <c r="G15" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="H15" t="n">
         <v>5.2</v>
@@ -3829,19 +3829,19 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>2.7</v>
       </c>
       <c r="G16" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="H16" t="n">
         <v>4.3</v>
@@ -3864,39 +3864,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G17" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="H17" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="18">
@@ -3907,39 +3907,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.9</v>
+        <v>22.4</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="G18" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="19">
@@ -3950,36 +3950,36 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="G19" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="H19" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K19" t="n">
         <v>2.5</v>
@@ -3993,39 +3993,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.6</v>
+        <v>22</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
       <c r="G20" t="n">
-        <v>8.1</v>
+        <v>9.1</v>
       </c>
       <c r="H20" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="21">
@@ -4040,16 +4040,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4059,7 +4059,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I21" t="n">
         <v>1.8</v>
@@ -4068,7 +4068,7 @@
         <v>0.8</v>
       </c>
       <c r="K21" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="22">
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22</v>
+        <v>24.7</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="G22" t="n">
-        <v>9.1</v>
+        <v>8</v>
       </c>
       <c r="H22" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="I22" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -4130,12 +4130,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4145,16 +4145,16 @@
         <v>8.699999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J23" t="n">
         <v>0.8</v>
       </c>
       <c r="K23" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="24">
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.7</v>
+        <v>26.6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="G24" t="n">
-        <v>8.6</v>
+        <v>7.3</v>
       </c>
       <c r="H24" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="K24" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="25">
@@ -4208,36 +4208,36 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>26.6</v>
+        <v>23.6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="G25" t="n">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
         <v>2.7</v>
@@ -4251,11 +4251,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.5</v>
+        <v>23.4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4264,26 +4264,26 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="G26" t="n">
         <v>7.7</v>
       </c>
       <c r="H26" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
         <v>0.9</v>
       </c>
       <c r="K26" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="27">
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.7</v>
+        <v>24.6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="G27" t="n">
         <v>7.8</v>
       </c>
       <c r="H27" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K27" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="28">
@@ -4341,11 +4341,11 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.2</v>
+        <v>24</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4369,7 +4369,7 @@
         <v>0.8</v>
       </c>
       <c r="K28" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="29">
@@ -4380,30 +4380,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>3.1</v>
       </c>
       <c r="G29" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="H29" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="I29" t="n">
         <v>1.8</v>
@@ -4412,7 +4412,7 @@
         <v>0.8</v>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="30">
@@ -4423,30 +4423,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>3.1</v>
       </c>
       <c r="G30" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="H30" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="I30" t="n">
         <v>1.8</v>
@@ -4455,7 +4455,7 @@
         <v>0.8</v>
       </c>
       <c r="K30" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -4623,36 +4623,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="G3" t="n">
-        <v>10.1</v>
+        <v>10.7</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K3" t="n">
         <v>3.1</v>
@@ -4666,39 +4666,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.6</v>
+        <v>20.6</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="G4" t="n">
-        <v>10.9</v>
+        <v>8.6</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J4" t="n">
         <v>1.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -4709,39 +4709,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="G5" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -4752,39 +4752,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.4</v>
+        <v>20.7</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1.8</v>
       </c>
       <c r="G6" t="n">
-        <v>8.5</v>
+        <v>10.1</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -4799,16 +4799,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.1</v>
+        <v>22.4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.8</v>
+        <v>20.4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K8" t="n">
         <v>2.4</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>2.9</v>
       </c>
     </row>
     <row r="9">
@@ -4881,39 +4881,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.1</v>
+        <v>21.4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I9" t="n">
         <v>1.4</v>
       </c>
-      <c r="G9" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.2</v>
-      </c>
       <c r="J9" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="10">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -4932,31 +4932,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G10" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="H10" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11">
@@ -4967,39 +4967,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20.6</v>
+        <v>22.4</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G11" t="n">
-        <v>9.4</v>
+        <v>10.3</v>
       </c>
       <c r="H11" t="n">
         <v>3.9</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="12">
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.3</v>
+        <v>23.5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="G12" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K12" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="13">
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.5</v>
+        <v>22.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K13" t="n">
         <v>2.8</v>
-      </c>
-      <c r="G13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2.1</v>
       </c>
     </row>
     <row r="14">
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.8</v>
+        <v>23.4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="G14" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="H14" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="15">
@@ -5139,36 +5139,36 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.2</v>
+        <v>21.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="G15" t="n">
-        <v>11.1</v>
+        <v>9.9</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J15" t="n">
         <v>1.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>2.8</v>
@@ -5182,39 +5182,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.5</v>
+        <v>22.8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="G16" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="H16" t="n">
         <v>3.6</v>
       </c>
       <c r="I16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J16" t="n">
         <v>1.5</v>
       </c>
-      <c r="J16" t="n">
-        <v>1.1</v>
-      </c>
       <c r="K16" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="17">
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="G18" t="n">
-        <v>10.2</v>
+        <v>11.1</v>
       </c>
       <c r="H18" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="19">
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>2.1</v>
       </c>
       <c r="G19" t="n">
-        <v>9.699999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="H19" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="20">
@@ -5354,36 +5354,36 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.2</v>
+        <v>22.3</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="G20" t="n">
-        <v>10.2</v>
+        <v>9.4</v>
       </c>
       <c r="H20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>2.2</v>
@@ -5401,7 +5401,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5410,14 +5410,14 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>2.2</v>
       </c>
       <c r="G21" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="H21" t="n">
         <v>4</v>
@@ -5440,30 +5440,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.3</v>
+        <v>23.8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="G22" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="I22" t="n">
         <v>1.7</v>
@@ -5472,7 +5472,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23">
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.7</v>
+        <v>23.4</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="G23" t="n">
-        <v>10.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="24">
@@ -5530,26 +5530,26 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G24" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="H24" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I24" t="n">
         <v>1.5</v>
@@ -5558,7 +5558,7 @@
         <v>1.4</v>
       </c>
       <c r="K24" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="25">
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G25" t="n">
-        <v>10.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="K25" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="26">
@@ -5616,23 +5616,23 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G26" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="H26" t="n">
         <v>4.4</v>
@@ -5655,39 +5655,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>22.9</v>
+        <v>23.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="G27" t="n">
-        <v>9.699999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="H27" t="n">
         <v>4.2</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="K27" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="28">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -5730,7 +5730,7 @@
         <v>1.2</v>
       </c>
       <c r="K28" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="29">
@@ -5984,39 +5984,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>21.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>13.6</v>
+        <v>15.3</v>
       </c>
       <c r="H3" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="I3" t="n">
         <v>1.3</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -6027,39 +6027,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.3</v>
+        <v>18</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="G4" t="n">
-        <v>15.4</v>
+        <v>13</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="5">
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.8</v>
+        <v>19.5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="6">
@@ -6113,39 +6113,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.4</v>
+        <v>19</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="G6" t="n">
-        <v>14.8</v>
+        <v>14.4</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="I6" t="n">
         <v>1.4</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="7">
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19</v>
+        <v>20.1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="G7" t="n">
-        <v>14.4</v>
+        <v>13.7</v>
       </c>
       <c r="H7" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="I7" t="n">
         <v>1.4</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="K7" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.5</v>
+        <v>21.4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="G8" t="n">
-        <v>13.2</v>
+        <v>14.7</v>
       </c>
       <c r="H8" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="K8" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="9">
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19.9</v>
+        <v>19.5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>13.6</v>
+        <v>14.3</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -6285,39 +6285,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19.5</v>
+        <v>19.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="G10" t="n">
-        <v>14.3</v>
+        <v>13.6</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J10" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K10" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11">
@@ -6418,16 +6418,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>68.2</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -6437,13 +6437,13 @@
         <v>14.2</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I13" t="n">
         <v>1.4</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="K13" t="n">
         <v>2.7</v>
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.5</v>
+        <v>22.3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>67.1</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I14" t="n">
         <v>1.2</v>
       </c>
-      <c r="G14" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.4</v>
-      </c>
       <c r="J14" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="15">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>68.2</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="G15" t="n">
-        <v>13.7</v>
+        <v>12.4</v>
       </c>
       <c r="H15" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="16">
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20.6</v>
+        <v>21.7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="G16" t="n">
-        <v>15.3</v>
+        <v>14.4</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="17">
@@ -6586,36 +6586,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.2</v>
+        <v>21.1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="G17" t="n">
-        <v>11.7</v>
+        <v>14.3</v>
       </c>
       <c r="H17" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="K17" t="n">
         <v>2.4</v>
@@ -6629,39 +6629,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21.8</v>
+        <v>20.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G18" t="n">
-        <v>14.5</v>
+        <v>15.4</v>
       </c>
       <c r="H18" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K18" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="19">
@@ -6672,39 +6672,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>57.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="H19" t="n">
-        <v>4.9</v>
+        <v>3.6</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="20">
@@ -6715,39 +6715,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="F20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I20" t="n">
         <v>1.4</v>
       </c>
-      <c r="G20" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="H20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1.3</v>
-      </c>
       <c r="J20" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="21">
@@ -6758,39 +6758,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.7</v>
+        <v>22.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="G21" t="n">
-        <v>14.3</v>
+        <v>13.8</v>
       </c>
       <c r="H21" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="K21" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="22">
@@ -6801,39 +6801,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>20.8</v>
+        <v>23.7</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="G22" t="n">
-        <v>14</v>
+        <v>14.3</v>
       </c>
       <c r="H22" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="23">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -6934,11 +6934,11 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -6950,10 +6950,10 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="H25" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -6973,39 +6973,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>20.6</v>
+        <v>22.2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="G26" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="H26" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="K26" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="27">
@@ -7016,39 +7016,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>22.1</v>
+        <v>21.2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="G27" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="H27" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="K27" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="28">
@@ -7102,39 +7102,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G29" t="n">
-        <v>15.4</v>
+        <v>15.6</v>
       </c>
       <c r="H29" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="30">
@@ -7145,39 +7145,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.2</v>
+        <v>24.6</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1.3</v>
       </c>
       <c r="G30" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="H30" t="n">
         <v>4.4</v>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="K30" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="31">

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -501,26 +501,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="H2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I2" t="n">
         <v>1.5</v>
@@ -540,39 +540,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="G3" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="H3" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J3" t="n">
         <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="4">
@@ -583,39 +583,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.3</v>
+        <v>21.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="G4" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="H4" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="I4" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
         <v>0.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="5">
@@ -673,11 +673,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -755,39 +755,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.8</v>
+        <v>22.9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>2.7</v>
       </c>
       <c r="G8" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="H8" t="n">
-        <v>8.6</v>
+        <v>7.1</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="9">
@@ -798,30 +798,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>22.3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>2.8</v>
       </c>
       <c r="G9" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="H9" t="n">
-        <v>7.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I9" t="n">
         <v>2</v>
@@ -830,7 +830,7 @@
         <v>0.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="10">
@@ -841,39 +841,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23.3</v>
+        <v>25.1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G10" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="H10" t="n">
         <v>8.6</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="11">
@@ -884,36 +884,36 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25.1</v>
+        <v>27</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K11" t="n">
         <v>3.4</v>
@@ -927,39 +927,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G12" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="H12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J12" t="n">
         <v>0.6</v>
       </c>
       <c r="K12" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="13">
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24.5</v>
+        <v>23</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="G13" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>8.1</v>
+        <v>9.1</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J13" t="n">
         <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="14">
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>27.1</v>
+        <v>24.2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="15">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.1</v>
+        <v>24.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="G15" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="H15" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
         <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="16">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1107,22 +1107,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="H16" t="n">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="I16" t="n">
         <v>2</v>
@@ -1131,7 +1131,7 @@
         <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="17">
@@ -1146,26 +1146,26 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>3.1</v>
       </c>
       <c r="G17" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I17" t="n">
         <v>2.5</v>
@@ -1174,7 +1174,7 @@
         <v>0.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="18">
@@ -1228,39 +1228,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.2</v>
+        <v>23.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G19" t="n">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="H19" t="n">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K19" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="20">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1374,13 +1374,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G22" t="n">
         <v>6.2</v>
       </c>
       <c r="H22" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I22" t="n">
         <v>2.1</v>
@@ -1389,7 +1389,7 @@
         <v>0.6</v>
       </c>
       <c r="K22" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="23">
@@ -1400,39 +1400,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>25.8</v>
+        <v>24.2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="H23" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K23" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="24">
@@ -1443,39 +1443,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.3</v>
+        <v>25.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="H24" t="n">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K24" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="25">
@@ -1533,35 +1533,35 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.8</v>
+        <v>24.4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H26" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J26" t="n">
         <v>0.5</v>
       </c>
       <c r="K26" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="27">
@@ -1572,39 +1572,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.8</v>
+        <v>26.6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="H27" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K27" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="28">
@@ -1615,39 +1615,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>26.8</v>
+        <v>24.6</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="G28" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="H28" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K28" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="29">
@@ -1658,39 +1658,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.4</v>
+        <v>25.8</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="F29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K29" t="n">
         <v>3</v>
-      </c>
-      <c r="G29" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H29" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2.9</v>
       </c>
     </row>
     <row r="30">
@@ -1701,39 +1701,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26.1</v>
+        <v>24.3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="H30" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K30" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="31">
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1757,14 +1757,14 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>3.7</v>
       </c>
       <c r="G31" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H31" t="n">
         <v>8.4</v>
@@ -1776,7 +1776,7 @@
         <v>0.6</v>
       </c>
       <c r="K31" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
   </sheetData>
@@ -1858,33 +1858,33 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G2" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J2" t="n">
         <v>0.5</v>
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>21.6</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H4" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="5">
@@ -1987,39 +1987,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="H5" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
         <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="6">
@@ -2030,39 +2030,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.4</v>
+        <v>23.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="7">
@@ -2073,39 +2073,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.9</v>
+        <v>22.4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="G7" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="8">
@@ -2116,15 +2116,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2133,22 +2133,22 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K8" t="n">
         <v>3.1</v>
-      </c>
-      <c r="G8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.5</v>
       </c>
     </row>
     <row r="9">
@@ -2202,39 +2202,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>24.2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="G10" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="H10" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J10" t="n">
         <v>0.7</v>
       </c>
       <c r="K10" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="11">
@@ -2245,39 +2245,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="G11" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="H11" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K11" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="12">
@@ -2288,39 +2288,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>84.1</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="H12" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
         <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="13">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2339,31 +2339,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="G13" t="n">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="H13" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -2374,39 +2374,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="G14" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="H14" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0.6</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="15">
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24.3</v>
+        <v>23</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="G15" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="H15" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="16">
@@ -2460,39 +2460,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G16" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
         <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="17">
@@ -2507,11 +2507,11 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2520,13 +2520,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G17" t="n">
         <v>6.6</v>
       </c>
       <c r="H17" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I17" t="n">
         <v>1.7</v>
@@ -2535,7 +2535,7 @@
         <v>0.6</v>
       </c>
       <c r="K17" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="18">
@@ -2589,39 +2589,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.5</v>
+        <v>24.1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="G19" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="H19" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="20">
@@ -2632,36 +2632,36 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="G20" t="n">
         <v>6.7</v>
       </c>
       <c r="H20" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K20" t="n">
         <v>2.7</v>
@@ -2675,15 +2675,15 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.9</v>
+        <v>25.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2692,22 +2692,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="G21" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="H21" t="n">
-        <v>6.3</v>
+        <v>4.8</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K21" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="22">
@@ -2718,39 +2718,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.5</v>
+        <v>23.4</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>3.7</v>
       </c>
       <c r="G22" t="n">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="H22" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -2761,39 +2761,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.8</v>
+        <v>24.5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="G23" t="n">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="H23" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I23" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K23" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -2804,39 +2804,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.1</v>
+        <v>23.9</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="G24" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
         <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="25">
@@ -2847,33 +2847,33 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25.1</v>
+        <v>23.3</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="G25" t="n">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="H25" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0.6</v>
@@ -2894,16 +2894,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -2913,7 +2913,7 @@
         <v>7.1</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I26" t="n">
         <v>1.8</v>
@@ -2933,39 +2933,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.9</v>
+        <v>23.2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="G27" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="H27" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="28">
@@ -2976,39 +2976,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.3</v>
+        <v>24.9</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="G28" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="H28" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K28" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="29">
@@ -3070,22 +3070,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
         <v>6.9</v>
       </c>
       <c r="H30" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="I30" t="n">
         <v>1.7</v>
@@ -3219,39 +3219,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20.4</v>
+        <v>22.4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>2.6</v>
       </c>
       <c r="G2" t="n">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="3">
@@ -3262,11 +3262,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.3</v>
+        <v>20.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3275,26 +3275,26 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="G3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="4">
@@ -3305,39 +3305,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>7.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="5">
@@ -3352,23 +3352,23 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="H5" t="n">
         <v>3.9</v>
@@ -3380,7 +3380,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="6">
@@ -3391,39 +3391,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.6</v>
+        <v>22.7</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>40.2</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G6" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="H6" t="n">
         <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="7">
@@ -3434,39 +3434,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.4</v>
+        <v>20.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G7" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="H7" t="n">
         <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="K7" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
@@ -3477,39 +3477,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.3</v>
+        <v>20.7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="G8" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="H8" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="9">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20.8</v>
+        <v>22.3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>2.5</v>
       </c>
       <c r="G10" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="H10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K10" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>7.7</v>
+        <v>8.4</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="I11" t="n">
         <v>1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="K11" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="12">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3662,20 +3662,20 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>2.6</v>
       </c>
       <c r="G12" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="H12" t="n">
         <v>3.6</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>0.9</v>
@@ -3692,33 +3692,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.6</v>
+        <v>23.2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G13" t="n">
-        <v>7.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
         <v>0.6</v>
@@ -3735,39 +3735,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.6</v>
+        <v>22.7</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>8.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="H14" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0.6</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="15">
@@ -3778,39 +3778,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G15" t="n">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="H15" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
         <v>0.8</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="16">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3829,28 +3829,28 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G16" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="H16" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K16" t="n">
         <v>2.7</v>
@@ -3864,39 +3864,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>2.7</v>
       </c>
       <c r="G17" t="n">
-        <v>6.7</v>
+        <v>8.9</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="18">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3958,31 +3958,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>2.7</v>
       </c>
       <c r="G19" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="H19" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K19" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="20">
@@ -3993,39 +3993,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22</v>
+        <v>24.4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="G20" t="n">
-        <v>9.1</v>
+        <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="I20" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K20" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -4036,39 +4036,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.8</v>
+        <v>23.5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0.8</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="22">
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.7</v>
+        <v>23.3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="G22" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="H22" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="K22" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -4122,30 +4122,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.6</v>
+        <v>22.8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="H23" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I23" t="n">
         <v>1.8</v>
@@ -4154,7 +4154,7 @@
         <v>0.8</v>
       </c>
       <c r="K23" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="24">
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26.6</v>
+        <v>22.1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="G24" t="n">
-        <v>7.3</v>
+        <v>9.1</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="25">
@@ -4208,39 +4208,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.6</v>
+        <v>26.6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="G25" t="n">
-        <v>8.5</v>
+        <v>7.2</v>
       </c>
       <c r="H25" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K25" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="26">
@@ -4251,39 +4251,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.4</v>
+        <v>24.6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="G26" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="H26" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
         <v>0.9</v>
       </c>
       <c r="K26" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="27">
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.6</v>
+        <v>23.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="G27" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="H27" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>0.9</v>
       </c>
       <c r="K27" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="28">
@@ -4380,39 +4380,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
         <v>7.7</v>
       </c>
       <c r="H29" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="I29" t="n">
         <v>1.8</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K29" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -4423,30 +4423,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>3.1</v>
       </c>
       <c r="G30" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="H30" t="n">
-        <v>5.8</v>
+        <v>4.8</v>
       </c>
       <c r="I30" t="n">
         <v>1.8</v>
@@ -4455,7 +4455,7 @@
         <v>0.8</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="31">
@@ -4470,23 +4470,23 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G31" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="H31" t="n">
         <v>4.3</v>
@@ -4498,7 +4498,7 @@
         <v>0.9</v>
       </c>
       <c r="K31" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4584,11 +4584,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4600,10 +4600,10 @@
         <v>2.4</v>
       </c>
       <c r="G2" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
         <v>1.3</v>
@@ -4666,11 +4666,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4679,26 +4679,26 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1.8</v>
       </c>
       <c r="G4" t="n">
-        <v>8.6</v>
+        <v>10.2</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -4709,39 +4709,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.6</v>
+        <v>20.6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="G5" t="n">
-        <v>10.9</v>
+        <v>8.6</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
         <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -4752,39 +4752,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.7</v>
+        <v>22.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="G6" t="n">
-        <v>10.1</v>
+        <v>10.9</v>
       </c>
       <c r="H6" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="I6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J6" t="n">
         <v>1.7</v>
       </c>
-      <c r="J6" t="n">
-        <v>1.2</v>
-      </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="7">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -4803,31 +4803,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="H7" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8">
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.4</v>
+        <v>21.4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="G8" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="K8" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9">
@@ -4881,39 +4881,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>2.4</v>
       </c>
       <c r="G9" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="H9" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="10">
@@ -4924,39 +4924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.6</v>
+        <v>20.1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K10" t="n">
         <v>2.4</v>
-      </c>
-      <c r="G10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2.8</v>
       </c>
     </row>
     <row r="11">
@@ -4967,39 +4967,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.4</v>
+        <v>23.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="G11" t="n">
-        <v>10.3</v>
+        <v>9.9</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K11" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="12">
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.5</v>
+        <v>22.1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K12" t="n">
         <v>2.8</v>
-      </c>
-      <c r="G12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2.1</v>
       </c>
     </row>
     <row r="13">
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.3</v>
+        <v>21.7</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G13" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K13" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.4</v>
+        <v>21.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="H14" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J14" t="n">
         <v>1.5</v>
       </c>
-      <c r="J14" t="n">
-        <v>1.2</v>
-      </c>
       <c r="K14" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="15">
@@ -5139,39 +5139,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.8</v>
+        <v>23.4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="G15" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="16">
@@ -5186,16 +5186,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -5208,13 +5208,13 @@
         <v>3.6</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="17">
@@ -5276,22 +5276,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>2.2</v>
       </c>
       <c r="G18" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="H18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I18" t="n">
         <v>1.5</v>
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.2</v>
+        <v>22.2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="G19" t="n">
-        <v>10.2</v>
+        <v>9.5</v>
       </c>
       <c r="H19" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="20">
@@ -5354,36 +5354,36 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.3</v>
+        <v>23</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="G20" t="n">
-        <v>9.4</v>
+        <v>10.1</v>
       </c>
       <c r="H20" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K20" t="n">
         <v>2.2</v>
@@ -5397,15 +5397,15 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.5</v>
+        <v>23.8</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -5414,19 +5414,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="G21" t="n">
-        <v>11.6</v>
+        <v>10</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="I21" t="n">
         <v>1.7</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
         <v>2.9</v>
@@ -5440,36 +5440,36 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.8</v>
+        <v>22.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G22" t="n">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="H22" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="I22" t="n">
         <v>1.7</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="K22" t="n">
         <v>2.9</v>
@@ -5487,11 +5487,11 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -5506,7 +5506,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I23" t="n">
         <v>1.4</v>
@@ -5515,7 +5515,7 @@
         <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="24">
@@ -5573,7 +5573,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -5582,26 +5582,26 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>2.3</v>
       </c>
       <c r="G25" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="H25" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>1.7</v>
       </c>
       <c r="K25" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="26">
@@ -5655,39 +5655,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.3</v>
+        <v>23.8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>10.8</v>
+        <v>10.3</v>
       </c>
       <c r="H27" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>1.2</v>
       </c>
       <c r="K27" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="28">
@@ -5698,39 +5698,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.9</v>
+        <v>23.3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="F28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I28" t="n">
         <v>2</v>
-      </c>
-      <c r="G28" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="H28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1.5</v>
       </c>
       <c r="J28" t="n">
         <v>1.2</v>
       </c>
       <c r="K28" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="29">
@@ -5754,11 +5754,11 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G29" t="n">
         <v>10.9</v>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -5804,7 +5804,7 @@
         <v>2</v>
       </c>
       <c r="G30" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="H30" t="n">
         <v>4.7</v>
@@ -5831,16 +5831,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -5850,7 +5850,7 @@
         <v>10.5</v>
       </c>
       <c r="H31" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I31" t="n">
         <v>1.7</v>
@@ -5859,7 +5859,7 @@
         <v>1.6</v>
       </c>
       <c r="K31" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
   </sheetData>
@@ -5945,7 +5945,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -5961,16 +5961,16 @@
         <v>0.6</v>
       </c>
       <c r="G2" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I2" t="n">
         <v>1.4</v>
       </c>
       <c r="J2" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="K2" t="n">
         <v>3.2</v>
@@ -5984,39 +5984,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.3</v>
+        <v>19.2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G3" t="n">
-        <v>15.3</v>
+        <v>14.3</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="4">
@@ -6031,11 +6031,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6047,19 +6047,19 @@
         <v>1.2</v>
       </c>
       <c r="G4" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="H4" t="n">
         <v>3.5</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
         <v>2.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="5">
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19.5</v>
+        <v>20.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="G5" t="n">
-        <v>13.2</v>
+        <v>13.7</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="6">
@@ -6113,39 +6113,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>21.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="G6" t="n">
-        <v>14.4</v>
+        <v>14.8</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="I6" t="n">
         <v>1.4</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="K6" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.1</v>
+        <v>19.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G7" t="n">
-        <v>13.7</v>
+        <v>13.4</v>
       </c>
       <c r="H7" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="8">
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I8" t="n">
         <v>1.3</v>
       </c>
-      <c r="G8" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="H8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.4</v>
-      </c>
       <c r="J8" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G9" t="n">
-        <v>14.3</v>
+        <v>13.2</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="K9" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="10">
@@ -6285,39 +6285,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19.9</v>
+        <v>21.5</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I10" t="n">
         <v>1.4</v>
       </c>
-      <c r="G10" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.1</v>
-      </c>
       <c r="J10" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="K10" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="11">
@@ -6328,39 +6328,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18</v>
+        <v>20.8</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="G11" t="n">
-        <v>13.6</v>
+        <v>15.4</v>
       </c>
       <c r="H11" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="K11" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18.8</v>
+        <v>19.5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J12" t="n">
         <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20.8</v>
+        <v>18.8</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G13" t="n">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14">
@@ -6461,23 +6461,23 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1.4</v>
       </c>
       <c r="G14" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="H14" t="n">
         <v>3.6</v>
@@ -6489,7 +6489,7 @@
         <v>1.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="15">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="G15" t="n">
-        <v>12.4</v>
+        <v>14.2</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="I15" t="n">
         <v>1.4</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="16">
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>21.7</v>
+        <v>17.8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="F16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G16" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I16" t="n">
         <v>1.5</v>
       </c>
-      <c r="G16" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H16" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.8</v>
-      </c>
       <c r="J16" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="K16" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="17">
@@ -6586,39 +6586,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="G17" t="n">
-        <v>14.3</v>
+        <v>14.7</v>
       </c>
       <c r="H17" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="18">
@@ -6629,36 +6629,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G18" t="n">
-        <v>15.4</v>
+        <v>14.2</v>
       </c>
       <c r="H18" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="K18" t="n">
         <v>2.4</v>
@@ -6672,39 +6672,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20.8</v>
+        <v>22.1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="G19" t="n">
-        <v>14.1</v>
+        <v>13.8</v>
       </c>
       <c r="H19" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="20">
@@ -6758,39 +6758,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.1</v>
+        <v>22.7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="F21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I21" t="n">
         <v>1.4</v>
       </c>
-      <c r="G21" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="H21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.3</v>
-      </c>
       <c r="J21" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="K21" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="22">
@@ -6801,39 +6801,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.7</v>
+        <v>21.9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="G22" t="n">
-        <v>14.3</v>
+        <v>15.4</v>
       </c>
       <c r="H22" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="K22" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -6844,39 +6844,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22.7</v>
+        <v>23.6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="H23" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="K23" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="24">
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>21.8</v>
+        <v>24.5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="G24" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="K24" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="25">
@@ -6930,39 +6930,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.6</v>
+        <v>21.1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="H25" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="K25" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="26">
@@ -6973,39 +6973,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>22.2</v>
+        <v>21.1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="G26" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="H26" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="K26" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="27">
@@ -7016,39 +7016,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>21.2</v>
+        <v>22.7</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="G27" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="H27" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="28">
@@ -7063,26 +7063,26 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1.3</v>
       </c>
       <c r="G28" t="n">
-        <v>16.3</v>
+        <v>16.1</v>
       </c>
       <c r="H28" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I28" t="n">
         <v>1.3</v>

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -630,23 +630,23 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H5" t="n">
         <v>7.9</v>
@@ -841,33 +841,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25.1</v>
+        <v>24.2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="G10" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="H10" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J10" t="n">
         <v>0.5</v>
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>25.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="H13" t="n">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="14">
@@ -1013,15 +1013,15 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24.2</v>
+        <v>23</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1033,19 +1033,19 @@
         <v>2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J14" t="n">
         <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="15">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="G15" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="H15" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="16">
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24.2</v>
+        <v>23.4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G16" t="n">
-        <v>6.3</v>
+        <v>5.2</v>
       </c>
       <c r="H16" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K16" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="17">
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>3.1</v>
       </c>
       <c r="G17" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="H17" t="n">
-        <v>9.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K17" t="n">
         <v>2.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.6</v>
       </c>
     </row>
     <row r="18">
@@ -1185,39 +1185,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.6</v>
+        <v>23.9</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G18" t="n">
         <v>5.3</v>
       </c>
       <c r="H18" t="n">
-        <v>8.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J18" t="n">
         <v>0.4</v>
       </c>
       <c r="K18" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="19">
@@ -1228,39 +1228,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.7</v>
+        <v>24.2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>5.6</v>
+        <v>6.3</v>
       </c>
       <c r="H19" t="n">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="20">
@@ -1314,20 +1314,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1337,16 +1337,16 @@
         <v>6.2</v>
       </c>
       <c r="H21" t="n">
-        <v>9.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K21" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="22">
@@ -1357,20 +1357,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>24.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1380,16 +1380,16 @@
         <v>6.2</v>
       </c>
       <c r="H22" t="n">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I22" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K22" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="23">
@@ -1400,39 +1400,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.2</v>
+        <v>25.8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>6.7</v>
+        <v>5.7</v>
       </c>
       <c r="H23" t="n">
-        <v>7.1</v>
+        <v>7.6</v>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K23" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="24">
@@ -1443,39 +1443,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25.8</v>
+        <v>24.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="H24" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K24" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="25">
@@ -1494,22 +1494,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G25" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="H25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I25" t="n">
         <v>2.2</v>
@@ -1572,39 +1572,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26.6</v>
+        <v>24.6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="G27" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="H27" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="28">
@@ -1615,39 +1615,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.6</v>
+        <v>26.6</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="G28" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="H28" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K28" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="29">
@@ -1905,20 +1905,20 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
         <v>6.3</v>
@@ -2077,26 +2077,26 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I7" t="n">
         <v>1.7</v>
@@ -2105,7 +2105,7 @@
         <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="8">
@@ -2159,39 +2159,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23.4</v>
+        <v>23</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="G9" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="H9" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K9" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="10">
@@ -2245,39 +2245,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>23.3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="H11" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K11" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12">
@@ -2288,39 +2288,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23</v>
+        <v>22.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>84.1</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="G12" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="H12" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="I12" t="n">
         <v>1.7</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -2331,39 +2331,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.3</v>
+        <v>23</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>84.1</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="G13" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="H13" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="I13" t="n">
         <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="14">
@@ -2417,30 +2417,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="G15" t="n">
         <v>6.2</v>
       </c>
       <c r="H15" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="I15" t="n">
         <v>1.8</v>
@@ -2449,7 +2449,7 @@
         <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="16">
@@ -2460,39 +2460,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>3.3</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="H16" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="17">
@@ -2503,39 +2503,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="G17" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H17" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="18">
@@ -2589,39 +2589,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.1</v>
+        <v>23.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="G19" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="H19" t="n">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K19" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="20">
@@ -2632,39 +2632,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.5</v>
+        <v>24.1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="G20" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="H20" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="21">
@@ -2675,39 +2675,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>25.1</v>
+        <v>23.8</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3.7</v>
       </c>
       <c r="G21" t="n">
-        <v>5.9</v>
+        <v>6.7</v>
       </c>
       <c r="H21" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K21" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="22">
@@ -2718,39 +2718,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.4</v>
+        <v>24.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>3.7</v>
       </c>
       <c r="G22" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="H22" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -2761,15 +2761,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.5</v>
+        <v>25.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2781,19 +2781,19 @@
         <v>3.7</v>
       </c>
       <c r="G23" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="H23" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="24">
@@ -2804,39 +2804,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.9</v>
+        <v>23.3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="G24" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="H24" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
         <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="25">
@@ -2847,39 +2847,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.3</v>
+        <v>23.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="G25" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="H25" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
         <v>0.6</v>
       </c>
       <c r="K25" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="26">
@@ -2933,39 +2933,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.2</v>
+        <v>24.8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="G27" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="H27" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="I27" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="28">
@@ -2976,39 +2976,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.9</v>
+        <v>23.2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="G28" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="H28" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K28" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="29">
@@ -3219,39 +3219,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22.4</v>
+        <v>20.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>2.6</v>
       </c>
       <c r="G2" t="n">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="H2" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="3">
@@ -3262,39 +3262,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.4</v>
+        <v>22.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>2.6</v>
       </c>
       <c r="G3" t="n">
-        <v>7.9</v>
+        <v>7.3</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="4">
@@ -3391,39 +3391,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.7</v>
+        <v>20.8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="H6" t="n">
         <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7">
@@ -3434,39 +3434,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.8</v>
+        <v>22.7</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G7" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="H7" t="n">
         <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="8">
@@ -3477,39 +3477,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>2.7</v>
       </c>
       <c r="G8" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="H8" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="9">
@@ -3520,39 +3520,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.6</v>
+        <v>20.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="H9" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="I9" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="K9" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="10">
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.3</v>
+        <v>20.8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>2.5</v>
       </c>
       <c r="G10" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="H10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="11">
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20.8</v>
+        <v>22.3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="H11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -3821,39 +3821,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G16" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="H16" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="17">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3872,28 +3872,28 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G17" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="H17" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K17" t="n">
         <v>2.7</v>
@@ -3907,39 +3907,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.4</v>
+        <v>22.7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G18" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H18" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="K18" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="19">
@@ -3950,11 +3950,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3963,26 +3963,26 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="G19" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="20">
@@ -3993,39 +3993,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.4</v>
+        <v>23.3</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="G20" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="H20" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="21">
@@ -4036,39 +4036,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.5</v>
+        <v>24.4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="G21" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="H21" t="n">
         <v>4.7</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
         <v>0.8</v>
       </c>
       <c r="K21" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>2.8</v>
       </c>
       <c r="G22" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I22" t="n">
         <v>1.7</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="23">
@@ -4255,26 +4255,26 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.6</v>
+        <v>24.3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G26" t="n">
         <v>7.8</v>
       </c>
       <c r="H26" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I26" t="n">
         <v>1.7</v>
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.3</v>
+        <v>24</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>7.6</v>
+        <v>8.9</v>
       </c>
       <c r="H27" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I27" t="n">
         <v>1.9</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K27" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="28">
@@ -4337,39 +4337,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24</v>
+        <v>23.3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G28" t="n">
-        <v>8.9</v>
+        <v>7.6</v>
       </c>
       <c r="H28" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I28" t="n">
         <v>1.9</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K28" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="29">
@@ -4380,39 +4380,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G29" t="n">
         <v>7.7</v>
       </c>
       <c r="H29" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="I29" t="n">
         <v>1.8</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="30">
@@ -4423,39 +4423,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
         <v>7.7</v>
       </c>
       <c r="H30" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="I30" t="n">
         <v>1.8</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K30" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -4713,35 +4713,35 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20.6</v>
+        <v>20.9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="G5" t="n">
         <v>8.6</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J5" t="n">
         <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="6">
@@ -4795,39 +4795,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.4</v>
+        <v>21.6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="G7" t="n">
-        <v>10.3</v>
+        <v>9.4</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="I7" t="n">
         <v>1.3</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="8">
@@ -4842,23 +4842,23 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>2.4</v>
       </c>
       <c r="G8" t="n">
-        <v>10.5</v>
+        <v>10.7</v>
       </c>
       <c r="H8" t="n">
         <v>4.3</v>
@@ -4881,39 +4881,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.6</v>
+        <v>20.1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K9" t="n">
         <v>2.4</v>
-      </c>
-      <c r="G9" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.8</v>
       </c>
     </row>
     <row r="10">
@@ -4924,39 +4924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20.1</v>
+        <v>22.4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G10" t="n">
-        <v>9.300000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="H10" t="n">
         <v>3.8</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K10" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="11">
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.2</v>
+        <v>23</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="G19" t="n">
-        <v>9.5</v>
+        <v>10.1</v>
       </c>
       <c r="H19" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="20">
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23</v>
+        <v>22.2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="G20" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="H20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="21">
@@ -5397,36 +5397,36 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.8</v>
+        <v>22.5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G21" t="n">
-        <v>10</v>
+        <v>11.7</v>
       </c>
       <c r="H21" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="I21" t="n">
         <v>1.7</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="K21" t="n">
         <v>2.9</v>
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.5</v>
+        <v>23.3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
         <v>2.2</v>
-      </c>
-      <c r="G22" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2.9</v>
       </c>
     </row>
     <row r="23">
@@ -5483,27 +5483,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="G23" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="H23" t="n">
         <v>4.4</v>
@@ -5512,10 +5512,10 @@
         <v>1.4</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K23" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="24">
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22.7</v>
+        <v>23.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="G25" t="n">
-        <v>9.6</v>
+        <v>10.3</v>
       </c>
       <c r="H25" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="K25" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="26">
@@ -5612,39 +5612,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.4</v>
+        <v>22.7</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="G26" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="H26" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="K26" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="27">
@@ -5655,36 +5655,36 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="G27" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="H27" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
         <v>2.8</v>
@@ -5702,26 +5702,26 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>2.5</v>
       </c>
       <c r="G28" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="H28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I28" t="n">
         <v>2</v>
@@ -5984,39 +5984,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.2</v>
+        <v>21.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>14.3</v>
+        <v>15.3</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -6074,32 +6074,32 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1.3</v>
       </c>
       <c r="G5" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="H5" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I5" t="n">
         <v>1.4</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>3.1</v>
@@ -6113,39 +6113,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.4</v>
+        <v>19.8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G6" t="n">
-        <v>14.8</v>
+        <v>13.4</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="7">
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19.8</v>
+        <v>21.4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I7" t="n">
         <v>1.4</v>
       </c>
-      <c r="G7" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.1</v>
-      </c>
       <c r="J7" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="K7" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.3</v>
+        <v>19.2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>15.3</v>
+        <v>14.3</v>
       </c>
       <c r="H8" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9">
@@ -6285,39 +6285,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.5</v>
+        <v>19.5</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>12.4</v>
+        <v>14.4</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="11">
@@ -6328,39 +6328,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20.8</v>
+        <v>18.8</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="G11" t="n">
-        <v>15.4</v>
+        <v>14.4</v>
       </c>
       <c r="H11" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J11" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19.5</v>
+        <v>22.2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="G12" t="n">
-        <v>14.4</v>
+        <v>13.5</v>
       </c>
       <c r="H12" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="I12" t="n">
         <v>1.2</v>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>18.8</v>
+        <v>20.8</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I13" t="n">
         <v>1.4</v>
       </c>
-      <c r="G13" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1.1</v>
-      </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="14">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.2</v>
+        <v>17.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="G14" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="H14" t="n">
         <v>3.6</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="15">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I15" t="n">
         <v>1.3</v>
       </c>
-      <c r="G15" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="H15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.4</v>
-      </c>
       <c r="J15" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="16">
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.8</v>
+        <v>21.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="G16" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
       <c r="H16" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="17">
@@ -6586,39 +6586,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1.4</v>
       </c>
       <c r="G17" t="n">
-        <v>14.7</v>
+        <v>13.7</v>
       </c>
       <c r="H17" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="18">
@@ -6629,39 +6629,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G18" t="n">
-        <v>14.2</v>
+        <v>14.7</v>
       </c>
       <c r="H18" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="19">
@@ -6672,39 +6672,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.1</v>
+        <v>20.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G19" t="n">
-        <v>13.8</v>
+        <v>15.4</v>
       </c>
       <c r="H19" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="K19" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="20">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -6744,7 +6744,7 @@
         <v>1.4</v>
       </c>
       <c r="J20" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="K20" t="n">
         <v>2.4</v>
@@ -6844,39 +6844,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.6</v>
+        <v>21.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="H23" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="24">
@@ -6930,39 +6930,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>21.1</v>
+        <v>24.1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>14.2</v>
+        <v>15.3</v>
       </c>
       <c r="H25" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
         <v>1.5</v>
       </c>
-      <c r="J25" t="n">
-        <v>2</v>
-      </c>
       <c r="K25" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="26">
@@ -7158,11 +7158,11 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G30" t="n">
         <v>15.4</v>

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -505,12 +505,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -520,7 +520,7 @@
         <v>5.6</v>
       </c>
       <c r="H2" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="I2" t="n">
         <v>1.5</v>
@@ -540,39 +540,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.9</v>
+        <v>21.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="G3" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="H3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J3" t="n">
         <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="4">
@@ -583,39 +583,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.4</v>
+        <v>22.2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="G4" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="H4" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J4" t="n">
         <v>0.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -669,39 +669,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.9</v>
+        <v>23.6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G6" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="H6" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="7">
@@ -712,39 +712,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23.8</v>
+        <v>20.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
@@ -806,12 +806,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -821,10 +821,10 @@
         <v>5.9</v>
       </c>
       <c r="H9" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J9" t="n">
         <v>0.4</v>
@@ -841,39 +841,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="G10" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>0.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="11">
@@ -884,36 +884,36 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27</v>
+        <v>24.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="H11" t="n">
-        <v>8.9</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
         <v>3.4</v>
@@ -931,11 +931,11 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1033,10 +1033,10 @@
         <v>2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H14" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>2.1</v>
@@ -1056,11 +1056,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1069,17 +1069,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>2.9</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="H15" t="n">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="I15" t="n">
         <v>2</v>
@@ -1088,7 +1088,7 @@
         <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="16">
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.4</v>
+        <v>26.9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>8.1</v>
+        <v>9</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
         <v>0.4</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="17">
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>3.1</v>
       </c>
       <c r="G17" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="H17" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="18">
@@ -1185,39 +1185,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.9</v>
+        <v>23.4</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G18" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H18" t="n">
-        <v>9.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I18" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
         <v>0.4</v>
       </c>
       <c r="K18" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="19">
@@ -1228,39 +1228,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
       <c r="H19" t="n">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K19" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="20">
@@ -1314,20 +1314,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24</v>
+        <v>24.6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1337,16 +1337,16 @@
         <v>6.2</v>
       </c>
       <c r="H21" t="n">
-        <v>8.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="I21" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K21" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="22">
@@ -1357,39 +1357,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.6</v>
+        <v>25.8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="F22" t="n">
+        <v>3</v>
+      </c>
+      <c r="G22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K22" t="n">
         <v>3.2</v>
-      </c>
-      <c r="G22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.4</v>
       </c>
     </row>
     <row r="23">
@@ -1400,39 +1400,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>25.8</v>
+        <v>24.2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>5.7</v>
+        <v>6.7</v>
       </c>
       <c r="H23" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K23" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="24">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1451,31 +1451,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>83.9</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G24" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="H24" t="n">
-        <v>7.1</v>
+        <v>8.4</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="25">
@@ -1490,26 +1490,26 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>26.2</v>
+        <v>26</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G25" t="n">
         <v>6.7</v>
       </c>
       <c r="H25" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="I25" t="n">
         <v>2.2</v>
@@ -1518,7 +1518,7 @@
         <v>0.6</v>
       </c>
       <c r="K25" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1576,11 +1576,11 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1595,7 +1595,7 @@
         <v>7.1</v>
       </c>
       <c r="H27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="I27" t="n">
         <v>1.9</v>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>26.6</v>
+        <v>26.4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1638,16 +1638,16 @@
         <v>6.5</v>
       </c>
       <c r="H28" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
         <v>0.5</v>
       </c>
       <c r="K28" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1662,11 +1662,11 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G29" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="H29" t="n">
         <v>8.800000000000001</v>
@@ -1687,7 +1687,7 @@
         <v>2.4</v>
       </c>
       <c r="J29" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K29" t="n">
         <v>3</v>
@@ -1748,7 +1748,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1757,17 +1757,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>3.7</v>
       </c>
       <c r="G31" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H31" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="I31" t="n">
         <v>2.5</v>
@@ -1862,23 +1862,23 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.9</v>
+        <v>21.6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>3.2</v>
       </c>
       <c r="G2" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H2" t="n">
         <v>5.2</v>
@@ -1948,20 +1948,20 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.9</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G4" t="n">
         <v>6.5</v>
@@ -1987,39 +1987,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23.2</v>
+        <v>22.5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J5" t="n">
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="6">
@@ -2030,39 +2030,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="H6" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="I6" t="n">
         <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="7">
@@ -2073,39 +2073,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.5</v>
+        <v>24</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H7" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="8">
@@ -2116,39 +2116,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>23.3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="G8" t="n">
-        <v>6.9</v>
+        <v>6.7</v>
       </c>
       <c r="H8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
@@ -2159,39 +2159,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H9" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J9" t="n">
         <v>0.7</v>
       </c>
       <c r="K9" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="10">
@@ -2202,39 +2202,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24.2</v>
+        <v>22.3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="G10" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="H10" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -2245,39 +2245,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.3</v>
+        <v>23</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G11" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="H11" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K11" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="12">
@@ -2288,39 +2288,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.3</v>
+        <v>23.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="H12" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
         <v>0.6</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
@@ -2331,39 +2331,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>84.1</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G13" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="H13" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="14">
@@ -2374,39 +2374,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.7</v>
+        <v>23.1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="G14" t="n">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
       <c r="H14" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="15">
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>84.1</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="H15" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
         <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="16">
@@ -2460,39 +2460,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="G16" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H16" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="17">
@@ -2503,39 +2503,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>3.5</v>
       </c>
       <c r="G17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H17" t="n">
         <v>6.2</v>
       </c>
-      <c r="H17" t="n">
-        <v>5.1</v>
-      </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="18">
@@ -2546,39 +2546,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24</v>
+        <v>23.3</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G18" t="n">
         <v>6.6</v>
       </c>
       <c r="H18" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K18" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="19">
@@ -2589,39 +2589,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>3.1</v>
       </c>
       <c r="G19" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="H19" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="20">
@@ -2632,39 +2632,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.1</v>
+        <v>23</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="G20" t="n">
         <v>6.6</v>
       </c>
       <c r="H20" t="n">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K20" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="21">
@@ -2675,39 +2675,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.8</v>
+        <v>24.8</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="G21" t="n">
-        <v>6.7</v>
+        <v>5.9</v>
       </c>
       <c r="H21" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K21" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22">
@@ -2718,39 +2718,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.5</v>
+        <v>23.8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>3.7</v>
       </c>
       <c r="G22" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="H22" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="23">
@@ -2761,15 +2761,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>25.1</v>
+        <v>24.6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2781,19 +2781,19 @@
         <v>3.7</v>
       </c>
       <c r="G23" t="n">
-        <v>5.9</v>
+        <v>7.1</v>
       </c>
       <c r="H23" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K23" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="24">
@@ -2808,29 +2808,29 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G24" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J24" t="n">
         <v>0.6</v>
@@ -2980,26 +2980,26 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>3.7</v>
       </c>
       <c r="G28" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="H28" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I28" t="n">
         <v>1.7</v>
@@ -3008,7 +3008,7 @@
         <v>0.7</v>
       </c>
       <c r="K28" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="29">
@@ -3023,26 +3023,26 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>2.9</v>
       </c>
       <c r="G29" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="H29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I29" t="n">
         <v>2.2</v>
@@ -3070,22 +3070,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="H30" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="I30" t="n">
         <v>1.7</v>
@@ -3113,16 +3113,16 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G31" t="n">
         <v>7.1</v>
@@ -3270,25 +3270,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>2.6</v>
       </c>
       <c r="G3" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="H3" t="n">
         <v>3.5</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
@@ -3309,11 +3309,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -3391,39 +3391,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.8</v>
+        <v>22.7</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G6" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="H6" t="n">
         <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="7">
@@ -3434,39 +3434,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.7</v>
+        <v>20.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G7" t="n">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="H7" t="n">
         <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
@@ -3520,11 +3520,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.7</v>
+        <v>22.3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3533,26 +3533,26 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="G9" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="K9" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="G10" t="n">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="H10" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="I10" t="n">
         <v>1.6</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="K10" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="11">
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.3</v>
+        <v>20.7</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="H11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="12">
@@ -3657,25 +3657,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G12" t="n">
         <v>7.7</v>
       </c>
       <c r="H12" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
         <v>0.9</v>
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.2</v>
+        <v>22.7</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G13" t="n">
-        <v>8.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="H13" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
         <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="14">
@@ -3735,39 +3735,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G14" t="n">
-        <v>7.2</v>
+        <v>8.5</v>
       </c>
       <c r="H14" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="15">
@@ -3782,7 +3782,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3825,35 +3825,35 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G16" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H16" t="n">
         <v>4.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
         <v>0.9</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="17">
@@ -3864,39 +3864,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G17" t="n">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="H17" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="18">
@@ -3907,39 +3907,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G18" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="19">
@@ -3950,11 +3950,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.5</v>
+        <v>22.9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3963,26 +3963,26 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="G19" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="H19" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K19" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="20">
@@ -3993,39 +3993,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.3</v>
+        <v>24.2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="G20" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -4036,39 +4036,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.4</v>
+        <v>23.5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="G21" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0.8</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="22">
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>2.8</v>
       </c>
       <c r="G22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H22" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="I22" t="n">
         <v>1.7</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="K22" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -4212,7 +4212,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>26.6</v>
+        <v>26.7</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4221,14 +4221,14 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>3.2</v>
       </c>
       <c r="G25" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="H25" t="n">
         <v>4</v>
@@ -4251,30 +4251,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="H26" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="I26" t="n">
         <v>1.7</v>
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24</v>
+        <v>24.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G27" t="n">
-        <v>8.9</v>
+        <v>7.8</v>
       </c>
       <c r="H27" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K27" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="28">
@@ -4341,16 +4341,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -4360,7 +4360,7 @@
         <v>7.6</v>
       </c>
       <c r="H28" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I28" t="n">
         <v>1.9</v>
@@ -4380,33 +4380,33 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>7.7</v>
+        <v>9</v>
       </c>
       <c r="H29" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0.8</v>
@@ -4423,39 +4423,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G30" t="n">
         <v>7.7</v>
       </c>
       <c r="H30" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="I30" t="n">
         <v>1.8</v>
       </c>
       <c r="J30" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="31">
@@ -4474,31 +4474,31 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G31" t="n">
         <v>8.5</v>
       </c>
       <c r="H31" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>
@@ -4584,23 +4584,23 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G2" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="H2" t="n">
         <v>4.1</v>
@@ -4631,7 +4631,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4643,7 +4643,7 @@
         <v>2.3</v>
       </c>
       <c r="G3" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="H3" t="n">
         <v>4.1</v>
@@ -4709,39 +4709,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20.9</v>
+        <v>22</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1.9</v>
       </c>
       <c r="G5" t="n">
-        <v>8.6</v>
+        <v>10.9</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="I5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J5" t="n">
         <v>1.6</v>
       </c>
-      <c r="J5" t="n">
-        <v>1.2</v>
-      </c>
       <c r="K5" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="6">
@@ -4752,39 +4752,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.4</v>
+        <v>20.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1.9</v>
       </c>
       <c r="G6" t="n">
-        <v>10.9</v>
+        <v>8.6</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="I6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J6" t="n">
         <v>1.2</v>
       </c>
-      <c r="J6" t="n">
-        <v>1.7</v>
-      </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="7">
@@ -4885,23 +4885,23 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="H9" t="n">
         <v>3.8</v>
@@ -4913,7 +4913,7 @@
         <v>1.2</v>
       </c>
       <c r="K9" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="10">
@@ -4928,16 +4928,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.4</v>
+        <v>22.7</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -4956,7 +4956,7 @@
         <v>1.3</v>
       </c>
       <c r="K10" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11">
@@ -4967,39 +4967,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.2</v>
+        <v>21.7</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="G11" t="n">
-        <v>9.9</v>
+        <v>11</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K11" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.1</v>
+        <v>23.5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="G12" t="n">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K12" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="13">
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G13" t="n">
-        <v>11</v>
+        <v>10.3</v>
       </c>
       <c r="H13" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J13" t="n">
         <v>1.3</v>
       </c>
-      <c r="J13" t="n">
-        <v>1.2</v>
-      </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="14">
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.8</v>
+        <v>22.4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="G14" t="n">
-        <v>9.9</v>
+        <v>11.1</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="15">
@@ -5139,39 +5139,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.4</v>
+        <v>21.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J15" t="n">
         <v>1.5</v>
       </c>
-      <c r="J15" t="n">
-        <v>1.2</v>
-      </c>
       <c r="K15" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="16">
@@ -5182,39 +5182,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.1</v>
+        <v>23.4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="G16" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="H16" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="17">
@@ -5225,39 +5225,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.3</v>
+        <v>23.1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="G17" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="H17" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="K17" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="18">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -5337,13 +5337,13 @@
         <v>4.7</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>1.2</v>
       </c>
       <c r="K19" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="20">
@@ -5358,11 +5358,11 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G20" t="n">
         <v>9.5</v>
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.5</v>
+        <v>23.3</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
         <v>2.2</v>
-      </c>
-      <c r="G21" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H21" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2.9</v>
       </c>
     </row>
     <row r="22">
@@ -5440,27 +5440,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="G22" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="H22" t="n">
         <v>4.4</v>
@@ -5469,10 +5469,10 @@
         <v>1.4</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K22" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="23">
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.1</v>
+        <v>24</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="G23" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="H23" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="24">
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>2.2</v>
       </c>
       <c r="G24" t="n">
-        <v>11.2</v>
+        <v>11.7</v>
       </c>
       <c r="H24" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="K24" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="25">
@@ -5569,27 +5569,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.8</v>
+        <v>22.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="G25" t="n">
-        <v>10.3</v>
+        <v>11.2</v>
       </c>
       <c r="H25" t="n">
         <v>4.5</v>
@@ -5598,10 +5598,10 @@
         <v>1.5</v>
       </c>
       <c r="J25" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="K25" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="26">
@@ -5655,36 +5655,36 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="G27" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="H27" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="I27" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K27" t="n">
         <v>2.8</v>
@@ -5749,12 +5749,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -5764,7 +5764,7 @@
         <v>10.9</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I29" t="n">
         <v>1.4</v>
@@ -5788,7 +5788,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5797,14 +5797,14 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>2</v>
       </c>
       <c r="G30" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="H30" t="n">
         <v>4.7</v>
@@ -5831,16 +5831,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -5859,7 +5859,7 @@
         <v>1.6</v>
       </c>
       <c r="K31" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5945,26 +5945,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19.3</v>
+        <v>19.6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>0.6</v>
       </c>
       <c r="G2" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I2" t="n">
         <v>1.4</v>
@@ -5973,7 +5973,7 @@
         <v>2.3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="3">
@@ -5988,26 +5988,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>15.3</v>
+        <v>15.5</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>1.3</v>
@@ -6027,39 +6027,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.9</v>
+        <v>20</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G4" t="n">
-        <v>13.1</v>
+        <v>13.8</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="5">
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20</v>
+        <v>18.3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G5" t="n">
-        <v>13.8</v>
+        <v>13.3</v>
       </c>
       <c r="H5" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="6">
@@ -6113,39 +6113,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19.8</v>
+        <v>21.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I6" t="n">
         <v>1.4</v>
       </c>
-      <c r="G6" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="H6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.1</v>
-      </c>
       <c r="J6" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="K6" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.4</v>
+        <v>19.3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>14.8</v>
+        <v>14.3</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="I7" t="n">
         <v>1.4</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="8">
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="G8" t="n">
-        <v>14.3</v>
+        <v>13.2</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="9">
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19.4</v>
+        <v>19.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="G9" t="n">
-        <v>13.2</v>
+        <v>13.6</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="K9" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="10">
@@ -6375,26 +6375,26 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1.4</v>
       </c>
       <c r="G12" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="H12" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I12" t="n">
         <v>1.2</v>
@@ -6403,7 +6403,7 @@
         <v>1.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="13">
@@ -6414,36 +6414,36 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20.8</v>
+        <v>18.1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G13" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J13" t="n">
         <v>1.3</v>
-      </c>
-      <c r="G13" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J13" t="n">
-        <v>2.1</v>
       </c>
       <c r="K13" t="n">
         <v>2.7</v>
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.8</v>
+        <v>21.5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>67.3</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="G14" t="n">
-        <v>13.6</v>
+        <v>12.4</v>
       </c>
       <c r="H14" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="15">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.5</v>
+        <v>20.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="G15" t="n">
-        <v>12.4</v>
+        <v>13.9</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="I15" t="n">
         <v>1.3</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="16">
@@ -6543,36 +6543,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G16" t="n">
-        <v>14.2</v>
+        <v>15.5</v>
       </c>
       <c r="H16" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K16" t="n">
         <v>2.4</v>
@@ -6586,39 +6586,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.9</v>
+        <v>21.1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G17" t="n">
-        <v>13.7</v>
+        <v>14.2</v>
       </c>
       <c r="H17" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I17" t="n">
         <v>1.3</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="18">
@@ -6629,39 +6629,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1.4</v>
       </c>
       <c r="G18" t="n">
-        <v>14.7</v>
+        <v>13.7</v>
       </c>
       <c r="H18" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="K18" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="19">
@@ -6672,39 +6672,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20.8</v>
+        <v>21.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="G19" t="n">
-        <v>15.4</v>
+        <v>14.7</v>
       </c>
       <c r="H19" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="20">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -6787,7 +6787,7 @@
         <v>1.4</v>
       </c>
       <c r="J21" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="K21" t="n">
         <v>2.2</v>
@@ -6805,16 +6805,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -6833,7 +6833,7 @@
         <v>1.9</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="23">
@@ -6848,23 +6848,23 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>58.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="H23" t="n">
         <v>3.7</v>
@@ -6873,10 +6873,10 @@
         <v>1.5</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K23" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="24">
@@ -6938,22 +6938,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="H25" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -6973,36 +6973,36 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>21.1</v>
+        <v>22.7</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="G26" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="H26" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="K26" t="n">
         <v>2.2</v>
@@ -7016,39 +7016,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>22.7</v>
+        <v>21.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="G27" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="H27" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="K27" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="28">
@@ -7063,16 +7063,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>56.6</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -7085,7 +7085,7 @@
         <v>4.3</v>
       </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J28" t="n">
         <v>3</v>
@@ -7110,7 +7110,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -7122,19 +7122,19 @@
         <v>1.3</v>
       </c>
       <c r="G29" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="H29" t="n">
         <v>4.5</v>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="30">

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -501,16 +501,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.1</v>
+        <v>21.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -520,7 +520,7 @@
         <v>5.6</v>
       </c>
       <c r="H2" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="I2" t="n">
         <v>1.5</v>
@@ -548,12 +548,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -563,7 +563,7 @@
         <v>6.5</v>
       </c>
       <c r="H3" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="I3" t="n">
         <v>1.7</v>
@@ -572,7 +572,7 @@
         <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="4">
@@ -626,39 +626,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.6</v>
+        <v>23.6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G5" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="H5" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="6">
@@ -669,39 +669,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.6</v>
+        <v>22.8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="H6" t="n">
         <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="7">
@@ -716,7 +716,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="H7" t="n">
         <v>9.199999999999999</v>
@@ -763,12 +763,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -781,7 +781,7 @@
         <v>7.1</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J8" t="n">
         <v>0.4</v>
@@ -798,39 +798,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.3</v>
+        <v>24.1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="G9" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="H9" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="10">
@@ -841,39 +841,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23.8</v>
+        <v>22.3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>2.8</v>
       </c>
       <c r="G10" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="H10" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="11">
@@ -884,33 +884,33 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24.2</v>
+        <v>25.3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="G11" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
         <v>0.5</v>
@@ -927,39 +927,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.5</v>
+        <v>23.8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="H12" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="I12" t="n">
         <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="13">
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25.3</v>
+        <v>23.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>2.7</v>
       </c>
       <c r="G13" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="H13" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="14">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24.1</v>
+        <v>26.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="16">
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26.9</v>
+        <v>23.4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="H16" t="n">
-        <v>9</v>
+        <v>8.1</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
         <v>0.4</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="17">
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.6</v>
+        <v>24.1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G17" t="n">
-        <v>5.3</v>
+        <v>6.3</v>
       </c>
       <c r="H17" t="n">
-        <v>9.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="I17" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K17" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="18">
@@ -1185,39 +1185,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G18" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H18" t="n">
-        <v>8.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>0.4</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="19">
@@ -1228,39 +1228,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.9</v>
+        <v>24.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="G19" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="H19" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I19" t="n">
         <v>1.9</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="20">
@@ -1271,39 +1271,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>25.1</v>
+        <v>24.1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="G20" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="H20" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K20" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="21">
@@ -1318,35 +1318,35 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G21" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="H21" t="n">
         <v>9.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>0.5</v>
       </c>
       <c r="K21" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="22">
@@ -1365,25 +1365,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H22" t="n">
         <v>7.6</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>0.8</v>
@@ -1404,11 +1404,11 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>8.4</v>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
         <v>0.6</v>
@@ -1529,39 +1529,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="H26" t="n">
-        <v>7.8</v>
+        <v>9.1</v>
       </c>
       <c r="I26" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K26" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="27">
@@ -1572,39 +1572,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.7</v>
+        <v>26.5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="G27" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="H27" t="n">
         <v>9.1</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="K27" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -1615,36 +1615,36 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>26.4</v>
+        <v>25.7</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="G28" t="n">
         <v>6.5</v>
       </c>
       <c r="H28" t="n">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K28" t="n">
         <v>3</v>
@@ -1658,39 +1658,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25.7</v>
+        <v>24.8</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>3.1</v>
       </c>
       <c r="G29" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="H29" t="n">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="30">
@@ -1705,16 +1705,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.3</v>
+        <v>24.7</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1733,7 +1733,7 @@
         <v>0.6</v>
       </c>
       <c r="K30" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="31">
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -1881,7 +1881,7 @@
         <v>6.3</v>
       </c>
       <c r="H2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I2" t="n">
         <v>1.2</v>
@@ -1901,39 +1901,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.8</v>
+        <v>21.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>83.9</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H3" t="n">
         <v>4.9</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="4">
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>83.9</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="5">
@@ -1987,39 +1987,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.5</v>
+        <v>23.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H5" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="6">
@@ -2030,39 +2030,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.2</v>
+        <v>22.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
         <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="7">
@@ -2073,39 +2073,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>24</v>
+        <v>23.2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="H7" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
@@ -2116,39 +2116,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23.3</v>
+        <v>24</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="G8" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="H8" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9">
@@ -2202,39 +2202,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.3</v>
+        <v>22.8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="G10" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="H10" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="11">
@@ -2245,39 +2245,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23</v>
+        <v>22.3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="G11" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="H11" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K11" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -2288,39 +2288,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>84.1</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K12" t="n">
         <v>3</v>
-      </c>
-      <c r="G12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="13">
@@ -2331,30 +2331,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.8</v>
+        <v>23.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="H13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I13" t="n">
         <v>1.5</v>
@@ -2363,7 +2363,7 @@
         <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14">
@@ -2374,39 +2374,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.1</v>
+        <v>22.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
       <c r="H14" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="15">
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>84.1</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="G15" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="H15" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="16">
@@ -2460,30 +2460,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="H16" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="I16" t="n">
         <v>1.8</v>
@@ -2492,7 +2492,7 @@
         <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="17">
@@ -2589,39 +2589,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>24.4</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="G19" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="H19" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K19" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="20">
@@ -2632,39 +2632,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="G20" t="n">
         <v>6.6</v>
       </c>
       <c r="H20" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="21">
@@ -2675,39 +2675,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.8</v>
+        <v>23</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="G21" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="H21" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
         <v>0.6</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="22">
@@ -2722,23 +2722,23 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>3.7</v>
       </c>
       <c r="G22" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="H22" t="n">
         <v>5.3</v>
@@ -2804,39 +2804,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.4</v>
+        <v>23.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="G24" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="H24" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="I24" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
         <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="25">
@@ -2847,39 +2847,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.9</v>
+        <v>23.4</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="G25" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H25" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>0.6</v>
       </c>
       <c r="K25" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="26">
@@ -2894,7 +2894,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -2913,7 +2913,7 @@
         <v>7.1</v>
       </c>
       <c r="H26" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I26" t="n">
         <v>1.8</v>
@@ -2922,7 +2922,7 @@
         <v>0.5</v>
       </c>
       <c r="K26" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="27">
@@ -2937,11 +2937,11 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2953,7 +2953,7 @@
         <v>3.9</v>
       </c>
       <c r="G27" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="H27" t="n">
         <v>5.6</v>
@@ -2980,16 +2980,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -3219,39 +3219,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>20.5</v>
+        <v>22.4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>2.6</v>
       </c>
       <c r="G2" t="n">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="3">
@@ -3262,39 +3262,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.4</v>
+        <v>22</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>7.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="4">
@@ -3305,39 +3305,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.2</v>
+        <v>20.8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="G4" t="n">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="H4" t="n">
         <v>3.8</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="5">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -3371,7 +3371,7 @@
         <v>7.6</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I5" t="n">
         <v>1.3</v>
@@ -3391,39 +3391,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.7</v>
+        <v>20.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7">
@@ -3434,39 +3434,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.8</v>
+        <v>22.7</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G7" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="H7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="8">
@@ -3520,11 +3520,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.3</v>
+        <v>20.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -3533,26 +3533,26 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="H9" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="10">
@@ -3563,36 +3563,36 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20.7</v>
+        <v>22.6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I10" t="n">
         <v>1.6</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="K10" t="n">
         <v>2.7</v>
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20.7</v>
+        <v>22.3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="H11" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -3649,36 +3649,36 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>20.7</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="G12" t="n">
-        <v>7.7</v>
+        <v>8.4</v>
       </c>
       <c r="H12" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="I12" t="n">
         <v>1.6</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K12" t="n">
         <v>2.3</v>
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.7</v>
+        <v>22</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="G13" t="n">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="14">
@@ -3735,39 +3735,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="G14" t="n">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="H14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I14" t="n">
         <v>1.7</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="15">
@@ -3778,27 +3778,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.7</v>
+        <v>23.2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="G15" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="H15" t="n">
         <v>4.6</v>
@@ -3810,7 +3810,7 @@
         <v>0.8</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="16">
@@ -3821,39 +3821,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G16" t="n">
-        <v>8.800000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="H16" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="17">
@@ -3864,39 +3864,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G17" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="18">
@@ -3950,30 +3950,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.9</v>
+        <v>23.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="H19" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="I19" t="n">
         <v>1.5</v>
@@ -3982,7 +3982,7 @@
         <v>0.8</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="20">
@@ -3993,30 +3993,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.2</v>
+        <v>22.9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="G20" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="H20" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="I20" t="n">
         <v>1.5</v>
@@ -4025,7 +4025,7 @@
         <v>0.8</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="21">
@@ -4036,39 +4036,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>2.8</v>
       </c>
       <c r="G21" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H21" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I21" t="n">
         <v>1.7</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="K21" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="22">
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.2</v>
+        <v>23.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>2.8</v>
       </c>
       <c r="G22" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I22" t="n">
         <v>1.7</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="23">
@@ -4130,16 +4130,16 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G23" t="n">
         <v>8.1</v>
@@ -4173,31 +4173,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>2.4</v>
       </c>
       <c r="G24" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="H24" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
         <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="25">
@@ -4251,30 +4251,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G26" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H26" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="I26" t="n">
         <v>1.7</v>
@@ -4294,30 +4294,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="H27" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="I27" t="n">
         <v>1.7</v>
@@ -4427,7 +4427,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4436,17 +4436,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>3.1</v>
       </c>
       <c r="G30" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="H30" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I30" t="n">
         <v>1.8</v>
@@ -4455,7 +4455,7 @@
         <v>0.8</v>
       </c>
       <c r="K30" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="31">
@@ -4584,23 +4584,23 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>2.3</v>
       </c>
       <c r="G2" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="H2" t="n">
         <v>4.1</v>
@@ -4623,39 +4623,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.6</v>
+        <v>20.9</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="G3" t="n">
-        <v>10.8</v>
+        <v>10.1</v>
       </c>
       <c r="H3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J3" t="n">
         <v>1.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -4666,39 +4666,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="G4" t="n">
-        <v>10.2</v>
+        <v>10.8</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J4" t="n">
         <v>1.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="5">
@@ -4756,7 +4756,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>1.6</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K6" t="n">
         <v>2.1</v>
@@ -4795,39 +4795,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.6</v>
+        <v>22.7</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>9.4</v>
+        <v>10.2</v>
       </c>
       <c r="H7" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="I7" t="n">
         <v>1.3</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="K7" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8">
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.3</v>
+        <v>20.3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>10.7</v>
+        <v>9.4</v>
       </c>
       <c r="H8" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9</v>
+        <v>1.2</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="9">
@@ -4881,39 +4881,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.3</v>
+        <v>21.8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>2</v>
       </c>
       <c r="G9" t="n">
-        <v>9.5</v>
+        <v>10.8</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
         <v>1.2</v>
       </c>
       <c r="K9" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -4924,39 +4924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.7</v>
+        <v>21.4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="G10" t="n">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="K10" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="11">
@@ -4967,39 +4967,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="I11" t="n">
         <v>1.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="12">
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.5</v>
+        <v>21.9</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="G12" t="n">
-        <v>9.9</v>
+        <v>10.3</v>
       </c>
       <c r="H12" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="K12" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="13">
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>23.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="G13" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K13" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="14">
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.4</v>
+        <v>21.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="G14" t="n">
-        <v>11.1</v>
+        <v>9.9</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J14" t="n">
         <v>1.5</v>
       </c>
-      <c r="J14" t="n">
-        <v>1.2</v>
-      </c>
       <c r="K14" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="15">
@@ -5139,39 +5139,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.8</v>
+        <v>23.4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="G15" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="16">
@@ -5182,39 +5182,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.4</v>
+        <v>23.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="G16" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="H16" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="17">
@@ -5225,39 +5225,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>2.3</v>
       </c>
       <c r="G17" t="n">
-        <v>10.4</v>
+        <v>10.9</v>
       </c>
       <c r="H17" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="18">
@@ -5272,26 +5272,26 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>2.2</v>
       </c>
       <c r="G18" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="H18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I18" t="n">
         <v>1.5</v>
@@ -5300,7 +5300,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="19">
@@ -5311,11 +5311,11 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23</v>
+        <v>23.3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5324,26 +5324,26 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>2.1</v>
       </c>
       <c r="G19" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="20">
@@ -5397,27 +5397,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>49.8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="G21" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="H21" t="n">
         <v>4.4</v>
@@ -5426,10 +5426,10 @@
         <v>1.4</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K21" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="G22" t="n">
-        <v>9.9</v>
+        <v>11.7</v>
       </c>
       <c r="H22" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="K22" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23">
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24</v>
+        <v>23.2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="G23" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="H23" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K23" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="24">
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="G24" t="n">
-        <v>11.7</v>
+        <v>9.6</v>
       </c>
       <c r="H24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="K24" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="25">
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G25" t="n">
-        <v>11.2</v>
+        <v>10.1</v>
       </c>
       <c r="H25" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="26">
@@ -5612,39 +5612,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G26" t="n">
-        <v>9.6</v>
+        <v>11.2</v>
       </c>
       <c r="H26" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="K26" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="27">
@@ -5941,39 +5941,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19.6</v>
+        <v>21.4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>14.6</v>
+        <v>15.5</v>
       </c>
       <c r="H2" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -5984,36 +5984,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.4</v>
+        <v>20.2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G3" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -6027,36 +6027,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>19.6</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="G4" t="n">
-        <v>13.8</v>
+        <v>14.6</v>
       </c>
       <c r="H4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I4" t="n">
         <v>1.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="K4" t="n">
         <v>3.1</v>
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18.3</v>
+        <v>19.2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="G5" t="n">
-        <v>13.3</v>
+        <v>14.6</v>
       </c>
       <c r="H5" t="n">
         <v>3.5</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="6">
@@ -6117,32 +6117,32 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1.3</v>
       </c>
       <c r="G6" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="H6" t="n">
         <v>4.3</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>3</v>
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="G7" t="n">
-        <v>14.3</v>
+        <v>13</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="8">
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.4</v>
+        <v>18.3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="G8" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="H8" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="K8" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="9">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -6265,7 +6265,7 @@
         <v>13.6</v>
       </c>
       <c r="H9" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I9" t="n">
         <v>1.2</v>
@@ -6289,32 +6289,32 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>72.9</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="H10" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
         <v>1.2</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K10" t="n">
         <v>2.6</v>
@@ -6332,11 +6332,11 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -6351,7 +6351,7 @@
         <v>14.4</v>
       </c>
       <c r="H11" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="I11" t="n">
         <v>1.1</v>
@@ -6360,7 +6360,7 @@
         <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.3</v>
+        <v>20.9</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>68.3</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1.4</v>
       </c>
       <c r="G12" t="n">
-        <v>13.6</v>
+        <v>13.9</v>
       </c>
       <c r="H12" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="K12" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>18.1</v>
+        <v>22.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="G13" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="H13" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="14">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.5</v>
+        <v>18.1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>67.3</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="G14" t="n">
-        <v>12.4</v>
+        <v>13.7</v>
       </c>
       <c r="H14" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="I14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J14" t="n">
         <v>1.3</v>
       </c>
-      <c r="J14" t="n">
-        <v>1.8</v>
-      </c>
       <c r="K14" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="15">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20.9</v>
+        <v>21.4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I15" t="n">
         <v>1.4</v>
       </c>
-      <c r="G15" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.3</v>
-      </c>
       <c r="J15" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="16">
@@ -6543,36 +6543,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G16" t="n">
-        <v>15.5</v>
+        <v>14.2</v>
       </c>
       <c r="H16" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="K16" t="n">
         <v>2.4</v>
@@ -6586,39 +6586,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.1</v>
+        <v>21.5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G17" t="n">
-        <v>14.2</v>
+        <v>14.6</v>
       </c>
       <c r="H17" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="18">
@@ -6672,39 +6672,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21.6</v>
+        <v>20.9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G19" t="n">
-        <v>14.7</v>
+        <v>15.5</v>
       </c>
       <c r="H19" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="K19" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="20">
@@ -6801,39 +6801,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21.8</v>
+        <v>24.7</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="G22" t="n">
-        <v>15.4</v>
+        <v>14.5</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="23">
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.5</v>
+        <v>21.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>55.5</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G24" t="n">
-        <v>14.4</v>
+        <v>15.4</v>
       </c>
       <c r="H24" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J24" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="K24" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="25">
@@ -7024,19 +7024,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>1.4</v>
       </c>
       <c r="G27" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="H27" t="n">
         <v>3.8</v>
@@ -7045,7 +7045,7 @@
         <v>1.8</v>
       </c>
       <c r="J27" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="K27" t="n">
         <v>2.2</v>
@@ -7149,11 +7149,11 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -7162,10 +7162,10 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G30" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="H30" t="n">
         <v>4.4</v>

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -587,29 +587,29 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>2.6</v>
       </c>
       <c r="G4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H4" t="n">
         <v>7.3</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
         <v>0.5</v>
@@ -630,23 +630,23 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>2.9</v>
       </c>
       <c r="G5" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H5" t="n">
         <v>8</v>
@@ -673,11 +673,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -689,13 +689,13 @@
         <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
         <v>0.6</v>
@@ -755,30 +755,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.9</v>
+        <v>22.4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="H8" t="n">
-        <v>7.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I8" t="n">
         <v>2.1</v>
@@ -787,7 +787,7 @@
         <v>0.4</v>
       </c>
       <c r="K8" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9">
@@ -798,39 +798,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>24.1</v>
+        <v>23</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="H9" t="n">
-        <v>8.1</v>
+        <v>7.1</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="10">
@@ -841,39 +841,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.3</v>
+        <v>24.1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="G10" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="H10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I10" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="11">
@@ -935,12 +935,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -950,7 +950,7 @@
         <v>6.2</v>
       </c>
       <c r="H12" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="I12" t="n">
         <v>2</v>
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.5</v>
+        <v>23</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K13" t="n">
         <v>2.7</v>
-      </c>
-      <c r="G13" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H13" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="I13" t="n">
-        <v>2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.3</v>
       </c>
     </row>
     <row r="14">
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>23.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H14" t="n">
-        <v>9.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
         <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="15">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26.9</v>
+        <v>23.3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="H15" t="n">
-        <v>9</v>
+        <v>8.1</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
         <v>0.4</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="16">
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G16" t="n">
-        <v>5.2</v>
+        <v>6.5</v>
       </c>
       <c r="H16" t="n">
-        <v>8.1</v>
+        <v>8.6</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="17">
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.1</v>
+        <v>27</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>7.9</v>
+        <v>8.9</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="18">
@@ -1189,35 +1189,35 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>3.1</v>
       </c>
       <c r="G18" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H18" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="19">
@@ -1314,39 +1314,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.7</v>
+        <v>24</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="H21" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
         <v>0.5</v>
       </c>
       <c r="K21" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="22">
@@ -1357,39 +1357,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>25.8</v>
+        <v>24.7</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G22" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="H22" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K22" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="23">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1408,31 +1408,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>83.9</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G23" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="H23" t="n">
-        <v>7.1</v>
+        <v>8.4</v>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="24">
@@ -1443,39 +1443,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.1</v>
+        <v>25.7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>83.9</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="F24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H24" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K24" t="n">
         <v>3.3</v>
-      </c>
-      <c r="G24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3.1</v>
       </c>
     </row>
     <row r="25">
@@ -1619,23 +1619,23 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>25.7</v>
+        <v>26</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>3.1</v>
       </c>
       <c r="G28" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="H28" t="n">
         <v>8.800000000000001</v>
@@ -1644,7 +1644,7 @@
         <v>2.4</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K28" t="n">
         <v>3</v>
@@ -1748,35 +1748,35 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.8</v>
+        <v>25.5</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="G31" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H31" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="I31" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
         <v>0.6</v>
       </c>
       <c r="K31" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
   </sheetData>
@@ -1948,26 +1948,26 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I4" t="n">
         <v>1.8</v>
@@ -1976,7 +1976,7 @@
         <v>0.6</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="5">
@@ -1991,26 +1991,26 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I5" t="n">
         <v>1.5</v>
@@ -2019,7 +2019,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="6">
@@ -2116,30 +2116,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="I8" t="n">
         <v>1.6</v>
@@ -2148,7 +2148,7 @@
         <v>0.7</v>
       </c>
       <c r="K8" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="9">
@@ -2159,39 +2159,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23.1</v>
+        <v>23.8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="G9" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="H9" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="I9" t="n">
         <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K9" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="10">
@@ -2206,7 +2206,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2215,26 +2215,26 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G10" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="H10" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J10" t="n">
         <v>0.7</v>
       </c>
       <c r="K10" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="11">
@@ -2245,39 +2245,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.3</v>
+        <v>23.3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="H11" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
         <v>0.6</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2296,31 +2296,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>84.1</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="G12" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="H12" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -2331,39 +2331,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.3</v>
+        <v>22.1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G13" t="n">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="H13" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
         <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="14">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2382,31 +2382,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>84.1</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="G14" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="H14" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -2421,11 +2421,11 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2477,10 +2477,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G16" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="H16" t="n">
         <v>5.5</v>
@@ -2503,39 +2503,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="G17" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="H17" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="18">
@@ -2546,39 +2546,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.3</v>
+        <v>23.9</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G18" t="n">
         <v>6.6</v>
       </c>
       <c r="H18" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K18" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="19">
@@ -2589,39 +2589,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.4</v>
+        <v>23.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G19" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="H19" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="K19" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="20">
@@ -2632,39 +2632,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>24.4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="G20" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="H20" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K20" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="21">
@@ -2675,15 +2675,15 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23</v>
+        <v>23.9</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2692,22 +2692,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="G21" t="n">
         <v>6.6</v>
       </c>
       <c r="H21" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="I21" t="n">
         <v>1.8</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="22">
@@ -2718,39 +2718,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.9</v>
+        <v>24.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>3.7</v>
       </c>
       <c r="G22" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="H22" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K22" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23">
@@ -2761,33 +2761,33 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.6</v>
+        <v>23</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="G23" t="n">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="H23" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0.7</v>
@@ -2847,39 +2847,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.4</v>
+        <v>24.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="G25" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="H25" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0.6</v>
       </c>
       <c r="K25" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="26">
@@ -2890,39 +2890,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24</v>
+        <v>23.4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="G26" t="n">
-        <v>7.1</v>
+        <v>6.3</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K26" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="27">
@@ -2933,39 +2933,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.9</v>
+        <v>24</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="G27" t="n">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="H27" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K27" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="28">
@@ -3023,23 +3023,23 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>2.9</v>
       </c>
       <c r="G29" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="H29" t="n">
         <v>5.2</v>
@@ -3062,39 +3062,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26.3</v>
+        <v>24.5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="G30" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="H30" t="n">
-        <v>6.7</v>
+        <v>5.3</v>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K30" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="31">
@@ -3105,39 +3105,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.5</v>
+        <v>26.4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="G31" t="n">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="H31" t="n">
-        <v>5.3</v>
+        <v>6.7</v>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K31" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
     </row>
   </sheetData>
@@ -3219,39 +3219,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22.4</v>
+        <v>23.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K2" t="n">
         <v>2.6</v>
-      </c>
-      <c r="G2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.1</v>
       </c>
     </row>
     <row r="3">
@@ -3348,39 +3348,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23.3</v>
+        <v>22.5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="G5" t="n">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -3457,7 +3457,7 @@
         <v>7.6</v>
       </c>
       <c r="H7" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I7" t="n">
         <v>1.7</v>
@@ -3477,39 +3477,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.6</v>
+        <v>22.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="H8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K8" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -3520,39 +3520,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.7</v>
+        <v>21.8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="I9" t="n">
         <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="10">
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.6</v>
+        <v>20.7</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G10" t="n">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="H10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I10" t="n">
         <v>1.6</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="K10" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11">
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.3</v>
+        <v>22.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="H11" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
         <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="12">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>2.7</v>
       </c>
       <c r="G13" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="14">
@@ -3821,39 +3821,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G16" t="n">
-        <v>6.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="17">
@@ -3864,39 +3864,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.6</v>
+        <v>23.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="H17" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="18">
@@ -3907,39 +3907,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.5</v>
+        <v>22.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="G18" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="H18" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="19">
@@ -3950,39 +3950,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.7</v>
+        <v>22.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G19" t="n">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="20">
@@ -3993,11 +3993,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.9</v>
+        <v>22.5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -4006,26 +4006,26 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>84.1</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G20" t="n">
-        <v>8.4</v>
+        <v>6.9</v>
       </c>
       <c r="H20" t="n">
-        <v>5.2</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="21">
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.5</v>
+        <v>22.1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="G22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="H22" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22.1</v>
+        <v>23.7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="G24" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="I24" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K24" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="25">
@@ -4212,29 +4212,29 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>26.7</v>
+        <v>26.4</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>3.2</v>
       </c>
       <c r="G25" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="H25" t="n">
         <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
         <v>0.7</v>
@@ -4251,36 +4251,36 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="H26" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="I26" t="n">
         <v>1.7</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K26" t="n">
         <v>2.1</v>
@@ -4294,30 +4294,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G27" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="H27" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="I27" t="n">
         <v>1.7</v>
@@ -4341,7 +4341,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4384,26 +4384,26 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G29" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="H29" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I29" t="n">
         <v>1.9</v>
@@ -4412,7 +4412,7 @@
         <v>0.8</v>
       </c>
       <c r="K29" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="30">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4483,16 +4483,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G31" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="H31" t="n">
         <v>4.5</v>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -4627,16 +4627,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -4646,7 +4646,7 @@
         <v>10.1</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I3" t="n">
         <v>1.6</v>
@@ -4670,11 +4670,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4683,13 +4683,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G4" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I4" t="n">
         <v>1.4</v>
@@ -4717,19 +4717,19 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>1.9</v>
       </c>
       <c r="G5" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="H5" t="n">
         <v>4.3</v>
@@ -4741,7 +4741,7 @@
         <v>1.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="6">
@@ -4756,32 +4756,32 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="G6" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>3.6</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K6" t="n">
         <v>2.1</v>
@@ -4795,39 +4795,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.7</v>
+        <v>20.3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>10.2</v>
+        <v>9.4</v>
       </c>
       <c r="H7" t="n">
         <v>3.8</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="8">
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.3</v>
+        <v>22.7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>9.4</v>
+        <v>10.2</v>
       </c>
       <c r="H8" t="n">
         <v>3.8</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9">
@@ -4885,20 +4885,20 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="G9" t="n">
         <v>10.8</v>
@@ -4913,7 +4913,7 @@
         <v>1.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="10">
@@ -4924,39 +4924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.4</v>
+        <v>21.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="G10" t="n">
-        <v>10.6</v>
+        <v>10.3</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I10" t="n">
         <v>1.4</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11">
@@ -4967,39 +4967,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.9</v>
+        <v>21.4</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>9.5</v>
+        <v>10.6</v>
       </c>
       <c r="H11" t="n">
         <v>4.4</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="K11" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="12">
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G12" t="n">
-        <v>10.3</v>
+        <v>9.5</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I12" t="n">
         <v>1.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="13">
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.8</v>
+        <v>22.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="G14" t="n">
-        <v>9.9</v>
+        <v>10.4</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="15">
@@ -5139,39 +5139,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.4</v>
+        <v>22.1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J15" t="n">
         <v>1.5</v>
       </c>
-      <c r="J15" t="n">
-        <v>1.2</v>
-      </c>
       <c r="K15" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="16">
@@ -5182,39 +5182,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="G16" t="n">
-        <v>10.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="I16" t="n">
         <v>1.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="17">
@@ -5225,39 +5225,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G17" t="n">
         <v>10.9</v>
       </c>
       <c r="H17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I17" t="n">
         <v>1.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="18">
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.3</v>
+        <v>22.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="G18" t="n">
         <v>10.9</v>
       </c>
       <c r="H18" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I18" t="n">
         <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="19">
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.3</v>
+        <v>23.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G19" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="H19" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="20">
@@ -5362,22 +5362,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>2.5</v>
       </c>
       <c r="G20" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="H20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I20" t="n">
         <v>1.7</v>
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.1</v>
+        <v>22.7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>49.8</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="G21" t="n">
-        <v>9.9</v>
+        <v>11.7</v>
       </c>
       <c r="H21" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="22">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.7</v>
+        <v>23.2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G22" t="n">
-        <v>11.7</v>
+        <v>10.2</v>
       </c>
       <c r="H22" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="23">
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.2</v>
+        <v>23.7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="G23" t="n">
         <v>10.2</v>
       </c>
       <c r="H23" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>1.2</v>
       </c>
       <c r="K23" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="24">
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22.5</v>
+        <v>24</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G24" t="n">
-        <v>9.6</v>
+        <v>10.1</v>
       </c>
       <c r="H24" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="25">
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="G25" t="n">
-        <v>10.1</v>
+        <v>11.2</v>
       </c>
       <c r="H25" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="K25" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="26">
@@ -5612,39 +5612,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>22.9</v>
+        <v>22.5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="G26" t="n">
-        <v>11.2</v>
+        <v>9.6</v>
       </c>
       <c r="H26" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="K26" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="27">
@@ -5655,27 +5655,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.8</v>
+        <v>23.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="G27" t="n">
-        <v>10.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H27" t="n">
         <v>4.4</v>
@@ -5684,10 +5684,10 @@
         <v>1.5</v>
       </c>
       <c r="J27" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K27" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="28">
@@ -5741,39 +5741,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27.4</v>
+        <v>24.7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>50.5</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>10.9</v>
+        <v>12.4</v>
       </c>
       <c r="H29" t="n">
         <v>4.6</v>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K29" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="30">
@@ -5784,39 +5784,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.9</v>
+        <v>27.3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G30" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K30" t="n">
         <v>2</v>
-      </c>
-      <c r="G30" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="H30" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K30" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="31">
@@ -5840,17 +5840,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G31" t="n">
-        <v>10.5</v>
+        <v>10.7</v>
       </c>
       <c r="H31" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I31" t="n">
         <v>1.7</v>
@@ -5941,39 +5941,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.4</v>
+        <v>19.7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="G2" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="3">
@@ -5984,39 +5984,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.2</v>
+        <v>21.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>14</v>
+        <v>15.7</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J3" t="n">
         <v>1.9</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="4">
@@ -6027,27 +6027,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19.6</v>
+        <v>20.2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="G4" t="n">
-        <v>14.6</v>
+        <v>14</v>
       </c>
       <c r="H4" t="n">
         <v>4.4</v>
@@ -6056,10 +6056,10 @@
         <v>1.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6078,31 +6078,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="G5" t="n">
-        <v>14.6</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="6">
@@ -6117,26 +6117,26 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1.3</v>
       </c>
       <c r="G6" t="n">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I6" t="n">
         <v>1.3</v>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -6164,31 +6164,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>13</v>
+        <v>14.6</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="8">
@@ -6375,26 +6375,26 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1.4</v>
       </c>
       <c r="G12" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="H12" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I12" t="n">
         <v>1.3</v>
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18.1</v>
+        <v>20.9</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="G14" t="n">
-        <v>13.7</v>
+        <v>15.6</v>
       </c>
       <c r="H14" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J14" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="15">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.4</v>
+        <v>18.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="G15" t="n">
-        <v>12.5</v>
+        <v>13.6</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="16">
@@ -6543,36 +6543,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>21</v>
+        <v>21.8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>14.2</v>
+        <v>11.8</v>
       </c>
       <c r="H16" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="K16" t="n">
         <v>2.4</v>
@@ -6586,39 +6586,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.5</v>
+        <v>20.9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G17" t="n">
-        <v>14.6</v>
+        <v>14.2</v>
       </c>
       <c r="H17" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
         <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="18">
@@ -6629,39 +6629,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21.9</v>
+        <v>21.2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>68.2</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G18" t="n">
-        <v>13.7</v>
+        <v>12.5</v>
       </c>
       <c r="H18" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="19">
@@ -6672,39 +6672,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20.9</v>
+        <v>21.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="G19" t="n">
-        <v>15.5</v>
+        <v>14.6</v>
       </c>
       <c r="H19" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="20">
@@ -6715,39 +6715,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="G20" t="n">
-        <v>11.7</v>
+        <v>13.7</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J20" t="n">
         <v>1.4</v>
       </c>
-      <c r="J20" t="n">
-        <v>1.6</v>
-      </c>
       <c r="K20" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="21">
@@ -6758,39 +6758,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.7</v>
+        <v>21.2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>57.7</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I21" t="n">
         <v>1.5</v>
       </c>
-      <c r="G21" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="H21" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.4</v>
-      </c>
       <c r="J21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K21" t="n">
         <v>2.3</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2.2</v>
       </c>
     </row>
     <row r="22">
@@ -6844,15 +6844,15 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21</v>
+        <v>21.8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>58.3</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -6861,22 +6861,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G23" t="n">
-        <v>14.1</v>
+        <v>15.4</v>
       </c>
       <c r="H23" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J23" t="n">
         <v>1.9</v>
       </c>
       <c r="K23" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="24">
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>21.8</v>
+        <v>23</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="G24" t="n">
-        <v>15.4</v>
+        <v>14.2</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="K24" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="25">
@@ -7063,11 +7063,11 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -7076,7 +7076,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G28" t="n">
         <v>16.1</v>
@@ -7091,7 +7091,7 @@
         <v>3</v>
       </c>
       <c r="K28" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="29">
@@ -7102,39 +7102,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.1</v>
+        <v>24.5</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1.3</v>
       </c>
       <c r="G29" t="n">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="K29" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="30">
@@ -7145,39 +7145,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.5</v>
+        <v>24.1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1.3</v>
       </c>
       <c r="G30" t="n">
-        <v>15.3</v>
+        <v>15.5</v>
       </c>
       <c r="H30" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="31">

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -501,11 +501,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -520,10 +520,10 @@
         <v>5.6</v>
       </c>
       <c r="H2" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="n">
         <v>0.5</v>
@@ -583,39 +583,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.3</v>
+        <v>22.9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="H4" t="n">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="5">
@@ -626,39 +626,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23.5</v>
+        <v>22.2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -669,39 +669,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.9</v>
+        <v>23.5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G6" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="H6" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
         <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="7">
@@ -755,30 +755,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.4</v>
+        <v>23</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G8" t="n">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="H8" t="n">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="I8" t="n">
         <v>2.1</v>
@@ -787,7 +787,7 @@
         <v>0.4</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="9">
@@ -798,30 +798,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>22.4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G9" t="n">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
       <c r="H9" t="n">
-        <v>7.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I9" t="n">
         <v>2.1</v>
@@ -830,7 +830,7 @@
         <v>0.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="10">
@@ -1271,39 +1271,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.1</v>
+        <v>24.7</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>3.1</v>
       </c>
       <c r="G20" t="n">
-        <v>5.6</v>
+        <v>6.3</v>
       </c>
       <c r="H20" t="n">
-        <v>8.5</v>
+        <v>9.4</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K20" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="21">
@@ -1314,39 +1314,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G21" t="n">
-        <v>6.7</v>
+        <v>5.6</v>
       </c>
       <c r="H21" t="n">
-        <v>7.2</v>
+        <v>8.5</v>
       </c>
       <c r="I21" t="n">
         <v>1.9</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="22">
@@ -1357,39 +1357,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.7</v>
+        <v>24</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="H22" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>0.5</v>
       </c>
       <c r="K22" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23">
@@ -1400,39 +1400,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.1</v>
+        <v>25.7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>83.9</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="F23" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K23" t="n">
         <v>3.3</v>
-      </c>
-      <c r="G23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3.1</v>
       </c>
     </row>
     <row r="24">
@@ -1443,39 +1443,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25.7</v>
+        <v>24.1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.9</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G24" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="H24" t="n">
-        <v>7.7</v>
+        <v>8.4</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="25">
@@ -2073,39 +2073,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="G7" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="H7" t="n">
         <v>5.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
@@ -2116,39 +2116,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="G8" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="H8" t="n">
         <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -2182,7 +2182,7 @@
         <v>6.3</v>
       </c>
       <c r="H9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I9" t="n">
         <v>1.6</v>
@@ -2632,39 +2632,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.4</v>
+        <v>23.9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="G20" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="H20" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K20" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="21">
@@ -2675,39 +2675,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.9</v>
+        <v>24.3</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="G21" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="I21" t="n">
         <v>1.8</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K21" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22">
@@ -3219,39 +3219,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23.3</v>
+        <v>22.4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
         <v>3.1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="3">
@@ -3348,39 +3348,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.5</v>
+        <v>23.2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K5" t="n">
         <v>2.6</v>
-      </c>
-      <c r="G5" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -3520,36 +3520,36 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.8</v>
+        <v>20.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G9" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="I9" t="n">
         <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K9" t="n">
         <v>2.3</v>
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20.7</v>
+        <v>21.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>2.7</v>
       </c>
       <c r="G10" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="K10" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="11">
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.6</v>
+        <v>21.8</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G11" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="H11" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="I11" t="n">
         <v>1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="K11" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="12">
@@ -3649,39 +3649,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20.7</v>
+        <v>22.6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="I12" t="n">
         <v>1.6</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="13">
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.9</v>
+        <v>20.7</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>2.7</v>
       </c>
       <c r="G13" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="H13" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="K13" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="14">
@@ -3864,30 +3864,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.7</v>
+        <v>22.8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G17" t="n">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="H17" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="I17" t="n">
         <v>1.5</v>
@@ -3896,7 +3896,7 @@
         <v>0.8</v>
       </c>
       <c r="K17" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="18">
@@ -3907,30 +3907,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.8</v>
+        <v>23.7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="H18" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="I18" t="n">
         <v>1.5</v>
@@ -3939,7 +3939,7 @@
         <v>0.8</v>
       </c>
       <c r="K18" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="19">
@@ -4122,39 +4122,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22.8</v>
+        <v>23.7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>2.9</v>
       </c>
       <c r="G23" t="n">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
         <v>0.8</v>
       </c>
       <c r="K23" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="24">
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.7</v>
+        <v>22.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>2.9</v>
       </c>
       <c r="G24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="H24" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
         <v>0.8</v>
       </c>
       <c r="K24" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="25">
@@ -4709,39 +4709,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22</v>
+        <v>20.6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="G5" t="n">
-        <v>10.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="I5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J5" t="n">
         <v>1.2</v>
       </c>
-      <c r="J5" t="n">
-        <v>1.6</v>
-      </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="6">
@@ -4752,39 +4752,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.6</v>
+        <v>22</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="G6" t="n">
-        <v>8.699999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="K6" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7">
@@ -4795,39 +4795,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.3</v>
+        <v>22.7</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G7" t="n">
-        <v>9.4</v>
+        <v>10.2</v>
       </c>
       <c r="H7" t="n">
         <v>3.8</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8">
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.7</v>
+        <v>20.3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>10.2</v>
+        <v>9.4</v>
       </c>
       <c r="H8" t="n">
         <v>3.8</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K8" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="9">
@@ -4924,39 +4924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.9</v>
+        <v>21.4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="G10" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I10" t="n">
         <v>1.4</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="K10" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="11">
@@ -4967,27 +4967,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.4</v>
+        <v>22</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G11" t="n">
-        <v>10.6</v>
+        <v>9.5</v>
       </c>
       <c r="H11" t="n">
         <v>4.4</v>
@@ -4996,7 +4996,7 @@
         <v>1.4</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
         <v>2.9</v>
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>23.5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="G12" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="13">
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.5</v>
+        <v>22</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K13" t="n">
         <v>2.7</v>
-      </c>
-      <c r="G13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2.1</v>
       </c>
     </row>
     <row r="14">
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.8</v>
+        <v>21.9</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="G14" t="n">
-        <v>10.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="15">
@@ -5139,36 +5139,36 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="G15" t="n">
-        <v>9.9</v>
+        <v>10.9</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>2.9</v>
@@ -5182,39 +5182,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="G16" t="n">
-        <v>9.800000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="H16" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="I16" t="n">
         <v>1.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="17">
@@ -5225,39 +5225,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.3</v>
+        <v>23.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>2.2</v>
       </c>
       <c r="G17" t="n">
-        <v>10.9</v>
+        <v>10</v>
       </c>
       <c r="H17" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="I17" t="n">
         <v>1.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="18">
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.6</v>
+        <v>22.1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="F18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
         <v>2.3</v>
-      </c>
-      <c r="G18" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="H18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2.2</v>
       </c>
     </row>
     <row r="19">
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.7</v>
+        <v>23.3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G19" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="20">
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.1</v>
+        <v>22.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="G20" t="n">
-        <v>9.4</v>
+        <v>10.9</v>
       </c>
       <c r="H20" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K20" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="21">
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.7</v>
+        <v>23.2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G21" t="n">
-        <v>11.7</v>
+        <v>10.2</v>
       </c>
       <c r="H21" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="22">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.2</v>
+        <v>22.7</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G22" t="n">
-        <v>10.2</v>
+        <v>11.7</v>
       </c>
       <c r="H22" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K22" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23">
@@ -5569,36 +5569,36 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23</v>
+        <v>23.3</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="G25" t="n">
-        <v>11.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I25" t="n">
         <v>1.5</v>
       </c>
       <c r="J25" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K25" t="n">
         <v>2.5</v>
@@ -5655,36 +5655,36 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.3</v>
+        <v>23</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="G27" t="n">
-        <v>9.800000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="H27" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I27" t="n">
         <v>1.5</v>
       </c>
       <c r="J27" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="K27" t="n">
         <v>2.5</v>
@@ -5741,39 +5741,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.7</v>
+        <v>27.3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="G29" t="n">
-        <v>12.4</v>
+        <v>10.8</v>
       </c>
       <c r="H29" t="n">
         <v>4.6</v>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="K29" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -5784,39 +5784,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>27.3</v>
+        <v>24.7</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="G30" t="n">
-        <v>10.8</v>
+        <v>12.4</v>
       </c>
       <c r="H30" t="n">
         <v>4.6</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="31">
@@ -5984,39 +5984,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.5</v>
+        <v>20.2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G3" t="n">
-        <v>15.7</v>
+        <v>14</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J3" t="n">
         <v>1.9</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -6027,39 +6027,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.2</v>
+        <v>21.5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>14</v>
+        <v>15.7</v>
       </c>
       <c r="H4" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J4" t="n">
         <v>1.9</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="5">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -6078,31 +6078,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>14.6</v>
       </c>
       <c r="H5" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="6">
@@ -6113,39 +6113,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.5</v>
+        <v>19.7</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G6" t="n">
-        <v>14.9</v>
+        <v>13.6</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="7">
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19.2</v>
+        <v>21.5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="G7" t="n">
-        <v>14.6</v>
+        <v>14.9</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>18.3</v>
+        <v>19.2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="F8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G8" t="n">
+        <v>13</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I8" t="n">
         <v>1.2</v>
       </c>
-      <c r="G8" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="H8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.7</v>
-      </c>
       <c r="J8" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="9">
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19.7</v>
+        <v>18.1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G9" t="n">
-        <v>13.6</v>
+        <v>13.2</v>
       </c>
       <c r="H9" t="n">
         <v>3.5</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="10">
@@ -6328,39 +6328,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>20.7</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1.4</v>
       </c>
       <c r="G11" t="n">
-        <v>14.4</v>
+        <v>13.8</v>
       </c>
       <c r="H11" t="n">
         <v>3.2</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="12">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20.7</v>
+        <v>22.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1.4</v>
       </c>
       <c r="G12" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K12" t="n">
         <v>2.1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.3</v>
+        <v>19</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1.4</v>
       </c>
       <c r="G13" t="n">
-        <v>13.6</v>
+        <v>14.4</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="14">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20.9</v>
+        <v>18.5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="G14" t="n">
-        <v>15.6</v>
+        <v>13.6</v>
       </c>
       <c r="H14" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="15">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>18.5</v>
+        <v>21.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="G15" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="H15" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="16">
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>21.8</v>
+        <v>20.9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="F16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="G16" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="H16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.6</v>
-      </c>
       <c r="K16" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="17">
@@ -6586,36 +6586,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.9</v>
+        <v>21.2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>68.2</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1.2</v>
       </c>
       <c r="G17" t="n">
-        <v>14.2</v>
+        <v>12.5</v>
       </c>
       <c r="H17" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K17" t="n">
         <v>2.3</v>
@@ -6629,39 +6629,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21.2</v>
+        <v>20.9</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>68.2</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1.2</v>
       </c>
       <c r="G18" t="n">
-        <v>12.5</v>
+        <v>15.6</v>
       </c>
       <c r="H18" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="19">
@@ -6715,39 +6715,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F20" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I20" t="n">
         <v>1.4</v>
       </c>
-      <c r="G20" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="H20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1.3</v>
-      </c>
       <c r="J20" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="21">
@@ -6758,39 +6758,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21.2</v>
+        <v>23</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="G21" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="H21" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="K21" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="22">
@@ -6844,39 +6844,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21.8</v>
+        <v>21.2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>15.4</v>
+        <v>14.1</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>1.9</v>
       </c>
       <c r="K23" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="24">
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23</v>
+        <v>21.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="G24" t="n">
-        <v>14.2</v>
+        <v>15.4</v>
       </c>
       <c r="H24" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J24" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="K24" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="25">
@@ -6930,39 +6930,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.1</v>
+        <v>22.7</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="G25" t="n">
-        <v>15.4</v>
+        <v>14.2</v>
       </c>
       <c r="H25" t="n">
         <v>4.4</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="K25" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="26">
@@ -6973,39 +6973,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>22.7</v>
+        <v>24.1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>14.2</v>
+        <v>15.4</v>
       </c>
       <c r="H26" t="n">
         <v>4.4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="K26" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="27">

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -540,39 +540,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.3</v>
+        <v>22.2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="G3" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="H3" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J3" t="n">
         <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -583,39 +583,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.9</v>
+        <v>21.3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="G4" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="H4" t="n">
-        <v>7.9</v>
+        <v>7.5</v>
       </c>
       <c r="I4" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="5">
@@ -626,39 +626,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.2</v>
+        <v>23.2</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="G5" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="H5" t="n">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="6">
@@ -669,39 +669,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.5</v>
+        <v>20.8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>40.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>9.1</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="7">
@@ -712,39 +712,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G7" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="H7" t="n">
-        <v>9.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J7" t="n">
         <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="8">
@@ -759,29 +759,29 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G8" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H8" t="n">
         <v>7.1</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>0.4</v>
@@ -802,16 +802,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -821,16 +821,16 @@
         <v>5.9</v>
       </c>
       <c r="H9" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -841,39 +841,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="G10" t="n">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="H10" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>0.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="11">
@@ -888,11 +888,11 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25.3</v>
+        <v>25</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -916,7 +916,7 @@
         <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="12">
@@ -927,39 +927,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.8</v>
+        <v>23.5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H12" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K12" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="13">
@@ -970,36 +970,36 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>2.9</v>
       </c>
       <c r="G13" t="n">
-        <v>6.1</v>
+        <v>5.3</v>
       </c>
       <c r="H13" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="I13" t="n">
         <v>2.1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K13" t="n">
         <v>2.7</v>
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.8</v>
+        <v>24.4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="H14" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
         <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="15">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.3</v>
+        <v>27</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="H15" t="n">
-        <v>8.1</v>
+        <v>9</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0.4</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="16">
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.5</v>
+        <v>23.9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="G16" t="n">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="H16" t="n">
-        <v>8.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="17">
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>27</v>
+        <v>23.3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G17" t="n">
         <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K17" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="18">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1193,31 +1193,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G18" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="H18" t="n">
-        <v>9.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="I18" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="K18" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="19">
@@ -1232,20 +1232,20 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G19" t="n">
         <v>5.8</v>
@@ -1271,39 +1271,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.7</v>
+        <v>24.1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G20" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="H20" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J20" t="n">
         <v>0.5</v>
       </c>
       <c r="K20" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="21">
@@ -1318,35 +1318,35 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
         <v>5.6</v>
       </c>
       <c r="H21" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
         <v>0.6</v>
       </c>
       <c r="K21" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="22">
@@ -1357,39 +1357,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>24.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G22" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="H22" t="n">
-        <v>7.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J22" t="n">
         <v>0.5</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="23">
@@ -1400,39 +1400,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>25.7</v>
+        <v>24</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="H23" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="I23" t="n">
         <v>1.9</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K23" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="24">
@@ -1443,39 +1443,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.1</v>
+        <v>25.7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>83.9</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="F24" t="n">
+        <v>3</v>
+      </c>
+      <c r="G24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H24" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K24" t="n">
         <v>3.3</v>
-      </c>
-      <c r="G24" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="H24" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="I24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3.1</v>
       </c>
     </row>
     <row r="25">
@@ -1490,16 +1490,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1509,10 +1509,10 @@
         <v>6.7</v>
       </c>
       <c r="H25" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="I25" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
         <v>0.6</v>
@@ -1529,39 +1529,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.7</v>
+        <v>25.7</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G26" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="H26" t="n">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K26" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1572,39 +1572,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26.5</v>
+        <v>24.8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="G27" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="H27" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="28">
@@ -1615,39 +1615,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>26</v>
+        <v>24.7</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>3.1</v>
       </c>
       <c r="G28" t="n">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="H28" t="n">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="29">
@@ -1658,39 +1658,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.8</v>
+        <v>26.4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="G29" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="H29" t="n">
-        <v>7.9</v>
+        <v>9.1</v>
       </c>
       <c r="I29" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K29" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1705,16 +1705,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.7</v>
+        <v>24.4</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1752,12 +1752,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1767,13 +1767,13 @@
         <v>6.4</v>
       </c>
       <c r="H31" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I31" t="n">
         <v>2.4</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K31" t="n">
         <v>3.1</v>
@@ -1866,22 +1866,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>3.2</v>
       </c>
       <c r="G2" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I2" t="n">
         <v>1.2</v>
@@ -1890,7 +1890,7 @@
         <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3">
@@ -1905,26 +1905,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>83.9</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
         <v>1.3</v>
@@ -1948,11 +1948,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G4" t="n">
         <v>6.3</v>
@@ -1976,7 +1976,7 @@
         <v>0.6</v>
       </c>
       <c r="K4" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="5">
@@ -1991,7 +1991,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23</v>
+        <v>22.7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -2030,39 +2030,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.4</v>
+        <v>23.2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="H6" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
         <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="7">
@@ -2077,16 +2077,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -2096,7 +2096,7 @@
         <v>6.8</v>
       </c>
       <c r="H7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I7" t="n">
         <v>1.6</v>
@@ -2116,39 +2116,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23.2</v>
+        <v>22.4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J8" t="n">
         <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -2202,39 +2202,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.7</v>
+        <v>23.2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="H10" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="I10" t="n">
         <v>1.4</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K10" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11">
@@ -2245,39 +2245,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>84.1</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K11" t="n">
         <v>3</v>
-      </c>
-      <c r="G11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="12">
@@ -2331,39 +2331,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.1</v>
+        <v>22.9</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="G13" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="H13" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K13" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="14">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2382,31 +2382,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>84.1</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="G14" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="H14" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
         <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="15">
@@ -2417,15 +2417,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>22.1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2434,22 +2434,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="H15" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="16">
@@ -2516,17 +2516,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>3.2</v>
       </c>
       <c r="G17" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="H17" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I17" t="n">
         <v>1.4</v>
@@ -2535,7 +2535,7 @@
         <v>0.6</v>
       </c>
       <c r="K17" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="18">
@@ -2546,39 +2546,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>83.9</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="G18" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="H18" t="n">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="19">
@@ -2589,39 +2589,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="G19" t="n">
         <v>6.6</v>
       </c>
       <c r="H19" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="20">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2649,13 +2649,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="G20" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H20" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I20" t="n">
         <v>1.8</v>
@@ -2664,7 +2664,7 @@
         <v>0.8</v>
       </c>
       <c r="K20" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="21">
@@ -2675,39 +2675,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.3</v>
+        <v>24.7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>7.1</v>
       </c>
       <c r="H21" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="22">
@@ -2718,39 +2718,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.6</v>
+        <v>23.9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="G22" t="n">
-        <v>7.1</v>
+        <v>6.2</v>
       </c>
       <c r="H22" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="23">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -2787,7 +2787,7 @@
         <v>5.9</v>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J23" t="n">
         <v>0.7</v>
@@ -2804,39 +2804,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.8</v>
+        <v>23.3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="G24" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="H24" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="I24" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
         <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="25">
@@ -2847,39 +2847,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.9</v>
+        <v>24.3</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="G25" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="H25" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
         <v>0.6</v>
       </c>
       <c r="K25" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="26">
@@ -2890,39 +2890,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.4</v>
+        <v>25</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="G26" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="H26" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="I26" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
         <v>0.6</v>
       </c>
       <c r="K26" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="27">
@@ -2933,39 +2933,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24</v>
+        <v>23.4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="G27" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="28">
@@ -2976,39 +2976,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.3</v>
+        <v>24.1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="G28" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H28" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K28" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="29">
@@ -3023,26 +3023,26 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.3</v>
+        <v>24.7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>2.9</v>
       </c>
       <c r="G29" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="H29" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I29" t="n">
         <v>2.2</v>
@@ -3051,7 +3051,7 @@
         <v>0.7</v>
       </c>
       <c r="K29" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="30">
@@ -3066,26 +3066,26 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G30" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="H30" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I30" t="n">
         <v>1.9</v>
@@ -3109,20 +3109,20 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="G31" t="n">
         <v>6.7</v>
@@ -3137,7 +3137,7 @@
         <v>0.8</v>
       </c>
       <c r="K31" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>
@@ -3266,16 +3266,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -3294,7 +3294,7 @@
         <v>0.7</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="4">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -3328,16 +3328,16 @@
         <v>7.9</v>
       </c>
       <c r="H4" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J4" t="n">
         <v>0.6</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="5">
@@ -3391,39 +3391,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.9</v>
+        <v>22.6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G6" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="7">
@@ -3434,39 +3434,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.7</v>
+        <v>21.5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="G7" t="n">
         <v>7.6</v>
       </c>
       <c r="H7" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="8">
@@ -3477,39 +3477,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.5</v>
+        <v>21.1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="G8" t="n">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="9">
@@ -3520,39 +3520,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.7</v>
+        <v>22.6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="H9" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K9" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="10">
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.9</v>
+        <v>20.7</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>2.7</v>
       </c>
       <c r="G10" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="K10" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11">
@@ -3606,36 +3606,36 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.8</v>
+        <v>20.8</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2.6</v>
       </c>
       <c r="G11" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="H11" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="I11" t="n">
         <v>1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K11" t="n">
         <v>2.3</v>
@@ -3653,20 +3653,20 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G12" t="n">
         <v>7.2</v>
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20.7</v>
+        <v>21.8</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>2.7</v>
       </c>
       <c r="G13" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="14">
@@ -3735,39 +3735,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="G14" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="H14" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I14" t="n">
         <v>1.7</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="15">
@@ -3778,39 +3778,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.2</v>
+        <v>22.7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="G15" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="H15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0.8</v>
       </c>
       <c r="K15" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="16">
@@ -3821,39 +3821,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G16" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="H16" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="17">
@@ -3864,39 +3864,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G17" t="n">
-        <v>8.4</v>
+        <v>6.9</v>
       </c>
       <c r="H17" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="18">
@@ -3907,30 +3907,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.7</v>
+        <v>23</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G18" t="n">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="I18" t="n">
         <v>1.5</v>
@@ -3939,7 +3939,7 @@
         <v>0.8</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="19">
@@ -3950,39 +3950,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="F19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K19" t="n">
         <v>2.5</v>
-      </c>
-      <c r="G19" t="n">
-        <v>7</v>
-      </c>
-      <c r="H19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2.4</v>
       </c>
     </row>
     <row r="20">
@@ -3993,39 +3993,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.5</v>
+        <v>23.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>84.1</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="G20" t="n">
-        <v>6.9</v>
+        <v>7.9</v>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K20" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -4040,11 +4040,11 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4056,10 +4056,10 @@
         <v>2.8</v>
       </c>
       <c r="G21" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="H21" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I21" t="n">
         <v>1.7</v>
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4092,26 +4092,26 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>2.4</v>
       </c>
       <c r="G22" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H22" t="n">
         <v>5.1</v>
       </c>
       <c r="I22" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="23">
@@ -4122,30 +4122,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.7</v>
+        <v>22.8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="H23" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I23" t="n">
         <v>1.7</v>
@@ -4154,7 +4154,7 @@
         <v>0.8</v>
       </c>
       <c r="K23" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="24">
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22.8</v>
+        <v>23.9</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>2.9</v>
       </c>
       <c r="G24" t="n">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>0.8</v>
       </c>
       <c r="K24" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="25">
@@ -4221,14 +4221,14 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G25" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="H25" t="n">
         <v>4</v>
@@ -4251,36 +4251,36 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G26" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="H26" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="I26" t="n">
         <v>1.7</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K26" t="n">
         <v>2.1</v>
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.3</v>
+        <v>23.4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="G27" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="H27" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>0.9</v>
       </c>
       <c r="K27" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="28">
@@ -4337,39 +4337,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.3</v>
+        <v>24.1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="H28" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0.9</v>
       </c>
       <c r="K28" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="29">
@@ -4380,39 +4380,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.1</v>
+        <v>23.8</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G29" t="n">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0.8</v>
       </c>
       <c r="K29" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="30">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -4431,31 +4431,31 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>7.6</v>
+        <v>8.9</v>
       </c>
       <c r="H30" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
         <v>0.8</v>
       </c>
       <c r="K30" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="31">
@@ -4470,7 +4470,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4479,7 +4479,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -4492,7 +4492,7 @@
         <v>4.5</v>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
@@ -4593,17 +4593,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G2" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
         <v>1.3</v>
@@ -4612,7 +4612,7 @@
         <v>0.8</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="3">
@@ -4627,23 +4627,23 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="G3" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="H3" t="n">
         <v>3.9</v>
@@ -4655,7 +4655,7 @@
         <v>1.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="4">
@@ -4670,11 +4670,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4686,10 +4686,10 @@
         <v>2.4</v>
       </c>
       <c r="G4" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="H4" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I4" t="n">
         <v>1.4</v>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4726,7 +4726,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="G5" t="n">
         <v>8.699999999999999</v>
@@ -4756,7 +4756,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -4765,14 +4765,14 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1.9</v>
       </c>
       <c r="G6" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="H6" t="n">
         <v>4.3</v>
@@ -4795,39 +4795,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.7</v>
+        <v>20.3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>10.2</v>
+        <v>9.4</v>
       </c>
       <c r="H7" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="8">
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.3</v>
+        <v>21.7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="G8" t="n">
-        <v>9.4</v>
+        <v>10.8</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J8" t="n">
         <v>1.2</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9">
@@ -4881,39 +4881,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.7</v>
+        <v>22.8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="G9" t="n">
-        <v>10.8</v>
+        <v>10.1</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I9" t="n">
         <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -4924,39 +4924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.4</v>
+        <v>22.1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>2.5</v>
       </c>
       <c r="G10" t="n">
-        <v>10.6</v>
+        <v>9.6</v>
       </c>
       <c r="H10" t="n">
         <v>4.4</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11">
@@ -4967,39 +4967,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2.4</v>
       </c>
       <c r="G11" t="n">
-        <v>9.5</v>
+        <v>10.5</v>
       </c>
       <c r="H11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="K11" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="12">
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.5</v>
+        <v>22</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K12" t="n">
         <v>2.7</v>
-      </c>
-      <c r="G12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2.1</v>
       </c>
     </row>
     <row r="13">
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>23.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="G13" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="14">
@@ -5139,39 +5139,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>2.2</v>
       </c>
       <c r="G15" t="n">
-        <v>10.9</v>
+        <v>10.1</v>
       </c>
       <c r="H15" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="I15" t="n">
         <v>1.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="16">
@@ -5182,15 +5182,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -5202,19 +5202,19 @@
         <v>2.3</v>
       </c>
       <c r="G16" t="n">
-        <v>10.4</v>
+        <v>10.9</v>
       </c>
       <c r="H16" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="17">
@@ -5225,39 +5225,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.7</v>
+        <v>23.2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>2.2</v>
       </c>
       <c r="G17" t="n">
-        <v>10</v>
+        <v>10.9</v>
       </c>
       <c r="H17" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="I17" t="n">
         <v>1.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="18">
@@ -5272,16 +5272,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -5291,7 +5291,7 @@
         <v>9.4</v>
       </c>
       <c r="H18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I18" t="n">
         <v>1.7</v>
@@ -5315,16 +5315,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -5340,7 +5340,7 @@
         <v>1.4</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K19" t="n">
         <v>2.3</v>
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G20" t="n">
-        <v>10.9</v>
+        <v>11.7</v>
       </c>
       <c r="H20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K20" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="21">
@@ -5401,11 +5401,11 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -5414,13 +5414,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G21" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="H21" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I21" t="n">
         <v>1.6</v>
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G22" t="n">
-        <v>11.7</v>
+        <v>9.6</v>
       </c>
       <c r="H22" t="n">
         <v>4.1</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="G23" t="n">
-        <v>10.2</v>
+        <v>10.5</v>
       </c>
       <c r="H23" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="I23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J23" t="n">
         <v>1.5</v>
       </c>
-      <c r="J23" t="n">
-        <v>1.2</v>
-      </c>
       <c r="K23" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="24">
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="G24" t="n">
         <v>10.1</v>
       </c>
       <c r="H24" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K24" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="25">
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.3</v>
+        <v>24.4</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="G25" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="H25" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="26">
@@ -5612,39 +5612,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G26" t="n">
-        <v>9.6</v>
+        <v>11.4</v>
       </c>
       <c r="H26" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="K26" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="27">
@@ -5655,27 +5655,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="G27" t="n">
-        <v>11.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H27" t="n">
         <v>4.5</v>
@@ -5684,7 +5684,7 @@
         <v>1.5</v>
       </c>
       <c r="J27" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K27" t="n">
         <v>2.5</v>
@@ -5698,39 +5698,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.5</v>
+        <v>27.3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G28" t="n">
         <v>10.7</v>
       </c>
       <c r="H28" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I28" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K28" t="n">
         <v>2</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K28" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="29">
@@ -5741,39 +5741,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27.3</v>
+        <v>24.7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>10.8</v>
+        <v>12.3</v>
       </c>
       <c r="H29" t="n">
         <v>4.6</v>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K29" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="30">
@@ -5784,36 +5784,36 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.7</v>
+        <v>23.9</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="G30" t="n">
-        <v>12.4</v>
+        <v>10.6</v>
       </c>
       <c r="H30" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J30" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K30" t="n">
         <v>2.5</v>
@@ -5835,22 +5835,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>2.9</v>
       </c>
       <c r="G31" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="H31" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I31" t="n">
         <v>1.7</v>
@@ -5945,7 +5945,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -5954,17 +5954,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>0.6</v>
       </c>
       <c r="G2" t="n">
-        <v>14.5</v>
+        <v>14.7</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I2" t="n">
         <v>1.4</v>
@@ -5973,7 +5973,7 @@
         <v>2.2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="3">
@@ -5984,39 +5984,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.2</v>
+        <v>21.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>14</v>
+        <v>15.7</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J3" t="n">
         <v>1.9</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="4">
@@ -6027,36 +6027,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.5</v>
+        <v>20.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="G4" t="n">
-        <v>15.7</v>
+        <v>14.5</v>
       </c>
       <c r="H4" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I4" t="n">
         <v>1.3</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>3.1</v>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -6093,13 +6093,13 @@
         <v>14.6</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I5" t="n">
         <v>1.4</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="K5" t="n">
         <v>2.9</v>
@@ -6113,39 +6113,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19.7</v>
+        <v>18.1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G6" t="n">
-        <v>13.6</v>
+        <v>13.2</v>
       </c>
       <c r="H6" t="n">
         <v>3.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="K6" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="7">
@@ -6160,26 +6160,26 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G7" t="n">
         <v>14.9</v>
       </c>
       <c r="H7" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I7" t="n">
         <v>1.3</v>
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.2</v>
+        <v>19.7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="G8" t="n">
-        <v>13</v>
+        <v>13.6</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="I8" t="n">
         <v>1.2</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>18.1</v>
+        <v>19</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="G9" t="n">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="10">
@@ -6328,39 +6328,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20.7</v>
+        <v>19</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1.4</v>
       </c>
       <c r="G11" t="n">
-        <v>13.8</v>
+        <v>14.4</v>
       </c>
       <c r="H11" t="n">
         <v>3.2</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J11" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.3</v>
+        <v>20.6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1.4</v>
       </c>
       <c r="G12" t="n">
-        <v>13.6</v>
+        <v>13.9</v>
       </c>
       <c r="H12" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="K12" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>19</v>
+        <v>18.4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="G13" t="n">
-        <v>14.4</v>
+        <v>13.5</v>
       </c>
       <c r="H13" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="K13" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="14">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18.5</v>
+        <v>22.4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="G14" t="n">
         <v>13.6</v>
       </c>
       <c r="H14" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="I14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J14" t="n">
         <v>1.5</v>
       </c>
-      <c r="J14" t="n">
-        <v>1.3</v>
-      </c>
       <c r="K14" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="15">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.9</v>
+        <v>21.1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I15" t="n">
         <v>1.4</v>
       </c>
-      <c r="G15" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.3</v>
-      </c>
       <c r="J15" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="16">
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1.2</v>
       </c>
       <c r="G16" t="n">
-        <v>14.2</v>
+        <v>15.5</v>
       </c>
       <c r="H16" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="17">
@@ -6586,39 +6586,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.2</v>
+        <v>21.8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>51.6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>68.2</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="G17" t="n">
-        <v>12.5</v>
+        <v>13.7</v>
       </c>
       <c r="H17" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J17" t="n">
         <v>1.5</v>
       </c>
-      <c r="J17" t="n">
-        <v>1.9</v>
-      </c>
       <c r="K17" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="18">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -6637,31 +6637,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1.2</v>
       </c>
       <c r="G18" t="n">
-        <v>15.6</v>
+        <v>14.2</v>
       </c>
       <c r="H18" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="19">
@@ -6676,26 +6676,26 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>1.4</v>
       </c>
       <c r="G19" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="H19" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="I19" t="n">
         <v>1.8</v>
@@ -6723,7 +6723,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -6732,10 +6732,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="G20" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="H20" t="n">
         <v>4.1</v>
@@ -6747,7 +6747,7 @@
         <v>1.6</v>
       </c>
       <c r="K20" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="21">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -6781,7 +6781,7 @@
         <v>14.2</v>
       </c>
       <c r="H21" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I21" t="n">
         <v>1.4</v>
@@ -6801,39 +6801,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.7</v>
+        <v>21.2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I22" t="n">
         <v>1.5</v>
       </c>
-      <c r="G22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="H22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1.6</v>
-      </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="K22" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="23">
@@ -6844,39 +6844,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21.2</v>
+        <v>21.5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="G23" t="n">
-        <v>14.1</v>
+        <v>15.6</v>
       </c>
       <c r="H23" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J23" t="n">
         <v>1.9</v>
       </c>
       <c r="K23" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="24">
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>21.8</v>
+        <v>24.7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="G24" t="n">
-        <v>15.4</v>
+        <v>14.5</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="K24" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="25">
@@ -6930,39 +6930,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22.7</v>
+        <v>23.7</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>14.2</v>
+        <v>15.6</v>
       </c>
       <c r="H25" t="n">
         <v>4.4</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="K25" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="26">
@@ -6973,39 +6973,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.1</v>
+        <v>21.3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="G26" t="n">
-        <v>15.4</v>
+        <v>14.2</v>
       </c>
       <c r="H26" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="K26" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="27">
@@ -7016,36 +7016,36 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>21.3</v>
+        <v>23</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="G27" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="H27" t="n">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="K27" t="n">
         <v>2.2</v>
@@ -7063,32 +7063,32 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24</v>
+        <v>24.3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G28" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="H28" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I28" t="n">
         <v>1.2</v>
       </c>
       <c r="J28" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="K28" t="n">
         <v>2.7</v>
@@ -7106,23 +7106,23 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G29" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="H29" t="n">
         <v>4.4</v>
@@ -7149,11 +7149,11 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -7165,7 +7165,7 @@
         <v>1.3</v>
       </c>
       <c r="G30" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="H30" t="n">
         <v>4.5</v>
@@ -7192,26 +7192,26 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.6</v>
+        <v>25.8</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>59.3</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>67.7</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1.3</v>
       </c>
       <c r="G31" t="n">
-        <v>16.1</v>
+        <v>15.9</v>
       </c>
       <c r="H31" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I31" t="n">
         <v>1.8</v>

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -501,16 +501,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -523,7 +523,7 @@
         <v>8.5</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="n">
         <v>0.5</v>
@@ -540,39 +540,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.2</v>
+        <v>21.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="G3" t="n">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="H3" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J3" t="n">
         <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="4">
@@ -583,39 +583,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.3</v>
+        <v>22.2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="G4" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="H4" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J4" t="n">
         <v>0.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -673,23 +673,23 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.8</v>
+        <v>21.3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>40.8</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G6" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="H6" t="n">
         <v>9.1</v>
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -907,7 +907,7 @@
         <v>6.8</v>
       </c>
       <c r="H11" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I11" t="n">
         <v>1.8</v>
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.2</v>
+        <v>24.4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="G13" t="n">
-        <v>5.3</v>
+        <v>6.7</v>
       </c>
       <c r="H13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="14">
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24.4</v>
+        <v>23.2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>6.7</v>
+        <v>5.3</v>
       </c>
       <c r="H14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="15">
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.3</v>
+        <v>23.8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>2.9</v>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H17" t="n">
-        <v>9.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K17" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="18">
@@ -1185,39 +1185,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.8</v>
+        <v>25</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="G18" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="H18" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="19">
@@ -1228,39 +1228,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>25</v>
+        <v>23.3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="G19" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="H19" t="n">
-        <v>8.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
         <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="20">
@@ -1271,39 +1271,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="H20" t="n">
         <v>8.4</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K20" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="21">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1322,31 +1322,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G21" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="H21" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K21" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="22">
@@ -1357,39 +1357,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="H22" t="n">
-        <v>9.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>0.5</v>
       </c>
       <c r="K22" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23">
@@ -1400,39 +1400,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24</v>
+        <v>24.6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G23" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="H23" t="n">
-        <v>7.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
         <v>0.5</v>
       </c>
       <c r="K23" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="24">
@@ -1447,26 +1447,26 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="H24" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="I24" t="n">
         <v>1.9</v>
@@ -1490,7 +1490,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>26.1</v>
+        <v>25.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1512,7 +1512,7 @@
         <v>8.5</v>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J25" t="n">
         <v>0.6</v>
@@ -1529,39 +1529,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25.7</v>
+        <v>24.6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G26" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="H26" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="27">
@@ -1572,39 +1572,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.8</v>
+        <v>25.6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="H27" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J27" t="n">
         <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -1862,11 +1862,11 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G2" t="n">
         <v>6.4</v>
@@ -1884,13 +1884,13 @@
         <v>5.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J2" t="n">
         <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="3">
@@ -1901,39 +1901,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.7</v>
+        <v>21.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G3" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="4">
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="5">
@@ -2030,39 +2030,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23.2</v>
+        <v>22.8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="G6" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="H6" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7">
@@ -2073,39 +2073,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.8</v>
+        <v>22.3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="8">
@@ -2116,39 +2116,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.4</v>
+        <v>23.2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="H8" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
@@ -2159,39 +2159,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23.8</v>
+        <v>23.1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>6.3</v>
+        <v>7.5</v>
       </c>
       <c r="H9" t="n">
         <v>4.8</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K9" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -2202,39 +2202,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G10" t="n">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="H10" t="n">
         <v>4.8</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K10" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="11">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2253,31 +2253,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>84.1</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="G11" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="H11" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2296,31 +2296,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>84.1</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="G12" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="H12" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -2331,39 +2331,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G13" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="H13" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="14">
@@ -2374,39 +2374,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="H14" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="15">
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="G15" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="H15" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="16">
@@ -2460,39 +2460,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.3</v>
+        <v>22.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="H16" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="17">
@@ -2546,39 +2546,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>83.9</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="G18" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="H18" t="n">
-        <v>6.1</v>
+        <v>5.4</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="19">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2597,31 +2597,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="G19" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H19" t="n">
         <v>5.4</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K19" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="20">
@@ -2632,36 +2632,36 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>83.9</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="G20" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H20" t="n">
-        <v>5.4</v>
+        <v>6.1</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="K20" t="n">
         <v>2.7</v>
@@ -2675,15 +2675,15 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.7</v>
+        <v>24.4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2692,22 +2692,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="G21" t="n">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22">
@@ -2718,39 +2718,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.9</v>
+        <v>24.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="G22" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="H22" t="n">
         <v>5.3</v>
       </c>
       <c r="I22" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23">
@@ -2804,39 +2804,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.3</v>
+        <v>25</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="G24" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="H24" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="25">
@@ -2847,39 +2847,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.3</v>
+        <v>23.5</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="H25" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0.6</v>
       </c>
       <c r="K25" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="26">
@@ -2890,39 +2890,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25</v>
+        <v>23.9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="G26" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="H26" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="J26" t="n">
         <v>0.6</v>
       </c>
       <c r="K26" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="27">
@@ -2933,39 +2933,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.4</v>
+        <v>24.1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="G27" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H27" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="28">
@@ -2976,39 +2976,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.1</v>
+        <v>23.3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="G28" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="I28" t="n">
         <v>1.8</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K28" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="29">
@@ -3062,39 +3062,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.4</v>
+        <v>26.3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="G30" t="n">
-        <v>7.2</v>
+        <v>6.7</v>
       </c>
       <c r="H30" t="n">
-        <v>5.4</v>
+        <v>6.7</v>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K30" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="31">
@@ -3105,39 +3105,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>26.3</v>
+        <v>24.4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="G31" t="n">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="H31" t="n">
-        <v>6.7</v>
+        <v>5.4</v>
       </c>
       <c r="I31" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K31" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
     </row>
   </sheetData>
@@ -3262,39 +3262,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.9</v>
+        <v>22.9</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="4">
@@ -3305,39 +3305,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.8</v>
+        <v>22</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>43.2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>7.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="5">
@@ -3348,39 +3348,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23.2</v>
+        <v>21.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="G5" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="H5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J5" t="n">
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="6">
@@ -3391,39 +3391,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.6</v>
+        <v>21.1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="G6" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="H6" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="K6" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7">
@@ -3434,39 +3434,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.5</v>
+        <v>22.6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="G7" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="K7" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="8">
@@ -3477,39 +3477,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.1</v>
+        <v>21.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="G8" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="H8" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J8" t="n">
         <v>0.8</v>
       </c>
       <c r="K8" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="9">
@@ -3520,39 +3520,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.6</v>
+        <v>20.8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>7.7</v>
+        <v>8.4</v>
       </c>
       <c r="H9" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K9" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="10">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20.8</v>
+        <v>22.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2.6</v>
       </c>
       <c r="G11" t="n">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="H11" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="12">
@@ -3649,39 +3649,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.8</v>
+        <v>21.8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="G12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="H12" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K12" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="13">
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.8</v>
+        <v>22.8</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G13" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K13" t="n">
         <v>2.7</v>
-      </c>
-      <c r="G13" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="H13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2.1</v>
       </c>
     </row>
     <row r="14">
@@ -3735,30 +3735,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="G14" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="H14" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I14" t="n">
         <v>1.7</v>
@@ -3767,7 +3767,7 @@
         <v>0.8</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="15">
@@ -3778,39 +3778,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="G15" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
         <v>0.8</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="16">
@@ -3821,39 +3821,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>2.6</v>
       </c>
       <c r="G16" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="17">
@@ -3864,39 +3864,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>2.6</v>
       </c>
       <c r="G17" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="H17" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="18">
@@ -3954,11 +3954,11 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G19" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="H19" t="n">
         <v>4.2</v>
@@ -3979,7 +3979,7 @@
         <v>1.6</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
         <v>2.5</v>
@@ -3993,39 +3993,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.8</v>
+        <v>22.9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="G20" t="n">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="H20" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="21">
@@ -4036,39 +4036,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.9</v>
+        <v>23.8</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="G21" t="n">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="H21" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="K21" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -4251,39 +4251,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.3</v>
+        <v>23.4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="G26" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="H26" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0.9</v>
       </c>
       <c r="K26" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="27">
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.4</v>
+        <v>24.1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="H27" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
         <v>0.9</v>
       </c>
       <c r="K27" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="28">
@@ -4337,30 +4337,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G28" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="H28" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="I28" t="n">
         <v>1.7</v>
@@ -4470,35 +4470,35 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>3.3</v>
       </c>
       <c r="G31" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -4799,16 +4799,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -4818,7 +4818,7 @@
         <v>9.4</v>
       </c>
       <c r="H7" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I7" t="n">
         <v>1.7</v>
@@ -4846,19 +4846,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>2.1</v>
       </c>
       <c r="G8" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="H8" t="n">
         <v>3.9</v>
@@ -4881,39 +4881,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.8</v>
+        <v>21.5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="G9" t="n">
-        <v>10.1</v>
+        <v>10.5</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="I9" t="n">
         <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="K9" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="10">
@@ -4967,39 +4967,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.5</v>
+        <v>22.9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="G11" t="n">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="H11" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="I11" t="n">
         <v>1.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="K11" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12">
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>23.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="G12" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K12" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="13">
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.5</v>
+        <v>22</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K13" t="n">
         <v>2.7</v>
-      </c>
-      <c r="G13" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2.1</v>
       </c>
     </row>
     <row r="14">
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.9</v>
+        <v>22.7</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="G14" t="n">
-        <v>9.800000000000001</v>
+        <v>10.9</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="15">
@@ -5139,39 +5139,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.6</v>
+        <v>21.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="G15" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J15" t="n">
         <v>1.5</v>
       </c>
-      <c r="J15" t="n">
-        <v>1.3</v>
-      </c>
       <c r="K15" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="16">
@@ -5182,36 +5182,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.7</v>
+        <v>23.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G16" t="n">
-        <v>10.9</v>
+        <v>10.1</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="I16" t="n">
         <v>1.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K16" t="n">
         <v>2.2</v>
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.2</v>
+        <v>23.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="G19" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="H19" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="I19" t="n">
         <v>1.4</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="20">
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.7</v>
+        <v>23.2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>48.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G20" t="n">
-        <v>11.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K20" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="21">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G22" t="n">
-        <v>9.6</v>
+        <v>11.8</v>
       </c>
       <c r="H22" t="n">
         <v>4.1</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="G23" t="n">
-        <v>10.5</v>
+        <v>10.1</v>
       </c>
       <c r="H23" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K23" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="24">
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.7</v>
+        <v>23</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="G24" t="n">
-        <v>10.1</v>
+        <v>11.4</v>
       </c>
       <c r="H24" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I24" t="n">
         <v>1.5</v>
       </c>
       <c r="J24" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K24" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="25">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -5586,10 +5586,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G25" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="H25" t="n">
         <v>3.5</v>
@@ -5612,39 +5612,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G26" t="n">
-        <v>11.4</v>
+        <v>9.6</v>
       </c>
       <c r="H26" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="K26" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="27">
@@ -5698,39 +5698,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.3</v>
+        <v>23.9</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>2.6</v>
       </c>
       <c r="G28" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="H28" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K28" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="29">
@@ -5784,39 +5784,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>23.9</v>
+        <v>27.3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>51.0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>2.6</v>
       </c>
       <c r="G30" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="H30" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K30" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -5941,39 +5941,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19.6</v>
+        <v>21.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>14.7</v>
+        <v>15.7</v>
       </c>
       <c r="H2" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J2" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="3">
@@ -5984,39 +5984,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.5</v>
+        <v>19.6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="G3" t="n">
-        <v>15.7</v>
+        <v>14.7</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="4">
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19.2</v>
+        <v>18.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G5" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="6">
@@ -6113,39 +6113,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18.1</v>
+        <v>19.6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="G6" t="n">
-        <v>13.2</v>
+        <v>13.7</v>
       </c>
       <c r="H6" t="n">
         <v>3.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="7">
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.7</v>
+        <v>19</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="G8" t="n">
-        <v>13.6</v>
+        <v>12.9</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="K8" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="9">
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>12.9</v>
+        <v>14.6</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="K9" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="10">
@@ -6293,19 +6293,19 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>72.9</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="G10" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="H10" t="n">
         <v>3</v>
@@ -6317,7 +6317,7 @@
         <v>1.9</v>
       </c>
       <c r="K10" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11">
@@ -6332,35 +6332,35 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G11" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I11" t="n">
         <v>1.1</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20.6</v>
+        <v>18.4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="G12" t="n">
-        <v>13.9</v>
+        <v>13.5</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J12" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="K12" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>18.4</v>
+        <v>22.4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="G13" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="H13" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J13" t="n">
         <v>1.5</v>
       </c>
-      <c r="J13" t="n">
-        <v>1.3</v>
-      </c>
       <c r="K13" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="14">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.4</v>
+        <v>20.6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1.4</v>
       </c>
       <c r="G14" t="n">
-        <v>13.6</v>
+        <v>13.9</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="15">
@@ -6500,36 +6500,36 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="G15" t="n">
-        <v>12.6</v>
+        <v>14.2</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
         <v>2.3</v>
@@ -6586,39 +6586,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>51.6</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="F17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I17" t="n">
         <v>1.4</v>
       </c>
-      <c r="G17" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="H17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1.3</v>
-      </c>
       <c r="J17" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="18">
@@ -6629,39 +6629,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>20.9</v>
+        <v>21.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="F18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G18" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I18" t="n">
         <v>1.2</v>
       </c>
-      <c r="G18" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="H18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.3</v>
-      </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="19">
@@ -6672,39 +6672,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F19" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I19" t="n">
         <v>1.4</v>
       </c>
-      <c r="G19" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="H19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1.8</v>
-      </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="K19" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="20">
@@ -6715,39 +6715,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="G20" t="n">
-        <v>11.6</v>
+        <v>14.7</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="21">
@@ -6758,39 +6758,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23</v>
+        <v>21.2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="H21" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="K21" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="22">
@@ -6801,39 +6801,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21.2</v>
+        <v>21.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="G22" t="n">
-        <v>14.1</v>
+        <v>15.6</v>
       </c>
       <c r="H22" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
         <v>1.9</v>
       </c>
       <c r="K22" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="23">
@@ -6844,39 +6844,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21.5</v>
+        <v>23</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>58.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="G23" t="n">
-        <v>15.6</v>
+        <v>14.2</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="K23" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="24">
@@ -6977,16 +6977,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -7005,7 +7005,7 @@
         <v>1.8</v>
       </c>
       <c r="K26" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="27">
@@ -7016,39 +7016,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23</v>
+        <v>24.2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="G27" t="n">
-        <v>14.3</v>
+        <v>15.4</v>
       </c>
       <c r="H27" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="K27" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="28">
@@ -7059,39 +7059,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.3</v>
+        <v>23</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="G28" t="n">
-        <v>16</v>
+        <v>14.3</v>
       </c>
       <c r="H28" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I28" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="K28" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="29">
@@ -7102,39 +7102,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.2</v>
+        <v>24</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G29" t="n">
         <v>15.4</v>
       </c>
       <c r="H29" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="30">
@@ -7145,39 +7145,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24</v>
+        <v>24.6</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1.3</v>
       </c>
       <c r="G30" t="n">
-        <v>15.4</v>
+        <v>16.1</v>
       </c>
       <c r="H30" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="K30" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="31">

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -600,7 +600,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G4" t="n">
         <v>5.6</v>
@@ -609,7 +609,7 @@
         <v>7.3</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
         <v>0.5</v>
@@ -634,12 +634,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -649,7 +649,7 @@
         <v>6.2</v>
       </c>
       <c r="H5" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="I5" t="n">
         <v>1.7</v>
@@ -658,7 +658,7 @@
         <v>0.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="6">
@@ -755,30 +755,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23.2</v>
+        <v>22.3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G8" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>7.1</v>
+        <v>8.4</v>
       </c>
       <c r="I8" t="n">
         <v>2</v>
@@ -787,7 +787,7 @@
         <v>0.4</v>
       </c>
       <c r="K8" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -798,39 +798,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.3</v>
+        <v>23.2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>2.8</v>
       </c>
       <c r="G9" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="H9" t="n">
-        <v>8.6</v>
+        <v>7.1</v>
       </c>
       <c r="I9" t="n">
         <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="10">
@@ -841,39 +841,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23.9</v>
+        <v>24.3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="G10" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="H10" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J10" t="n">
         <v>0.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="11">
@@ -888,29 +888,29 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2.7</v>
       </c>
       <c r="G11" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="H11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J11" t="n">
         <v>0.5</v>
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24.4</v>
+        <v>27.1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>6.7</v>
+        <v>5.9</v>
       </c>
       <c r="H13" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="14">
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.2</v>
+        <v>24.1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="15">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27</v>
+        <v>23.1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="16">
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.9</v>
+        <v>23.4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="G16" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="H16" t="n">
-        <v>9.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K16" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="17">
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2</v>
+        <v>5.3</v>
       </c>
       <c r="H17" t="n">
-        <v>7.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="K17" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="18">
@@ -1185,39 +1185,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
+        <v>23.9</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="H18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K18" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="19">
@@ -1228,39 +1228,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.3</v>
+        <v>24.9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="G19" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="H19" t="n">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I19" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
         <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="20">
@@ -1271,39 +1271,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.2</v>
+        <v>24</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G20" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="H20" t="n">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J20" t="n">
         <v>0.6</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="21">
@@ -1314,39 +1314,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.2</v>
+        <v>24.7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="G21" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="H21" t="n">
-        <v>8.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
         <v>0.5</v>
       </c>
       <c r="K21" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="22">
@@ -1357,39 +1357,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G22" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H22" t="n">
-        <v>7.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J22" t="n">
         <v>0.5</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="23">
@@ -1400,39 +1400,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="H23" t="n">
-        <v>9.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J23" t="n">
         <v>0.5</v>
       </c>
       <c r="K23" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="24">
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1619,23 +1619,23 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>3.1</v>
       </c>
       <c r="G28" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="H28" t="n">
         <v>7.9</v>
@@ -1658,39 +1658,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.4</v>
+        <v>24.5</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="H29" t="n">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I29" t="n">
         <v>2.1</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="30">
@@ -1701,39 +1701,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.4</v>
+        <v>26.6</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>83.9</t>
         </is>
       </c>
       <c r="F30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H30" t="n">
+        <v>9</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K30" t="n">
         <v>3</v>
-      </c>
-      <c r="G30" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H30" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K30" t="n">
-        <v>2.8</v>
       </c>
     </row>
     <row r="31">
@@ -1748,23 +1748,23 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>3.6</v>
       </c>
       <c r="G31" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H31" t="n">
         <v>8.300000000000001</v>
@@ -1773,7 +1773,7 @@
         <v>2.4</v>
       </c>
       <c r="J31" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K31" t="n">
         <v>3.1</v>
@@ -1948,16 +1948,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>84.2</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1967,13 +1967,13 @@
         <v>6.5</v>
       </c>
       <c r="H4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I4" t="n">
         <v>1.3</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K4" t="n">
         <v>2.4</v>
@@ -2034,16 +2034,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -2053,7 +2053,7 @@
         <v>6.8</v>
       </c>
       <c r="H6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I6" t="n">
         <v>1.6</v>
@@ -2077,23 +2077,23 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H7" t="n">
         <v>5.5</v>
@@ -2105,7 +2105,7 @@
         <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="8">
@@ -2202,39 +2202,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23.8</v>
+        <v>22.7</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>83.9</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="G10" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="H10" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="11">
@@ -2245,39 +2245,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.8</v>
+        <v>23.7</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="G11" t="n">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="H11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="12">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2296,31 +2296,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>84.1</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="G12" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="H12" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="13">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2339,31 +2339,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G13" t="n">
-        <v>6.2</v>
+        <v>7.5</v>
       </c>
       <c r="H13" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="14">
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="H15" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J15" t="n">
         <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="16">
@@ -2460,39 +2460,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.1</v>
+        <v>23.3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="G16" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="H16" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="17">
@@ -2503,39 +2503,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.7</v>
+        <v>22</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="G17" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="H17" t="n">
         <v>5.8</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>0.6</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="18">
@@ -2546,39 +2546,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="G18" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H18" t="n">
         <v>5.4</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="19">
@@ -2589,39 +2589,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="G19" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H19" t="n">
         <v>5.4</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="20">
@@ -2722,11 +2722,11 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2735,19 +2735,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="G22" t="n">
         <v>7.2</v>
       </c>
       <c r="H22" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I22" t="n">
         <v>1.5</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K22" t="n">
         <v>2.9</v>
@@ -2761,39 +2761,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.1</v>
+        <v>25</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="G23" t="n">
         <v>6.7</v>
       </c>
       <c r="H23" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="24">
@@ -2804,39 +2804,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25</v>
+        <v>24.1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="G24" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="H24" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K24" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="25">
@@ -2894,32 +2894,32 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>3.1</v>
       </c>
       <c r="G26" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="H26" t="n">
         <v>5.3</v>
       </c>
       <c r="I26" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K26" t="n">
         <v>3.2</v>
@@ -2933,36 +2933,36 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.1</v>
+        <v>23.2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
         <v>2.9</v>
@@ -3109,7 +3109,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.4</v>
+        <v>24.6</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -3223,16 +3223,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -3248,7 +3248,7 @@
         <v>1.7</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K2" t="n">
         <v>3.1</v>
@@ -3352,23 +3352,23 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G5" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="H5" t="n">
         <v>4</v>
@@ -3434,39 +3434,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="G7" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="H7" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="8">
@@ -3477,39 +3477,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.5</v>
+        <v>22.6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="G8" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="K8" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9">
@@ -3520,39 +3520,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="H9" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="I9" t="n">
         <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="K9" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="10">
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G10" t="n">
-        <v>7.7</v>
+        <v>8.4</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I10" t="n">
         <v>1.6</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="K10" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="11">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -3629,16 +3629,16 @@
         <v>7.7</v>
       </c>
       <c r="H11" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
         <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="12">
@@ -3696,26 +3696,26 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
         <v>7.2</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I13" t="n">
         <v>1.6</v>
@@ -3724,7 +3724,7 @@
         <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="14">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3795,19 +3795,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G15" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="H15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I15" t="n">
         <v>1.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K15" t="n">
         <v>2.5</v>
@@ -3821,39 +3821,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>2.6</v>
       </c>
       <c r="G16" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="H16" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="17">
@@ -3864,39 +3864,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.1</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>2.6</v>
       </c>
       <c r="G17" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="18">
@@ -3907,39 +3907,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G18" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K18" t="n">
         <v>2.7</v>
-      </c>
-      <c r="G18" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="H18" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K18" t="n">
-        <v>2.8</v>
       </c>
     </row>
     <row r="19">
@@ -3950,39 +3950,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.8</v>
+        <v>23.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="G19" t="n">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="H19" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K19" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -3993,39 +3993,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G20" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="H20" t="n">
         <v>4.2</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="21">
@@ -4036,30 +4036,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.8</v>
+        <v>23.4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="G21" t="n">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="H21" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="I21" t="n">
         <v>1.5</v>
@@ -4068,7 +4068,7 @@
         <v>0.8</v>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="22">
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21.9</v>
+        <v>22.9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="H22" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="I22" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="23">
@@ -4122,39 +4122,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22.8</v>
+        <v>23.9</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G23" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="H23" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0.8</v>
       </c>
       <c r="K23" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="24">
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.9</v>
+        <v>22</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="G24" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="25">
@@ -4208,39 +4208,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>26.4</v>
+        <v>23.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G25" t="n">
-        <v>7.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K25" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="26">
@@ -4251,39 +4251,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.4</v>
+        <v>26.4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G26" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="H26" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="K26" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="27">
@@ -4298,16 +4298,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.1</v>
+        <v>23.9</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -4326,7 +4326,7 @@
         <v>0.9</v>
       </c>
       <c r="K27" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -4337,39 +4337,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.3</v>
+        <v>23.4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="G28" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="H28" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
         <v>0.9</v>
       </c>
       <c r="K28" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="29">
@@ -4380,33 +4380,33 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>23.8</v>
+        <v>24.2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>7.7</v>
+        <v>8.9</v>
       </c>
       <c r="H29" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
         <v>0.8</v>
@@ -4423,33 +4423,33 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G30" t="n">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="H30" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I30" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
         <v>0.8</v>
@@ -4666,39 +4666,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.4</v>
+        <v>20.6</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="G4" t="n">
-        <v>10.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="5">
@@ -4709,39 +4709,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20.6</v>
+        <v>21.4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="G5" t="n">
-        <v>8.699999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="I5" t="n">
         <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="6">
@@ -4756,11 +4756,11 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
         <v>10.8</v>
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.7</v>
+        <v>22.9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="G8" t="n">
-        <v>10.7</v>
+        <v>10.2</v>
       </c>
       <c r="H8" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I8" t="n">
         <v>1.3</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9">
@@ -4881,39 +4881,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="G9" t="n">
-        <v>10.5</v>
+        <v>10.7</v>
       </c>
       <c r="H9" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="I9" t="n">
         <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="10">
@@ -4967,39 +4967,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.9</v>
+        <v>23.3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="G11" t="n">
-        <v>10.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K11" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="12">
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.3</v>
+        <v>22</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K12" t="n">
         <v>2.7</v>
-      </c>
-      <c r="G12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2.1</v>
       </c>
     </row>
     <row r="13">
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G13" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I13" t="n">
         <v>1.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="K13" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="14">
@@ -5100,23 +5100,23 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>2.3</v>
       </c>
       <c r="G14" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="H14" t="n">
         <v>4.1</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -5182,39 +5182,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.6</v>
+        <v>22</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="G16" t="n">
-        <v>10.1</v>
+        <v>9.4</v>
       </c>
       <c r="H16" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="17">
@@ -5225,39 +5225,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.2</v>
+        <v>23.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>2.2</v>
       </c>
       <c r="G17" t="n">
-        <v>10.9</v>
+        <v>10.1</v>
       </c>
       <c r="H17" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="I17" t="n">
         <v>1.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="K17" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="18">
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22</v>
+        <v>23.5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G18" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="H18" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="19">
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="G19" t="n">
-        <v>10.5</v>
+        <v>10.9</v>
       </c>
       <c r="H19" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="20">
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>48.7</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="G20" t="n">
-        <v>9.800000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="H20" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="I20" t="n">
         <v>1.4</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="K20" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="21">
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.1</v>
+        <v>23.4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G21" t="n">
-        <v>10.1</v>
+        <v>9.9</v>
       </c>
       <c r="H21" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="22">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G22" t="n">
-        <v>11.8</v>
+        <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="23">
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.7</v>
+        <v>22.6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="G23" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="H23" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="K23" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="24">
@@ -5526,27 +5526,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23</v>
+        <v>23.6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="G24" t="n">
-        <v>11.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H24" t="n">
         <v>4.5</v>
@@ -5555,10 +5555,10 @@
         <v>1.5</v>
       </c>
       <c r="J24" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K24" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="25">
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.4</v>
+        <v>23.1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G25" t="n">
-        <v>10</v>
+        <v>11.8</v>
       </c>
       <c r="H25" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="K25" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -5612,39 +5612,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>22.6</v>
+        <v>23</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="F26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G26" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K26" t="n">
         <v>2.4</v>
-      </c>
-      <c r="G26" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="H26" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="K26" t="n">
-        <v>2.7</v>
       </c>
     </row>
     <row r="27">
@@ -5655,39 +5655,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.6</v>
+        <v>24.2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G27" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="H27" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="28">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G28" t="n">
         <v>10.6</v>
@@ -5730,7 +5730,7 @@
         <v>1.2</v>
       </c>
       <c r="K28" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="29">
@@ -5741,39 +5741,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.7</v>
+        <v>27.4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G29" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K29" t="n">
         <v>2</v>
-      </c>
-      <c r="G29" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="H29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2.5</v>
       </c>
     </row>
     <row r="30">
@@ -5784,39 +5784,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>27.3</v>
+        <v>25.8</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="G30" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="H30" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="K30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -5827,39 +5827,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.8</v>
+        <v>24.7</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>50.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>10.6</v>
+        <v>12.3</v>
       </c>
       <c r="H31" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="I31" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>
@@ -5941,39 +5941,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.5</v>
+        <v>18.4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="G2" t="n">
-        <v>15.7</v>
+        <v>13.5</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="I2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J2" t="n">
         <v>1.3</v>
       </c>
-      <c r="J2" t="n">
-        <v>1.9</v>
-      </c>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="3">
@@ -5984,39 +5984,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.6</v>
+        <v>21.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>14.7</v>
+        <v>15.5</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="4">
@@ -6027,36 +6027,36 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.4</v>
+        <v>19.5</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="G4" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="H4" t="n">
         <v>4.4</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="K4" t="n">
         <v>3.1</v>
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18.1</v>
+        <v>19.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="G5" t="n">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="6">
@@ -6113,39 +6113,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19.6</v>
+        <v>20.5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G6" t="n">
-        <v>13.7</v>
+        <v>14.5</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="K6" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7">
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.9</v>
+        <v>18.1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G7" t="n">
-        <v>14.9</v>
+        <v>13.2</v>
       </c>
       <c r="H7" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>12.9</v>
+        <v>14.6</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9">
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19.2</v>
+        <v>21.9</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>56.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G9" t="n">
-        <v>14.6</v>
+        <v>14.9</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -6285,7 +6285,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -6293,31 +6293,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="G10" t="n">
-        <v>14.4</v>
+        <v>13.7</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I10" t="n">
         <v>1.2</v>
       </c>
       <c r="J10" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="K10" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="11">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>18.4</v>
+        <v>20.8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>67.6</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="G12" t="n">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="H12" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="K12" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.4</v>
+        <v>19.6</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="G13" t="n">
-        <v>13.6</v>
+        <v>14.4</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
         <v>1.2</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="K13" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20.6</v>
+        <v>22.5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1.4</v>
       </c>
       <c r="G14" t="n">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K14" t="n">
         <v>2.1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="15">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20.9</v>
+        <v>21.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I15" t="n">
         <v>1.2</v>
       </c>
-      <c r="G15" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.3</v>
-      </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="16">
@@ -6629,39 +6629,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21.8</v>
+        <v>20.9</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G18" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
       <c r="H18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="19">
@@ -6676,16 +6676,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -6719,7 +6719,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -6728,17 +6728,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>79.1</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>1.4</v>
       </c>
       <c r="G20" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="H20" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I20" t="n">
         <v>1.8</v>
@@ -6747,7 +6747,7 @@
         <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="21">
@@ -6762,7 +6762,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -6787,7 +6787,7 @@
         <v>1.5</v>
       </c>
       <c r="J21" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
         <v>2.3</v>
@@ -6801,39 +6801,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21.5</v>
+        <v>23.1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>56.2</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="G22" t="n">
-        <v>15.6</v>
+        <v>14.3</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J22" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="K22" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="23">
@@ -6844,39 +6844,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23</v>
+        <v>23.7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>58.0</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>14.2</v>
+        <v>15.6</v>
       </c>
       <c r="H23" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="K23" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="24">
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.7</v>
+        <v>21.6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="G24" t="n">
-        <v>14.5</v>
+        <v>15.9</v>
       </c>
       <c r="H24" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J24" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="K24" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="25">
@@ -6930,39 +6930,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.7</v>
+        <v>24.6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G25" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="H25" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="K25" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="26">
@@ -7016,39 +7016,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.2</v>
+        <v>23.2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="G27" t="n">
-        <v>15.4</v>
+        <v>14.4</v>
       </c>
       <c r="H27" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="28">
@@ -7059,39 +7059,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23</v>
+        <v>24.6</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="G28" t="n">
-        <v>14.3</v>
+        <v>16.1</v>
       </c>
       <c r="H28" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K28" t="n">
         <v>2.6</v>
-      </c>
-      <c r="K28" t="n">
-        <v>2.2</v>
       </c>
     </row>
     <row r="29">
@@ -7102,39 +7102,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G29" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="K29" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="30">
@@ -7145,39 +7145,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>68.9</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1.3</v>
       </c>
       <c r="G30" t="n">
-        <v>16.1</v>
+        <v>15.4</v>
       </c>
       <c r="H30" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="K30" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="31">
@@ -7192,23 +7192,23 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.8</v>
+        <v>25.6</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>59.7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.2</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>1.3</v>
       </c>
       <c r="G31" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="H31" t="n">
         <v>4.1</v>

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -501,16 +501,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -523,13 +523,13 @@
         <v>8.5</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="n">
         <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
@@ -540,39 +540,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.3</v>
+        <v>22.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="G3" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="H3" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="J3" t="n">
         <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -583,39 +583,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.3</v>
+        <v>21.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="G4" t="n">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="H4" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J4" t="n">
         <v>0.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="5">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -735,7 +735,7 @@
         <v>5.7</v>
       </c>
       <c r="H7" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
         <v>1.8</v>
@@ -802,20 +802,20 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G9" t="n">
         <v>6.4</v>
@@ -824,7 +824,7 @@
         <v>7.1</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J9" t="n">
         <v>0.4</v>
@@ -841,39 +841,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24.3</v>
+        <v>25.1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="G10" t="n">
         <v>6.7</v>
       </c>
       <c r="H10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
         <v>0.5</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="11">
@@ -884,39 +884,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>25.1</v>
+        <v>23.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2.7</v>
       </c>
       <c r="G11" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="H11" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I11" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="12">
@@ -927,39 +927,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="G12" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="H12" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="13">
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="H14" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
         <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="15">
@@ -1056,20 +1056,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.1</v>
+        <v>24.1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1079,16 +1079,16 @@
         <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>9.4</v>
+        <v>8.5</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="16">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1150,31 +1150,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="H17" t="n">
-        <v>9.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="18">
@@ -1185,11 +1185,11 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.9</v>
+        <v>24.9</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1198,26 +1198,26 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G18" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="H18" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="19">
@@ -1228,39 +1228,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.9</v>
+        <v>23.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="H19" t="n">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K19" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="20">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1404,16 +1404,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1423,7 +1423,7 @@
         <v>6.6</v>
       </c>
       <c r="H23" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="I23" t="n">
         <v>1.9</v>
@@ -1432,7 +1432,7 @@
         <v>0.5</v>
       </c>
       <c r="K23" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1486,39 +1486,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25.9</v>
+        <v>24.5</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="G25" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="H25" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="I25" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K25" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="26">
@@ -1529,39 +1529,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.5</v>
+        <v>24.9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G26" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
       <c r="H26" t="n">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K26" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="27">
@@ -1615,39 +1615,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.9</v>
+        <v>26.6</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>83.9</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="G28" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="H28" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="I28" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
         <v>0.5</v>
       </c>
       <c r="K28" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1701,36 +1701,36 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26.6</v>
+        <v>26.1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>83.9</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="G30" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="H30" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="I30" t="n">
         <v>2.2</v>
       </c>
       <c r="J30" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K30" t="n">
         <v>3</v>
@@ -1901,39 +1901,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.4</v>
+        <v>22.6</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H3" t="n">
         <v>4.9</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J3" t="n">
         <v>0.6</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="4">
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.9</v>
+        <v>21.2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J4" t="n">
         <v>0.6</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="5">
@@ -1987,39 +1987,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.7</v>
+        <v>21.9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J5" t="n">
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="6">
@@ -2073,39 +2073,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="G7" t="n">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="H7" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
         <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
@@ -2116,39 +2116,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="H8" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="I8" t="n">
         <v>1.5</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="9">
@@ -2159,39 +2159,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23.1</v>
+        <v>22.4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>7.5</v>
+        <v>6.1</v>
       </c>
       <c r="H9" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K9" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="10">
@@ -2202,39 +2202,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.7</v>
+        <v>23.7</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>83.9</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K10" t="n">
         <v>3.3</v>
-      </c>
-      <c r="G10" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="H10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2.9</v>
       </c>
     </row>
     <row r="11">
@@ -2245,39 +2245,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.7</v>
+        <v>22.9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="G11" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="H11" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="12">
@@ -2288,39 +2288,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.9</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="G12" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="H12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
         <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="13">
@@ -2331,39 +2331,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.8</v>
+        <v>22</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="G13" t="n">
-        <v>7.5</v>
+        <v>6.7</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
         <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="14">
@@ -2374,39 +2374,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G14" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="H14" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="15">
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.6</v>
+        <v>22.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="G15" t="n">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="H15" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="16">
@@ -2460,39 +2460,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="G16" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="H16" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
         <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="17">
@@ -2503,39 +2503,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>23.3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="G17" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="H17" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="18">
@@ -2636,16 +2636,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>83.9</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -2664,7 +2664,7 @@
         <v>0.3</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="21">
@@ -2675,39 +2675,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="H21" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="22">
@@ -2718,39 +2718,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>3.6</v>
       </c>
       <c r="G22" t="n">
-        <v>7.2</v>
+        <v>6.1</v>
       </c>
       <c r="H22" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="23">
@@ -2804,39 +2804,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.1</v>
+        <v>23.5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="G24" t="n">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="25">
@@ -2847,39 +2847,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.5</v>
+        <v>23.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="G25" t="n">
         <v>6.3</v>
       </c>
       <c r="H25" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K25" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="26">
@@ -2890,39 +2890,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.8</v>
+        <v>24.1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>3.1</v>
       </c>
       <c r="G26" t="n">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="H26" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K26" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="27">
@@ -2984,12 +2984,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -3002,7 +3002,7 @@
         <v>5.4</v>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0.7</v>
@@ -3023,26 +3023,26 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>2.9</v>
       </c>
       <c r="G29" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="H29" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I29" t="n">
         <v>2.2</v>
@@ -3051,7 +3051,7 @@
         <v>0.7</v>
       </c>
       <c r="K29" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="30">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3395,29 +3395,29 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G6" t="n">
         <v>8.5</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J6" t="n">
         <v>0.8</v>
@@ -3481,16 +3481,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.6</v>
+        <v>22.9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -3567,16 +3567,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -3586,7 +3586,7 @@
         <v>8.4</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I10" t="n">
         <v>1.6</v>
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G11" t="n">
-        <v>7.7</v>
+        <v>6.8</v>
       </c>
       <c r="H11" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K11" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12">
@@ -3653,7 +3653,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G13" t="n">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="14">
@@ -3735,39 +3735,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G14" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="H14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="15">
@@ -3829,25 +3829,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G16" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="H16" t="n">
         <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0.6</v>
@@ -3907,39 +3907,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.9</v>
+        <v>23.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="G18" t="n">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="H18" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -3950,39 +3950,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.8</v>
+        <v>22.9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="G19" t="n">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="H19" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="20">
@@ -4001,12 +4001,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -4016,7 +4016,7 @@
         <v>9</v>
       </c>
       <c r="H20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I20" t="n">
         <v>1.6</v>
@@ -4122,39 +4122,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.9</v>
+        <v>22</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="G23" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="24">
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22</v>
+        <v>23.9</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="G24" t="n">
-        <v>8.699999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K24" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="25">
@@ -4255,16 +4255,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.9</v>
+        <v>23.4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G27" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="H27" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>0.9</v>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="28">
@@ -4337,39 +4337,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.4</v>
+        <v>23.9</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="H28" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0.9</v>
       </c>
       <c r="K28" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -4593,14 +4593,14 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>70.1</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>2.4</v>
       </c>
       <c r="G2" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="H2" t="n">
         <v>4</v>
@@ -4627,23 +4627,23 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1.8</v>
       </c>
       <c r="G3" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="H3" t="n">
         <v>3.9</v>
@@ -4666,39 +4666,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.6</v>
+        <v>21.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="G4" t="n">
-        <v>8.699999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="I4" t="n">
         <v>1.5</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="5">
@@ -4709,39 +4709,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="G5" t="n">
-        <v>10.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="I5" t="n">
         <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="6">
@@ -4799,16 +4799,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.9</v>
+        <v>22.1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="G8" t="n">
-        <v>10.2</v>
+        <v>9.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="I8" t="n">
         <v>1.3</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -4881,39 +4881,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.7</v>
+        <v>22.9</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="G9" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I9" t="n">
         <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -4924,39 +4924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.1</v>
+        <v>21.7</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="G10" t="n">
-        <v>9.6</v>
+        <v>10.7</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="I10" t="n">
         <v>1.3</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K10" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="11">
@@ -4967,39 +4967,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.3</v>
+        <v>22.1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K11" t="n">
         <v>2.7</v>
-      </c>
-      <c r="G11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="H11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2.1</v>
       </c>
     </row>
     <row r="12">
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22</v>
+        <v>23.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="G12" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="K12" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="13">
@@ -5182,39 +5182,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>23.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="G16" t="n">
-        <v>9.4</v>
+        <v>10.2</v>
       </c>
       <c r="H16" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="17">
@@ -5225,39 +5225,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="G17" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="H17" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="I17" t="n">
         <v>1.5</v>
       </c>
       <c r="J17" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K17" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="18">
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="G18" t="n">
-        <v>10</v>
+        <v>10.9</v>
       </c>
       <c r="H18" t="n">
         <v>4.3</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="19">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -5319,31 +5319,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>70.8</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>2.2</v>
       </c>
       <c r="G19" t="n">
-        <v>10.9</v>
+        <v>10</v>
       </c>
       <c r="H19" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I19" t="n">
         <v>1.6</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K19" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="20">
@@ -5354,11 +5354,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.4</v>
+        <v>22.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -5367,26 +5367,26 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="F20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
         <v>2.4</v>
-      </c>
-      <c r="G20" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="H20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="21">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -5405,31 +5405,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="G21" t="n">
-        <v>9.9</v>
+        <v>10.4</v>
       </c>
       <c r="H21" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="I21" t="n">
         <v>1.4</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="K21" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="22">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G22" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="H22" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="I22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J22" t="n">
         <v>1.6</v>
       </c>
-      <c r="J22" t="n">
-        <v>1.2</v>
-      </c>
       <c r="K22" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="23">
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22.6</v>
+        <v>23.4</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="G23" t="n">
-        <v>9.5</v>
+        <v>9.9</v>
       </c>
       <c r="H23" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I23" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="24">
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.6</v>
+        <v>23.1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="G24" t="n">
-        <v>9.699999999999999</v>
+        <v>11.8</v>
       </c>
       <c r="H24" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="K24" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.1</v>
+        <v>24.2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>76.9</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G25" t="n">
-        <v>11.8</v>
+        <v>10.1</v>
       </c>
       <c r="H25" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="26">
@@ -5655,39 +5655,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.2</v>
+        <v>23.6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G27" t="n">
-        <v>10.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K27" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="28">
@@ -5941,39 +5941,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18.4</v>
+        <v>21.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J2" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="K2" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="3">
@@ -5984,36 +5984,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.5</v>
+        <v>19.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="G3" t="n">
-        <v>15.5</v>
+        <v>14.6</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J3" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="K3" t="n">
         <v>3.1</v>
@@ -6027,39 +6027,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19.5</v>
+        <v>18.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>0.7</v>
       </c>
       <c r="G4" t="n">
-        <v>14.6</v>
+        <v>13.7</v>
       </c>
       <c r="H4" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="I4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J4" t="n">
         <v>1.4</v>
       </c>
-      <c r="J4" t="n">
-        <v>2.3</v>
-      </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="5">
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19.1</v>
+        <v>18.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="G5" t="n">
-        <v>12.9</v>
+        <v>13.2</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="6">
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>18.1</v>
+        <v>19.1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>53.8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="G7" t="n">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
       <c r="H7" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1</v>
+        <v>1.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="8">
@@ -6207,12 +6207,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -6228,7 +6228,7 @@
         <v>1.4</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="K8" t="n">
         <v>2.9</v>
@@ -6246,11 +6246,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>56.8</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -6274,7 +6274,7 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="10">
@@ -6336,19 +6336,19 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>1.3</v>
       </c>
       <c r="G11" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="H11" t="n">
         <v>3.1</v>
@@ -6360,7 +6360,7 @@
         <v>1.9</v>
       </c>
       <c r="K11" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20.8</v>
+        <v>19.6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>67.6</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="G12" t="n">
-        <v>13.9</v>
+        <v>14.4</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J12" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="K12" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>19.6</v>
+        <v>22.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>69.8</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="G13" t="n">
-        <v>14.4</v>
+        <v>13.7</v>
       </c>
       <c r="H13" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="I13" t="n">
         <v>1.2</v>
       </c>
       <c r="J13" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="14">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.5</v>
+        <v>20.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>67.6</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1.4</v>
       </c>
       <c r="G14" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="15">
@@ -6590,23 +6590,23 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1.1</v>
       </c>
       <c r="G17" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="H17" t="n">
         <v>4.2</v>
@@ -6633,20 +6633,20 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G18" t="n">
         <v>14.2</v>
@@ -6658,10 +6658,10 @@
         <v>1.3</v>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="19">
@@ -6758,36 +6758,36 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21.3</v>
+        <v>23.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="G21" t="n">
-        <v>14.1</v>
+        <v>14.3</v>
       </c>
       <c r="H21" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="K21" t="n">
         <v>2.3</v>
@@ -6801,36 +6801,36 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.1</v>
+        <v>21.3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="H22" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="I22" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="K22" t="n">
         <v>2.3</v>
@@ -6844,11 +6844,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.7</v>
+        <v>21.6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -6857,26 +6857,26 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="G23" t="n">
-        <v>15.6</v>
+        <v>15.9</v>
       </c>
       <c r="H23" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J23" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="K23" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="24">
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>21.6</v>
+        <v>24.6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="G24" t="n">
-        <v>15.9</v>
+        <v>14.4</v>
       </c>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I24" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="K24" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="25">
@@ -6930,39 +6930,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.6</v>
+        <v>23.6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
         <v>1.5</v>
       </c>
-      <c r="G25" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H25" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J25" t="n">
-        <v>3</v>
-      </c>
       <c r="K25" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="26">
@@ -6981,28 +6981,28 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>1.3</v>
       </c>
       <c r="G26" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="H26" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="K26" t="n">
         <v>2.3</v>
@@ -7059,39 +7059,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>1.3</v>
       </c>
       <c r="G28" t="n">
-        <v>16.1</v>
+        <v>15.5</v>
       </c>
       <c r="H28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J28" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="K28" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="29">
@@ -7145,39 +7145,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24</v>
+        <v>24.6</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>68.9</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>1.3</v>
       </c>
       <c r="G30" t="n">
-        <v>15.4</v>
+        <v>16.1</v>
       </c>
       <c r="H30" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="K30" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="31">

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.6</v>
+        <v>21.9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -510,14 +510,14 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H2" t="n">
         <v>8.5</v>
@@ -544,11 +544,11 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -626,39 +626,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>23.2</v>
+        <v>22.3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="G5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -669,39 +669,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.3</v>
+        <v>22.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="H6" t="n">
-        <v>9.1</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="7">
@@ -712,39 +712,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.9</v>
+        <v>21.4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G7" t="n">
         <v>5.7</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
         <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
@@ -755,39 +755,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.3</v>
+        <v>23.4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>6</v>
+        <v>6.3</v>
       </c>
       <c r="H8" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9">
@@ -802,7 +802,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         <v>6.4</v>
       </c>
       <c r="H9" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
         <v>2.1</v>
@@ -830,7 +830,7 @@
         <v>0.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="10">
@@ -841,36 +841,36 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>25.1</v>
+        <v>27.1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="G10" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K10" t="n">
         <v>3.5</v>
@@ -927,39 +927,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.1</v>
+        <v>25.4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G12" t="n">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="H12" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J12" t="n">
         <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="13">
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>27.1</v>
+        <v>23.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G13" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="14">
@@ -1017,16 +1017,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24.1</v>
+        <v>24.4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H15" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K15" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="16">
@@ -1103,16 +1103,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.9</v>
+        <v>24.1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G17" t="n">
-        <v>5.6</v>
+        <v>6.1</v>
       </c>
       <c r="H17" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="18">
@@ -1185,39 +1185,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24.9</v>
+        <v>24.2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="19">
@@ -1228,39 +1228,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.8</v>
+        <v>24.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G19" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="H19" t="n">
-        <v>9.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I19" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="20">
@@ -1271,39 +1271,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="H20" t="n">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
         <v>0.6</v>
       </c>
       <c r="K20" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="21">
@@ -1314,39 +1314,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.7</v>
+        <v>23.8</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>6.3</v>
+        <v>5.3</v>
       </c>
       <c r="H21" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K21" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="22">
@@ -1357,39 +1357,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.2</v>
+        <v>23.9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="H22" t="n">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="I22" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="J22" t="n">
         <v>0.5</v>
       </c>
       <c r="K22" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -1400,39 +1400,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.8</v>
+        <v>24.3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="G23" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H23" t="n">
-        <v>7.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="24">
@@ -1443,39 +1443,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25.5</v>
+        <v>26</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="H24" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K24" t="n">
         <v>3</v>
-      </c>
-      <c r="G24" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3.3</v>
       </c>
     </row>
     <row r="25">
@@ -1486,39 +1486,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.5</v>
+        <v>25.7</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="H25" t="n">
-        <v>9</v>
+        <v>7.7</v>
       </c>
       <c r="I25" t="n">
         <v>1.9</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K25" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="26">
@@ -1529,39 +1529,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.9</v>
+        <v>24.4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>3.1</v>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H26" t="n">
-        <v>7.9</v>
+        <v>9.1</v>
       </c>
       <c r="I26" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K26" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="27">
@@ -1576,16 +1576,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>25.6</v>
+        <v>25.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1615,39 +1615,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>26.6</v>
+        <v>24.9</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>83.9</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="G28" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="H28" t="n">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="I28" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="J28" t="n">
         <v>0.5</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="29">
@@ -1658,39 +1658,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.5</v>
+        <v>26.5</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>83.9</t>
         </is>
       </c>
       <c r="F29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>9</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K29" t="n">
         <v>3</v>
-      </c>
-      <c r="G29" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H29" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2.8</v>
       </c>
     </row>
     <row r="30">
@@ -1701,39 +1701,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26.1</v>
+        <v>24.5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="H30" t="n">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="I30" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0.6</v>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="31">
@@ -1748,26 +1748,26 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.4</v>
+        <v>25.3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G31" t="n">
         <v>6.3</v>
       </c>
       <c r="H31" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I31" t="n">
         <v>2.4</v>
@@ -1862,16 +1862,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -1884,7 +1884,7 @@
         <v>5.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J2" t="n">
         <v>0.5</v>
@@ -1901,39 +1901,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.6</v>
+        <v>21.7</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H3" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I3" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J3" t="n">
         <v>0.6</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="4">
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.2</v>
+        <v>22.7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J4" t="n">
         <v>0.6</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="5">
@@ -1987,39 +1987,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.9</v>
+        <v>21.3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H5" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J5" t="n">
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="6">
@@ -2030,39 +2030,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.6</v>
+        <v>22.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>81.9</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="H6" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
@@ -2073,39 +2073,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23.1</v>
+        <v>22.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="G7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H7" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
@@ -2116,39 +2116,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23.1</v>
+        <v>22.4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>7.4</v>
+        <v>6.1</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9">
@@ -2159,39 +2159,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="G9" t="n">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="H9" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>0.6</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="10">
@@ -2210,16 +2210,16 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G10" t="n">
         <v>6.3</v>
@@ -2234,7 +2234,7 @@
         <v>0.8</v>
       </c>
       <c r="K10" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="11">
@@ -2245,39 +2245,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.9</v>
+        <v>23.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="H11" t="n">
         <v>5.4</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="12">
@@ -2288,39 +2288,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>83.9</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G12" t="n">
         <v>6.5</v>
       </c>
       <c r="H12" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13">
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -2360,7 +2360,7 @@
         <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K13" t="n">
         <v>2.1</v>
@@ -2374,39 +2374,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="G14" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="H14" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="I14" t="n">
         <v>1.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="15">
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>3.4</v>
       </c>
       <c r="G15" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="16">
@@ -2460,39 +2460,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.6</v>
+        <v>22.9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="G16" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="H16" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
         <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="17">
@@ -2503,15 +2503,15 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2520,22 +2520,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="H17" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K17" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="18">
@@ -2550,20 +2550,20 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="G18" t="n">
         <v>6.4</v>
@@ -2589,39 +2589,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="G19" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="H19" t="n">
-        <v>5.4</v>
+        <v>6.1</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K19" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="20">
@@ -2632,15 +2632,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.6</v>
+        <v>24.5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2652,19 +2652,19 @@
         <v>3.5</v>
       </c>
       <c r="G20" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="H20" t="n">
-        <v>6.1</v>
+        <v>4.8</v>
       </c>
       <c r="I20" t="n">
         <v>1.7</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="K20" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="21">
@@ -2675,39 +2675,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.3</v>
+        <v>23</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3.6</v>
       </c>
       <c r="G21" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="H21" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
         <v>0.7</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22">
@@ -2718,39 +2718,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>3.6</v>
       </c>
       <c r="G22" t="n">
-        <v>6.1</v>
+        <v>7.1</v>
       </c>
       <c r="H22" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K22" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23">
@@ -2761,39 +2761,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>25</v>
+        <v>23.6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="G23" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="H23" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K23" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="24">
@@ -2804,39 +2804,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.5</v>
+        <v>25</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="G24" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="H24" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="25">
@@ -2847,39 +2847,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.8</v>
+        <v>23.2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G25" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="H25" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
         <v>0.7</v>
       </c>
       <c r="K25" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="26">
@@ -2890,39 +2890,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.1</v>
+        <v>23.1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="G26" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K26" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="27">
@@ -2933,39 +2933,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.2</v>
+        <v>23.9</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G27" t="n">
-        <v>6.7</v>
+        <v>7</v>
       </c>
       <c r="H27" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="28">
@@ -2976,36 +2976,36 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.3</v>
+        <v>23.9</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="G28" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="H28" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K28" t="n">
         <v>2.6</v>
@@ -3109,16 +3109,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -3128,7 +3128,7 @@
         <v>7.2</v>
       </c>
       <c r="H31" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I31" t="n">
         <v>1.9</v>
@@ -3219,39 +3219,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22.3</v>
+        <v>22.6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K2" t="n">
         <v>2.6</v>
-      </c>
-      <c r="G2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3.1</v>
       </c>
     </row>
     <row r="3">
@@ -3262,39 +3262,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.9</v>
+        <v>22.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
         <v>3.1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="H3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="4">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3334,7 +3334,7 @@
         <v>1.2</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K4" t="n">
         <v>2.3</v>
@@ -3352,16 +3352,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -3380,7 +3380,7 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="6">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -3417,7 +3417,7 @@
         <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
         <v>0.8</v>
@@ -3438,11 +3438,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G7" t="n">
         <v>7.6</v>
@@ -3466,7 +3466,7 @@
         <v>0.8</v>
       </c>
       <c r="K7" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="8">
@@ -3477,39 +3477,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.9</v>
+        <v>21</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="G8" t="n">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="H8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="9">
@@ -3520,36 +3520,36 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.7</v>
+        <v>23.2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="G9" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="H9" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I9" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="K9" t="n">
         <v>2.8</v>
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21</v>
+        <v>22.6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>2.6</v>
       </c>
       <c r="G10" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="H10" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K10" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="11">
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.5</v>
+        <v>20.7</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2.7</v>
       </c>
       <c r="G11" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="H11" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="12">
@@ -3649,39 +3649,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>2.7</v>
       </c>
       <c r="G12" t="n">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K12" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.6</v>
+        <v>21.7</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G13" t="n">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="H13" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I13" t="n">
         <v>1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="14">
@@ -3739,11 +3739,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3758,7 +3758,7 @@
         <v>7.2</v>
       </c>
       <c r="H14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I14" t="n">
         <v>1.6</v>
@@ -3782,29 +3782,29 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G15" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="H15" t="n">
         <v>4.7</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0.7</v>
@@ -3821,39 +3821,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.4</v>
+        <v>22.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="G16" t="n">
         <v>6.9</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="17">
@@ -3864,39 +3864,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>82.1</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G17" t="n">
         <v>6.9</v>
       </c>
       <c r="H17" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="18">
@@ -3907,39 +3907,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.8</v>
+        <v>22.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="G18" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="H18" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="19">
@@ -3954,23 +3954,23 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>2.8</v>
       </c>
       <c r="G19" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H19" t="n">
         <v>4.2</v>
@@ -3993,39 +3993,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.8</v>
+        <v>23.9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="G20" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="H20" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K20" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="21">
@@ -4036,33 +4036,33 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.4</v>
+        <v>22.8</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G21" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="H21" t="n">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
         <v>0.8</v>
@@ -4079,30 +4079,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.9</v>
+        <v>23.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>81.7</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G22" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I22" t="n">
         <v>1.7</v>
@@ -4111,7 +4111,7 @@
         <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="23">
@@ -4122,39 +4122,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22</v>
+        <v>23.4</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="G23" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="I23" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K23" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="24">
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="H24" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>0.8</v>
       </c>
       <c r="K24" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -4208,39 +4208,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.8</v>
+        <v>22</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="G25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="26">
@@ -4251,39 +4251,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>26.3</v>
+        <v>23.9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="G26" t="n">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K26" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="27">
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.4</v>
+        <v>26.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G27" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
       <c r="H27" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="28">
@@ -4337,39 +4337,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.9</v>
+        <v>23.4</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G28" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="H28" t="n">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
         <v>0.9</v>
       </c>
       <c r="K28" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="29">
@@ -4384,16 +4384,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -4406,7 +4406,7 @@
         <v>4.5</v>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0.8</v>
@@ -4427,23 +4427,23 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>3.1</v>
       </c>
       <c r="G30" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="H30" t="n">
         <v>4.8</v>
@@ -4470,23 +4470,23 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>3.3</v>
       </c>
       <c r="G31" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="H31" t="n">
         <v>4.7</v>
@@ -4588,12 +4588,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>70.1</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -4606,13 +4606,13 @@
         <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J2" t="n">
         <v>0.8</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="3">
@@ -4627,23 +4627,23 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1.8</v>
       </c>
       <c r="G3" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="H3" t="n">
         <v>3.9</v>
@@ -4655,7 +4655,7 @@
         <v>1.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -4666,11 +4666,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4679,26 +4679,26 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="G4" t="n">
-        <v>10.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="I4" t="n">
         <v>1.5</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="5">
@@ -4709,39 +4709,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="G5" t="n">
-        <v>8.800000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="I5" t="n">
         <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -4756,23 +4756,23 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>22.3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="H6" t="n">
         <v>4.3</v>
@@ -4799,7 +4799,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4808,26 +4808,26 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="H7" t="n">
         <v>3.8</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J7" t="n">
         <v>1.2</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="8">
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.1</v>
+        <v>22.9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="G8" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="H8" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="I8" t="n">
         <v>1.3</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="K8" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9">
@@ -4881,39 +4881,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.9</v>
+        <v>22.2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="G9" t="n">
-        <v>10.3</v>
+        <v>9.6</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="I9" t="n">
         <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="10">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -4971,11 +4971,11 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4987,7 +4987,7 @@
         <v>2.2</v>
       </c>
       <c r="G11" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="H11" t="n">
         <v>4</v>
@@ -4999,7 +4999,7 @@
         <v>1.2</v>
       </c>
       <c r="K11" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="12">
@@ -5014,23 +5014,23 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>2.7</v>
       </c>
       <c r="G12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H12" t="n">
         <v>3.4</v>
@@ -5100,35 +5100,35 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>2.3</v>
       </c>
       <c r="G14" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="H14" t="n">
         <v>4.1</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="15">
@@ -5143,23 +5143,23 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="H15" t="n">
         <v>4</v>
@@ -5182,39 +5182,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.6</v>
+        <v>23</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>2.2</v>
       </c>
       <c r="G16" t="n">
-        <v>10.2</v>
+        <v>10.9</v>
       </c>
       <c r="H16" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="17">
@@ -5225,36 +5225,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="G17" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="H17" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="I17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J17" t="n">
         <v>1.5</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.2</v>
       </c>
       <c r="K17" t="n">
         <v>2.7</v>
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.1</v>
+        <v>22.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="G18" t="n">
-        <v>10.9</v>
+        <v>9.4</v>
       </c>
       <c r="H18" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
       </c>
       <c r="K18" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="19">
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.1</v>
+        <v>23.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="G19" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="H19" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>1.2</v>
       </c>
       <c r="K19" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="20">
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.6</v>
+        <v>23.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="G20" t="n">
-        <v>9.4</v>
+        <v>10.2</v>
       </c>
       <c r="H20" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="K20" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="21">
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.4</v>
+        <v>24.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G21" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="H21" t="n">
         <v>3.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="22">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.6</v>
+        <v>23.3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G22" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="K22" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="23">
@@ -5487,23 +5487,23 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.4</v>
+        <v>23.7</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>2.1</v>
       </c>
       <c r="G23" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="H23" t="n">
         <v>4.4</v>
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.1</v>
+        <v>22.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G24" t="n">
-        <v>11.8</v>
+        <v>11.4</v>
       </c>
       <c r="H24" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="25">
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.2</v>
+        <v>23.1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>76.9</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G25" t="n">
-        <v>10.1</v>
+        <v>11.7</v>
       </c>
       <c r="H25" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K25" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -5612,39 +5612,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="G26" t="n">
-        <v>11.4</v>
+        <v>9.5</v>
       </c>
       <c r="H26" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="K26" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="27">
@@ -5675,13 +5675,13 @@
         <v>2.5</v>
       </c>
       <c r="G27" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="H27" t="n">
         <v>4.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>1.1</v>
@@ -5702,11 +5702,11 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -5718,16 +5718,16 @@
         <v>2.7</v>
       </c>
       <c r="G28" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="H28" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I28" t="n">
         <v>1.9</v>
       </c>
       <c r="J28" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K28" t="n">
         <v>2.6</v>
@@ -5788,11 +5788,11 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -5804,7 +5804,7 @@
         <v>2.9</v>
       </c>
       <c r="G30" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="H30" t="n">
         <v>5.4</v>
@@ -5831,7 +5831,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         <v>4.6</v>
       </c>
       <c r="I31" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>1.1</v>
@@ -5945,7 +5945,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -5954,17 +5954,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G2" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I2" t="n">
         <v>1.3</v>
@@ -5988,16 +5988,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -6007,7 +6007,7 @@
         <v>14.6</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I3" t="n">
         <v>1.4</v>
@@ -6016,7 +6016,7 @@
         <v>2.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18.1</v>
+        <v>19.5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="F5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I5" t="n">
         <v>1.2</v>
       </c>
-      <c r="G5" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.7</v>
-      </c>
       <c r="J5" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="6">
@@ -6113,39 +6113,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.5</v>
+        <v>18.1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1.2</v>
       </c>
       <c r="G6" t="n">
-        <v>14.5</v>
+        <v>13.2</v>
       </c>
       <c r="H6" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="7">
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19.1</v>
+        <v>20.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="G7" t="n">
-        <v>12.9</v>
+        <v>14.6</v>
       </c>
       <c r="H7" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="I7" t="n">
         <v>1.3</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="K7" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
@@ -6207,7 +6207,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -6219,10 +6219,10 @@
         <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I8" t="n">
         <v>1.4</v>
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.8</v>
+        <v>19.1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>53.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>13</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I9" t="n">
         <v>1.4</v>
       </c>
-      <c r="G9" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="H9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>1.3</v>
       </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
       <c r="K9" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="10">
@@ -6285,39 +6285,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19.6</v>
+        <v>21.8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1.4</v>
       </c>
       <c r="G10" t="n">
-        <v>13.7</v>
+        <v>14.8</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="11">
@@ -6328,39 +6328,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18.9</v>
+        <v>19.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="G11" t="n">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
         <v>1.9</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19.6</v>
+        <v>20.8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="G12" t="n">
-        <v>14.4</v>
+        <v>13.9</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="K12" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.5</v>
+        <v>18.7</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>69.8</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G13" t="n">
-        <v>13.7</v>
+        <v>14.1</v>
       </c>
       <c r="H13" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="K13" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20.8</v>
+        <v>22.4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>54.7</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>67.6</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1.4</v>
       </c>
       <c r="G14" t="n">
-        <v>13.9</v>
+        <v>13.6</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K14" t="n">
         <v>2.1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="15">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.9</v>
+        <v>20.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G15" t="n">
-        <v>13.5</v>
+        <v>15.4</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I15" t="n">
         <v>1.2</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="16">
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20.7</v>
+        <v>21.8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="G16" t="n">
-        <v>15.5</v>
+        <v>13.6</v>
       </c>
       <c r="H16" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I16" t="n">
         <v>1.2</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="17">
@@ -6590,7 +6590,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="G17" t="n">
-        <v>12.5</v>
+        <v>12.3</v>
       </c>
       <c r="H17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I17" t="n">
         <v>1.4</v>
@@ -6637,19 +6637,19 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1.3</v>
       </c>
       <c r="G18" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="H18" t="n">
         <v>4.6</v>
@@ -6661,7 +6661,7 @@
         <v>1.9</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="19">
@@ -6676,11 +6676,11 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -6692,10 +6692,10 @@
         <v>2.1</v>
       </c>
       <c r="G19" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="H19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
         <v>1.4</v>
@@ -6715,39 +6715,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21.9</v>
+        <v>22.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="F20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G20" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I20" t="n">
         <v>1.4</v>
       </c>
-      <c r="G20" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="H20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1.8</v>
-      </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="K20" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="21">
@@ -6758,39 +6758,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.1</v>
+        <v>21.9</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>57.6</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="G21" t="n">
-        <v>14.3</v>
+        <v>14.8</v>
       </c>
       <c r="H21" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="22">
@@ -6801,39 +6801,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="G22" t="n">
-        <v>14.1</v>
+        <v>15.9</v>
       </c>
       <c r="H22" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -6844,39 +6844,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21.6</v>
+        <v>24.6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="G23" t="n">
-        <v>15.9</v>
+        <v>14.4</v>
       </c>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="24">
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.6</v>
+        <v>21.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="G24" t="n">
-        <v>14.4</v>
+        <v>14</v>
       </c>
       <c r="H24" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="I24" t="n">
         <v>1.6</v>
       </c>
       <c r="J24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="25">
@@ -6934,23 +6934,23 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="H25" t="n">
         <v>4.4</v>
@@ -6959,10 +6959,10 @@
         <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="K25" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="26">
@@ -6981,12 +6981,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>53.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -7002,7 +7002,7 @@
         <v>1.7</v>
       </c>
       <c r="J26" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="K26" t="n">
         <v>2.3</v>
@@ -7020,20 +7020,20 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>68.8</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="G27" t="n">
         <v>14.4</v>
@@ -7048,7 +7048,7 @@
         <v>2.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="28">
@@ -7106,23 +7106,23 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>73.6</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G29" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="H29" t="n">
         <v>4.3</v>
@@ -7149,16 +7149,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -7192,16 +7192,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.6</v>
+        <v>25.4</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>59.7</t>
+          <t>59.6</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>68.2</t>
+          <t>68.4</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -7220,7 +7220,7 @@
         <v>2.3</v>
       </c>
       <c r="K31" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
   </sheetData>

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -606,7 +606,7 @@
         <v>6.5</v>
       </c>
       <c r="H4" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="I4" t="n">
         <v>1.8</v>
@@ -669,39 +669,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.9</v>
+        <v>21.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G6" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="7">
@@ -712,39 +712,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.4</v>
+        <v>22.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G7" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="8">
@@ -884,39 +884,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.2</v>
+        <v>24.5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="G11" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="H11" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="12">
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="H13" t="n">
-        <v>9.5</v>
+        <v>8.6</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="14">
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24.5</v>
+        <v>23.5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="G14" t="n">
-        <v>6.7</v>
+        <v>5.4</v>
       </c>
       <c r="H14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="15">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24.4</v>
+        <v>23.3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="16">
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.5</v>
+        <v>24.2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="17">
@@ -1142,36 +1142,36 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.1</v>
+        <v>24.4</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G17" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K17" t="n">
         <v>3.4</v>
@@ -1185,39 +1185,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G18" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="H18" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
         <v>0.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="19">
@@ -1228,39 +1228,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.8</v>
+        <v>23.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="H19" t="n">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K19" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="20">
@@ -1271,39 +1271,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.1</v>
+        <v>24.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G20" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="H20" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="I20" t="n">
         <v>1.9</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="21">
@@ -1314,39 +1314,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.8</v>
+        <v>24.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="H21" t="n">
-        <v>9.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I21" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K21" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="22">
@@ -1400,39 +1400,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.3</v>
+        <v>26</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="G23" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="H23" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I23" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
         <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1443,39 +1443,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26</v>
+        <v>24.3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="G24" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H24" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J24" t="n">
         <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="25">
@@ -1529,39 +1529,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="H26" t="n">
-        <v>9.1</v>
+        <v>7.9</v>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K26" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="27">
@@ -1572,39 +1572,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>25.3</v>
+        <v>24.4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>3.1</v>
       </c>
       <c r="G27" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="H27" t="n">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="I27" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
         <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="28">
@@ -1615,39 +1615,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.9</v>
+        <v>26.2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="G28" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="H28" t="n">
-        <v>7.9</v>
+        <v>8.9</v>
       </c>
       <c r="I28" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0.5</v>
       </c>
       <c r="K28" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1658,36 +1658,36 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.5</v>
+        <v>25.3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>83.9</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="G29" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="H29" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="K29" t="n">
         <v>3</v>
@@ -1748,26 +1748,26 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.3</v>
+        <v>25.7</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G31" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I31" t="n">
         <v>2.4</v>
@@ -1776,7 +1776,7 @@
         <v>0.6</v>
       </c>
       <c r="K31" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
   </sheetData>
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.7</v>
+        <v>21.3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H4" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J4" t="n">
         <v>0.6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="5">
@@ -1987,39 +1987,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.3</v>
+        <v>22.7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="6">
@@ -2073,39 +2073,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="G7" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
@@ -2116,39 +2116,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.4</v>
+        <v>22.8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G8" t="n">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="H8" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="9">
@@ -2159,39 +2159,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23.1</v>
+        <v>22.4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="H9" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J9" t="n">
         <v>0.6</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="10">
@@ -2245,39 +2245,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.6</v>
+        <v>21.8</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G11" t="n">
         <v>6.7</v>
       </c>
       <c r="H11" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="I11" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K11" t="n">
-        <v>3.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="12">
@@ -2331,39 +2331,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.8</v>
+        <v>23.1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="G13" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="H13" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="14">
@@ -2374,39 +2374,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="G14" t="n">
         <v>6.3</v>
       </c>
       <c r="H14" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I14" t="n">
         <v>1.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="15">
@@ -2460,39 +2460,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.9</v>
+        <v>23.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="H16" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J16" t="n">
         <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="17">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2511,31 +2511,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="G17" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H17" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K17" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="18">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2554,31 +2554,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="G18" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H18" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="19">
@@ -2632,36 +2632,36 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.5</v>
+        <v>22.9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G20" t="n">
-        <v>6.1</v>
+        <v>7.4</v>
       </c>
       <c r="H20" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K20" t="n">
         <v>2.4</v>
@@ -2675,36 +2675,36 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23</v>
+        <v>24.5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G21" t="n">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
       <c r="H21" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K21" t="n">
         <v>2.4</v>
@@ -2769,19 +2769,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>3.1</v>
       </c>
       <c r="G23" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H23" t="n">
         <v>5.3</v>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2941,31 +2941,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="28">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2984,31 +2984,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="G28" t="n">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="H28" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
         <v>0.6</v>
       </c>
       <c r="K28" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="29">
@@ -3066,16 +3066,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -3085,7 +3085,7 @@
         <v>6.7</v>
       </c>
       <c r="H30" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="I30" t="n">
         <v>1.8</v>
@@ -3399,19 +3399,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="H6" t="n">
         <v>4.5</v>
@@ -3420,7 +3420,7 @@
         <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K6" t="n">
         <v>3.1</v>
@@ -3520,39 +3520,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23.2</v>
+        <v>22.6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="H9" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I9" t="n">
         <v>1.7</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="10">
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.6</v>
+        <v>20.7</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G10" t="n">
         <v>7.8</v>
       </c>
       <c r="H10" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="11">
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20.7</v>
+        <v>23.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="G11" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I11" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="K11" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="12">
@@ -3782,11 +3782,11 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -4122,39 +4122,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.4</v>
+        <v>22.2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G23" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="H23" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="24">
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.7</v>
+        <v>23.4</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G24" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="H24" t="n">
         <v>5.5</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
         <v>0.8</v>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="25">
@@ -4208,39 +4208,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22</v>
+        <v>23.6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>8.699999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="H25" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K25" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="26">
@@ -4337,39 +4337,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.4</v>
+        <v>24.3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>7.5</v>
+        <v>8.9</v>
       </c>
       <c r="H28" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K28" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="29">
@@ -4380,39 +4380,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.3</v>
+        <v>23.4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G29" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K29" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="30">
@@ -4584,29 +4584,29 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="H2" t="n">
         <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J2" t="n">
         <v>0.8</v>
@@ -4666,11 +4666,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.7</v>
+        <v>21.6</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -4679,26 +4679,26 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="G4" t="n">
-        <v>8.800000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="I4" t="n">
         <v>1.5</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -4709,11 +4709,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.6</v>
+        <v>20.7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -4722,26 +4722,26 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="G5" t="n">
-        <v>10.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="I5" t="n">
         <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="6">
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.9</v>
+        <v>21.9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>48.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="G8" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K8" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -4881,39 +4881,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.2</v>
+        <v>21.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="G9" t="n">
-        <v>9.6</v>
+        <v>10.7</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="I9" t="n">
         <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="10">
@@ -4924,39 +4924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.7</v>
+        <v>22.2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="G10" t="n">
-        <v>10.7</v>
+        <v>9.6</v>
       </c>
       <c r="H10" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="I10" t="n">
         <v>1.3</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11">
@@ -4967,39 +4967,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.9</v>
+        <v>22.9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="G11" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K11" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12">
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.4</v>
+        <v>21.5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="G12" t="n">
-        <v>9.699999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="H12" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="K12" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="13">
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.5</v>
+        <v>22.3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G13" t="n">
-        <v>10.5</v>
+        <v>10.8</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I13" t="n">
         <v>1.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="K13" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="14">
@@ -5096,33 +5096,33 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.4</v>
+        <v>23.4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="G14" t="n">
-        <v>10.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J14" t="n">
         <v>1.1</v>
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.6</v>
+        <v>23.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="G18" t="n">
-        <v>9.4</v>
+        <v>10.2</v>
       </c>
       <c r="H18" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="19">
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.6</v>
+        <v>22.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="G19" t="n">
-        <v>10.1</v>
+        <v>9.4</v>
       </c>
       <c r="H19" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="20">
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.6</v>
+        <v>24.1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="G20" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="H20" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="21">
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.1</v>
+        <v>22.8</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G21" t="n">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="H21" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="K21" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="G22" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="H22" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
         <v>1.2</v>
       </c>
       <c r="K22" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.7</v>
+        <v>23.3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="G23" t="n">
         <v>10</v>
       </c>
       <c r="H23" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K23" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="24">
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="G24" t="n">
-        <v>11.4</v>
+        <v>11.7</v>
       </c>
       <c r="H24" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="K24" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.1</v>
+        <v>23.7</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>10</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
         <v>2.3</v>
-      </c>
-      <c r="G25" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="H25" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -5635,7 +5635,7 @@
         <v>9.5</v>
       </c>
       <c r="H26" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I26" t="n">
         <v>1.8</v>
@@ -5792,22 +5792,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>2.9</v>
       </c>
       <c r="G30" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="H30" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I30" t="n">
         <v>1.7</v>
@@ -5816,7 +5816,7 @@
         <v>1.6</v>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="31">
@@ -5984,39 +5984,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.4</v>
+        <v>18.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>0.7</v>
       </c>
       <c r="G3" t="n">
-        <v>14.6</v>
+        <v>13.7</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="I3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J3" t="n">
         <v>1.4</v>
       </c>
-      <c r="J3" t="n">
-        <v>2.3</v>
-      </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="4">
@@ -6027,39 +6027,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18.4</v>
+        <v>19.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>0.7</v>
       </c>
       <c r="G4" t="n">
-        <v>13.7</v>
+        <v>14.6</v>
       </c>
       <c r="H4" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="K4" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>19.5</v>
+        <v>18.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G5" t="n">
-        <v>13.6</v>
+        <v>13.2</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="6">
@@ -6113,36 +6113,36 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1.2</v>
       </c>
       <c r="G6" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K6" t="n">
         <v>3.2</v>
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.8</v>
+        <v>19.5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I7" t="n">
         <v>1.2</v>
       </c>
-      <c r="G7" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.3</v>
-      </c>
       <c r="J7" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="8">
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.2</v>
+        <v>21.8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G8" t="n">
-        <v>14.5</v>
+        <v>14.8</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J8" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="9">
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19.1</v>
+        <v>19.6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>53.5</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>14.4</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="10">
@@ -6285,39 +6285,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.8</v>
+        <v>19.2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1.4</v>
       </c>
       <c r="G10" t="n">
-        <v>14.8</v>
+        <v>14.5</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="K10" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="11">
@@ -6328,33 +6328,33 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19.6</v>
+        <v>18.7</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="G11" t="n">
-        <v>14.4</v>
+        <v>14.1</v>
       </c>
       <c r="H11" t="n">
         <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J11" t="n">
         <v>1.9</v>
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>20.8</v>
+        <v>19.2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G12" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I12" t="n">
         <v>1.4</v>
       </c>
-      <c r="G12" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>1.3</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>2.2</v>
-      </c>
-      <c r="K12" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>18.7</v>
+        <v>20.8</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I13" t="n">
         <v>1.3</v>
       </c>
-      <c r="G13" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1.1</v>
-      </c>
       <c r="J13" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="14">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.4</v>
+        <v>20.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I14" t="n">
         <v>1.4</v>
       </c>
-      <c r="G14" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="H14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.2</v>
-      </c>
       <c r="J14" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="15">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20.6</v>
+        <v>22.4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="G15" t="n">
-        <v>15.4</v>
+        <v>13.6</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="I15" t="n">
         <v>1.2</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="16">
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>21.8</v>
+        <v>20.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G16" t="n">
-        <v>13.6</v>
+        <v>15.4</v>
       </c>
       <c r="H16" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I16" t="n">
         <v>1.2</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="17">
@@ -6586,33 +6586,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G17" t="n">
-        <v>12.3</v>
+        <v>14</v>
       </c>
       <c r="H17" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
         <v>1.9</v>
@@ -6629,39 +6629,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21</v>
+        <v>21.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="G18" t="n">
-        <v>14</v>
+        <v>13.6</v>
       </c>
       <c r="H18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="19">
@@ -6715,39 +6715,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.8</v>
+        <v>21.9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="G20" t="n">
-        <v>14.2</v>
+        <v>14.8</v>
       </c>
       <c r="H20" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J20" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="21">
@@ -6758,39 +6758,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21.9</v>
+        <v>21.5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="G21" t="n">
-        <v>14.8</v>
+        <v>15.9</v>
       </c>
       <c r="H21" t="n">
         <v>3.9</v>
       </c>
       <c r="I21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J21" t="n">
         <v>1.8</v>
       </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
       <c r="K21" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="22">
@@ -6801,39 +6801,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21.5</v>
+        <v>21.2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>58.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="G22" t="n">
-        <v>15.9</v>
+        <v>14</v>
       </c>
       <c r="H22" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="23">
@@ -6844,39 +6844,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.6</v>
+        <v>23</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>70.9</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G23" t="n">
         <v>14.4</v>
       </c>
       <c r="H23" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="K23" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="24">
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>21.2</v>
+        <v>24.6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="G24" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="H24" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K24" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="25">
@@ -7016,39 +7016,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.3</v>
+        <v>24</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="G27" t="n">
-        <v>14.4</v>
+        <v>15.5</v>
       </c>
       <c r="H27" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="28">
@@ -7059,39 +7059,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24</v>
+        <v>23.3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="G28" t="n">
-        <v>15.5</v>
+        <v>14.4</v>
       </c>
       <c r="H28" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I28" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="K28" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="29">

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -669,39 +669,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.4</v>
+        <v>22.9</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="7">
@@ -712,39 +712,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.9</v>
+        <v>21.4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
@@ -841,39 +841,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>27.1</v>
+        <v>23.1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>42.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="H10" t="n">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="11">
@@ -884,39 +884,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24.5</v>
+        <v>27.1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="G11" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>8.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="I11" t="n">
         <v>1.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="12">
@@ -927,39 +927,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25.4</v>
+        <v>24.5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="G12" t="n">
         <v>6.7</v>
       </c>
       <c r="H12" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
         <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="13">
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.2</v>
+        <v>25.4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G13" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="H13" t="n">
         <v>8.6</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="14">
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G14" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="H14" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="I14" t="n">
         <v>2.1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="15">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="H15" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="I15" t="n">
         <v>2.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="16">
@@ -1099,36 +1099,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24.2</v>
+        <v>23.7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G16" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="H16" t="n">
-        <v>8.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K16" t="n">
         <v>3.6</v>
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.4</v>
+        <v>24.2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K17" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="18">
@@ -1185,36 +1185,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24.1</v>
+        <v>24.4</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G18" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H18" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K18" t="n">
         <v>3.4</v>
@@ -1228,39 +1228,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.8</v>
+        <v>24.1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G19" t="n">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="H19" t="n">
-        <v>9.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="I19" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="20">
@@ -1400,39 +1400,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>26</v>
+        <v>24.3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="G23" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H23" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J23" t="n">
         <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="24">
@@ -1443,39 +1443,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.3</v>
+        <v>26</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="G24" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="H24" t="n">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="I24" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
         <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.3</v>
+        <v>22.7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I4" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J4" t="n">
         <v>0.6</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="5">
@@ -1987,39 +1987,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.7</v>
+        <v>21.3</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F5" t="n">
         <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="J5" t="n">
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="6">
@@ -2073,39 +2073,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23.1</v>
+        <v>22.4</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="H7" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J7" t="n">
         <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="8">
@@ -2159,39 +2159,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.4</v>
+        <v>23.1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="G9" t="n">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="H9" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>0.6</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="10">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2296,31 +2296,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G12" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="H12" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="13">
@@ -2331,39 +2331,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G13" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="H13" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="14">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2382,19 +2382,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="G14" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="H14" t="n">
         <v>5.2</v>
@@ -2406,7 +2406,7 @@
         <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="15">
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="G15" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="H15" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I15" t="n">
         <v>1.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="16">
@@ -2593,23 +2593,23 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>3.5</v>
       </c>
       <c r="G19" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H19" t="n">
         <v>6.1</v>
@@ -2675,39 +2675,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G21" t="n">
-        <v>6.1</v>
+        <v>7.1</v>
       </c>
       <c r="H21" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="22">
@@ -2718,39 +2718,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G22" t="n">
-        <v>7.1</v>
+        <v>6.1</v>
       </c>
       <c r="H22" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="23">
@@ -2761,39 +2761,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.6</v>
+        <v>25</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="H23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K23" t="n">
         <v>3.1</v>
-      </c>
-      <c r="G23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="I23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K23" t="n">
-        <v>3.2</v>
       </c>
     </row>
     <row r="24">
@@ -2804,39 +2804,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25</v>
+        <v>23.6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="G24" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="H24" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K24" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="25">
@@ -2933,7 +2933,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -2941,31 +2941,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="G27" t="n">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="H27" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
         <v>0.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="28">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -2984,31 +2984,31 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="G28" t="n">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0.6</v>
       </c>
       <c r="K28" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="29">
@@ -3027,19 +3027,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.9</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>2.9</v>
       </c>
       <c r="G29" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="H29" t="n">
         <v>5.5</v>
@@ -3477,39 +3477,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G8" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="H8" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="I8" t="n">
         <v>1.6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="K8" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="9">
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20.7</v>
+        <v>21.2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G10" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="H10" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I10" t="n">
         <v>1.6</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="K10" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="11">
@@ -3649,39 +3649,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.4</v>
+        <v>21.7</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>2.7</v>
       </c>
       <c r="G12" t="n">
-        <v>6.7</v>
+        <v>7.4</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="13">
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>2.7</v>
       </c>
       <c r="G13" t="n">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="H13" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K13" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="14">
@@ -4208,39 +4208,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.6</v>
+        <v>26.3</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G25" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="H25" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K25" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="26">
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26.3</v>
+        <v>23.6</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K27" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="28">
@@ -4881,39 +4881,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.7</v>
+        <v>22.2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="G9" t="n">
-        <v>10.7</v>
+        <v>9.6</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="I9" t="n">
         <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="10">
@@ -4924,39 +4924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.2</v>
+        <v>21.7</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.1</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="G10" t="n">
-        <v>9.6</v>
+        <v>10.7</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="I10" t="n">
         <v>1.3</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K10" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="11">
@@ -4967,39 +4967,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.9</v>
+        <v>21.5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="G11" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="H11" t="n">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="K11" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="12">
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21.5</v>
+        <v>22.9</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="G12" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="K12" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.3</v>
+        <v>23.4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="G13" t="n">
-        <v>10.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J13" t="n">
         <v>1.1</v>
       </c>
       <c r="K13" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="14">
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.4</v>
+        <v>22.3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="G14" t="n">
-        <v>9.699999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
         <v>1.1</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="15">
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.6</v>
+        <v>22.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="G18" t="n">
-        <v>10.2</v>
+        <v>9.4</v>
       </c>
       <c r="H18" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="K18" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="19">
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.6</v>
+        <v>23.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="G19" t="n">
-        <v>9.4</v>
+        <v>10.1</v>
       </c>
       <c r="H19" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="K19" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="20">
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.1</v>
+        <v>23.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="G20" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="H20" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K20" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="21">
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.8</v>
+        <v>24.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="G21" t="n">
-        <v>11.4</v>
+        <v>10</v>
       </c>
       <c r="H21" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="22">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.6</v>
+        <v>23.3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="G22" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
         <v>1.2</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="23">
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.3</v>
+        <v>22.8</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G23" t="n">
-        <v>10</v>
+        <v>11.4</v>
       </c>
       <c r="H23" t="n">
         <v>4.6</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="K23" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="24">
@@ -5984,39 +5984,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>18.4</v>
+        <v>19.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>0.7</v>
       </c>
       <c r="G3" t="n">
-        <v>13.7</v>
+        <v>14.6</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="K3" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -6027,39 +6027,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19.4</v>
+        <v>18.2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>0.7</v>
       </c>
       <c r="G4" t="n">
-        <v>14.6</v>
+        <v>13.7</v>
       </c>
       <c r="H4" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="I4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J4" t="n">
         <v>1.4</v>
       </c>
-      <c r="J4" t="n">
-        <v>2.3</v>
-      </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="5">
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.8</v>
+        <v>20.8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1.4</v>
       </c>
       <c r="G8" t="n">
-        <v>14.8</v>
+        <v>13.9</v>
       </c>
       <c r="H8" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="I8" t="n">
         <v>1.3</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="9">
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19.6</v>
+        <v>19.2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="G9" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K9" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="10">
@@ -6285,39 +6285,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>19.2</v>
+        <v>18.7</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G10" t="n">
-        <v>14.5</v>
+        <v>14.1</v>
       </c>
       <c r="H10" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="11">
@@ -6328,39 +6328,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18.7</v>
+        <v>21.8</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I11" t="n">
         <v>1.3</v>
       </c>
-      <c r="G11" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.1</v>
-      </c>
       <c r="J11" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="12">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19.2</v>
+        <v>19.6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="G12" t="n">
-        <v>13.2</v>
+        <v>14.4</v>
       </c>
       <c r="H12" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="K12" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>20.8</v>
+        <v>19.2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G13" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I13" t="n">
         <v>1.4</v>
       </c>
-      <c r="G13" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>1.3</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>2.2</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="14">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20.8</v>
+        <v>22.4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="F14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G14" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I14" t="n">
         <v>1.2</v>
       </c>
-      <c r="G14" t="n">
-        <v>12.3</v>
-      </c>
-      <c r="H14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.4</v>
-      </c>
       <c r="J14" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="15">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.4</v>
+        <v>20.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G15" t="n">
-        <v>13.6</v>
+        <v>15.4</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="I15" t="n">
         <v>1.2</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="K15" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="16">
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20.6</v>
+        <v>21</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G16" t="n">
-        <v>15.4</v>
+        <v>14</v>
       </c>
       <c r="H16" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="17">
@@ -6586,33 +6586,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>67.2</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G17" t="n">
-        <v>14</v>
+        <v>12.3</v>
       </c>
       <c r="H17" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J17" t="n">
         <v>1.9</v>
@@ -7016,39 +7016,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24</v>
+        <v>23.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="G27" t="n">
-        <v>15.5</v>
+        <v>14.4</v>
       </c>
       <c r="H27" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="28">
@@ -7059,39 +7059,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.3</v>
+        <v>24</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="G28" t="n">
-        <v>14.4</v>
+        <v>15.3</v>
       </c>
       <c r="H28" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I28" t="n">
         <v>1.6</v>
       </c>
       <c r="J28" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="K28" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="29">

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -497,39 +497,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.9</v>
+        <v>22.4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="H2" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J2" t="n">
         <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="3">
@@ -540,11 +540,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.1</v>
+        <v>21.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -553,26 +553,26 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>71.3</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="G3" t="n">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="H3" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J3" t="n">
         <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="4">
@@ -583,39 +583,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.3</v>
+        <v>22.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="H4" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J4" t="n">
         <v>0.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="5">
@@ -626,39 +626,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.3</v>
+        <v>22.7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>75.9</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="H5" t="n">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="6">
@@ -669,39 +669,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.9</v>
+        <v>22.2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K6" t="n">
         <v>3.1</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="H6" t="n">
-        <v>8</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.6</v>
       </c>
     </row>
     <row r="7">
@@ -759,26 +759,26 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I8" t="n">
         <v>1.8</v>
@@ -802,29 +802,29 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>84.1</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H9" t="n">
         <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
         <v>0.4</v>
@@ -927,39 +927,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>24.5</v>
+        <v>23.1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="G12" t="n">
-        <v>6.7</v>
+        <v>5.9</v>
       </c>
       <c r="H12" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J12" t="n">
         <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="13">
@@ -1013,39 +1013,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>23.3</v>
+        <v>24.5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>6.7</v>
       </c>
       <c r="H14" t="n">
-        <v>9.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
         <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="15">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.5</v>
+        <v>24.5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="G15" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="H15" t="n">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="16">
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.2</v>
+        <v>24.4</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H17" t="n">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="18">
@@ -1185,39 +1185,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24.4</v>
+        <v>24.2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="19">
@@ -1271,39 +1271,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.8</v>
+        <v>23.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="G20" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="H20" t="n">
-        <v>8.9</v>
+        <v>8</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J20" t="n">
         <v>0.5</v>
       </c>
       <c r="K20" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="21">
@@ -1361,11 +1361,11 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1389,7 +1389,7 @@
         <v>0.5</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23">
@@ -1447,16 +1447,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>26</v>
+        <v>25.7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1490,16 +1490,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1509,7 +1509,7 @@
         <v>5.8</v>
       </c>
       <c r="H25" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="I25" t="n">
         <v>1.9</v>
@@ -1529,39 +1529,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.8</v>
+        <v>24.4</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G26" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="H26" t="n">
-        <v>7.9</v>
+        <v>9.1</v>
       </c>
       <c r="I26" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K26" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="27">
@@ -1572,39 +1572,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.4</v>
+        <v>24.8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="H27" t="n">
-        <v>9.1</v>
+        <v>7.9</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K27" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="28">
@@ -1615,39 +1615,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>26.2</v>
+        <v>25.1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="G28" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H28" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="29">
@@ -1658,36 +1658,36 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>25.3</v>
+        <v>26.2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="G29" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H29" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K29" t="n">
         <v>3</v>
@@ -1901,39 +1901,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.7</v>
+        <v>21.3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H3" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J3" t="n">
         <v>0.6</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="4">
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.7</v>
+        <v>21.7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="H4" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="I4" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J4" t="n">
         <v>0.6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="5">
@@ -1987,39 +1987,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.3</v>
+        <v>22.4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="H5" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J5" t="n">
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="6">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2038,31 +2038,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="H6" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
         <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="7">
@@ -2073,39 +2073,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.4</v>
+        <v>22.8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G7" t="n">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="H7" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K7" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8">
@@ -2116,39 +2116,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="G8" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
@@ -2159,30 +2159,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="H9" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="I9" t="n">
         <v>1.5</v>
@@ -2191,7 +2191,7 @@
         <v>0.6</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="10">
@@ -2215,11 +2215,11 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G10" t="n">
         <v>6.3</v>
@@ -2234,7 +2234,7 @@
         <v>0.8</v>
       </c>
       <c r="K10" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="11">
@@ -2245,39 +2245,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.8</v>
+        <v>23.1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="G11" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="H11" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
         <v>0.7</v>
       </c>
       <c r="K11" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="12">
@@ -2288,39 +2288,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.9</v>
+        <v>23.6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="G12" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="H12" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
         <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="13">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2339,31 +2339,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G13" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H13" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="14">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2406,7 +2406,7 @@
         <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="15">
@@ -2417,36 +2417,36 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.1</v>
+        <v>23.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="H15" t="n">
         <v>5.4</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K15" t="n">
         <v>3.2</v>
@@ -2460,36 +2460,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.6</v>
+        <v>23.1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="G16" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="H16" t="n">
         <v>5.4</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K16" t="n">
         <v>3.2</v>
@@ -2503,30 +2503,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.6</v>
+        <v>21.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="G17" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="H17" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="I17" t="n">
         <v>1.8</v>
@@ -2535,7 +2535,7 @@
         <v>0.7</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="18">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2554,31 +2554,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="G18" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H18" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K18" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="19">
@@ -2589,39 +2589,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.7</v>
+        <v>24.3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>3.5</v>
       </c>
       <c r="G19" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="H19" t="n">
-        <v>6.1</v>
+        <v>4.7</v>
       </c>
       <c r="I19" t="n">
         <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="K19" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="20">
@@ -2675,39 +2675,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.4</v>
+        <v>23.7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G21" t="n">
-        <v>7.1</v>
+        <v>6.4</v>
       </c>
       <c r="H21" t="n">
-        <v>5.4</v>
+        <v>6.1</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="22">
@@ -2718,39 +2718,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G22" t="n">
-        <v>6.1</v>
+        <v>7.1</v>
       </c>
       <c r="H22" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K22" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="23">
@@ -2761,39 +2761,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>25</v>
+        <v>23.6</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="G23" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="H23" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K23" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="24">
@@ -2804,39 +2804,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.6</v>
+        <v>23.9</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>3.1</v>
       </c>
       <c r="G24" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="H24" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="25">
@@ -2847,39 +2847,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="G25" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="H25" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K25" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="26">
@@ -2890,39 +2890,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.1</v>
+        <v>25</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="G26" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="H26" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K26" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="27">
@@ -2933,39 +2933,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.9</v>
+        <v>23.2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="H27" t="n">
         <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="28">
@@ -2976,36 +2976,36 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.9</v>
+        <v>23.1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>3.6</v>
       </c>
       <c r="G28" t="n">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="H28" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K28" t="n">
         <v>2.6</v>
@@ -3113,12 +3113,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -3128,16 +3128,16 @@
         <v>7.2</v>
       </c>
       <c r="H31" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I31" t="n">
         <v>1.9</v>
       </c>
       <c r="J31" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K31" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
   </sheetData>
@@ -3219,39 +3219,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22.6</v>
+        <v>22.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
         <v>3</v>
-      </c>
-      <c r="G2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="3">
@@ -3262,39 +3262,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>75.1</t>
         </is>
       </c>
       <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K3" t="n">
         <v>2.6</v>
-      </c>
-      <c r="G3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3.1</v>
       </c>
     </row>
     <row r="4">
@@ -3434,39 +3434,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.6</v>
+        <v>23</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="G7" t="n">
         <v>7.6</v>
       </c>
       <c r="H7" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="I7" t="n">
         <v>1.6</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="8">
@@ -3481,11 +3481,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3500,16 +3500,16 @@
         <v>7.8</v>
       </c>
       <c r="H8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
         <v>1.6</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -3520,39 +3520,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.6</v>
+        <v>21.6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="H9" t="n">
-        <v>4.7</v>
+        <v>3.5</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K9" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="10">
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>2.6</v>
       </c>
       <c r="G10" t="n">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="H10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K10" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="11">
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.2</v>
+        <v>22.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="G11" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="H11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I11" t="n">
         <v>1.7</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="12">
@@ -3649,39 +3649,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>2.7</v>
       </c>
       <c r="G12" t="n">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K12" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -3692,39 +3692,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.4</v>
+        <v>22.8</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="14">
@@ -3735,39 +3735,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.8</v>
+        <v>21.2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G14" t="n">
-        <v>7.2</v>
+        <v>8.5</v>
       </c>
       <c r="H14" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I14" t="n">
         <v>1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="15">
@@ -3825,11 +3825,11 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3841,10 +3841,10 @@
         <v>2.5</v>
       </c>
       <c r="G16" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="H16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I16" t="n">
         <v>1.7</v>
@@ -3872,16 +3872,16 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G17" t="n">
         <v>6.9</v>
@@ -3907,39 +3907,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.8</v>
+        <v>23.9</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="G18" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="H18" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K18" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="19">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3958,31 +3958,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="G19" t="n">
-        <v>8.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="20">
@@ -3993,39 +3993,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.9</v>
+        <v>22.8</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="G20" t="n">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="K20" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="21">
@@ -4040,16 +4040,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -4087,22 +4087,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>8.800000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="H22" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="I22" t="n">
         <v>1.7</v>
@@ -4111,7 +4111,7 @@
         <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="23">
@@ -4122,36 +4122,36 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G23" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="H23" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="I23" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K23" t="n">
         <v>2.7</v>
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.4</v>
+        <v>22.2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G24" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="H24" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K24" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="25">
@@ -4208,39 +4208,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>26.3</v>
+        <v>23.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="G25" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="K25" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="26">
@@ -4251,39 +4251,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.9</v>
+        <v>26.3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="G26" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="H26" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="K26" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="27">
@@ -4294,39 +4294,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G27" t="n">
-        <v>7.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="I27" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J27" t="n">
         <v>0.8</v>
       </c>
       <c r="K27" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="28">
@@ -4337,39 +4337,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24.3</v>
+        <v>23.3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G28" t="n">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
       <c r="H28" t="n">
         <v>4.5</v>
       </c>
       <c r="I28" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K28" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="29">
@@ -4380,39 +4380,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>23.4</v>
+        <v>24.4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I29" t="n">
         <v>1.9</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K29" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="30">
@@ -4470,11 +4470,11 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4486,7 +4486,7 @@
         <v>3.3</v>
       </c>
       <c r="G31" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H31" t="n">
         <v>4.7</v>
@@ -4495,7 +4495,7 @@
         <v>2</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
@@ -4636,23 +4636,23 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1.8</v>
       </c>
       <c r="G3" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
         <v>1.6</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -4713,20 +4713,20 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="G5" t="n">
         <v>8.800000000000001</v>
@@ -4756,16 +4756,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -4775,10 +4775,10 @@
         <v>10.9</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
         <v>1.6</v>
@@ -4846,16 +4846,16 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>48.4</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G8" t="n">
         <v>10.1</v>
@@ -4867,10 +4867,10 @@
         <v>1.4</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K8" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="9">
@@ -4881,39 +4881,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.2</v>
+        <v>21.6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="G9" t="n">
-        <v>9.6</v>
+        <v>10.8</v>
       </c>
       <c r="H9" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="10">
@@ -4924,39 +4924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.7</v>
+        <v>22.1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>76.1</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="G10" t="n">
-        <v>10.7</v>
+        <v>9.6</v>
       </c>
       <c r="H10" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="I10" t="n">
         <v>1.3</v>
       </c>
       <c r="J10" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11">
@@ -5018,19 +5018,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>1.6</v>
       </c>
       <c r="G12" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="H12" t="n">
         <v>3.8</v>
@@ -5147,12 +5147,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -5171,7 +5171,7 @@
         <v>1.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="16">
@@ -5202,7 +5202,7 @@
         <v>2.2</v>
       </c>
       <c r="G16" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="H16" t="n">
         <v>4.3</v>
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.6</v>
+        <v>23.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="G18" t="n">
-        <v>9.4</v>
+        <v>10.1</v>
       </c>
       <c r="H18" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="K18" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="19">
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>23.6</v>
+        <v>22.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G19" t="n">
-        <v>10.1</v>
+        <v>11.3</v>
       </c>
       <c r="H19" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="I19" t="n">
         <v>1.5</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="K19" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="20">
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.6</v>
+        <v>22.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>52.9</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="G20" t="n">
-        <v>10.1</v>
+        <v>9.4</v>
       </c>
       <c r="H20" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="21">
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.1</v>
+        <v>23.5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="G21" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="H21" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K21" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="22">
@@ -5440,20 +5440,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.3</v>
+        <v>24.1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>52.7</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -5463,16 +5463,16 @@
         <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="I22" t="n">
         <v>1.6</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K22" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="23">
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>47.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.7</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="G23" t="n">
-        <v>11.4</v>
+        <v>11.7</v>
       </c>
       <c r="H23" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="K23" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>2.3</v>
       </c>
       <c r="G24" t="n">
-        <v>11.7</v>
+        <v>10</v>
       </c>
       <c r="H24" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
         <v>1.2</v>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="25">
@@ -5659,16 +5659,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>50.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -5745,16 +5745,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27.4</v>
+        <v>27.2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -5764,7 +5764,7 @@
         <v>10.7</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I29" t="n">
         <v>1.4</v>
@@ -5831,35 +5831,35 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.8</v>
+        <v>24.6</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>2</v>
       </c>
       <c r="G31" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="H31" t="n">
         <v>4.6</v>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J31" t="n">
         <v>1.1</v>
       </c>
       <c r="K31" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
   </sheetData>
@@ -5941,39 +5941,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.4</v>
+        <v>19.4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.1</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="G2" t="n">
-        <v>15.6</v>
+        <v>14.6</v>
       </c>
       <c r="H2" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -5984,36 +5984,36 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>19.4</v>
+        <v>21.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="G3" t="n">
-        <v>14.6</v>
+        <v>15.7</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -6083,7 +6083,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -6113,39 +6113,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20.8</v>
+        <v>19.5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>49.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I6" t="n">
         <v>1.2</v>
       </c>
-      <c r="G6" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.3</v>
-      </c>
       <c r="J6" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="7">
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19.5</v>
+        <v>20.7</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I7" t="n">
         <v>1.4</v>
       </c>
-      <c r="G7" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="H7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.2</v>
-      </c>
       <c r="J7" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="K7" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="8">
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.8</v>
+        <v>19.2</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>67.4</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="F8" t="n">
         <v>1.4</v>
       </c>
       <c r="G8" t="n">
-        <v>13.9</v>
+        <v>14.5</v>
       </c>
       <c r="H8" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="K8" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9">
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19.2</v>
+        <v>20.8</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>74.4</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G9" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="H9" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="10">
@@ -6285,39 +6285,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>18.7</v>
+        <v>21.8</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G10" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I10" t="n">
         <v>1.3</v>
       </c>
-      <c r="G10" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.1</v>
-      </c>
       <c r="J10" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="11">
@@ -6328,39 +6328,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.8</v>
+        <v>19.7</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="G11" t="n">
-        <v>14.8</v>
+        <v>14.4</v>
       </c>
       <c r="H11" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K11" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="12">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19.6</v>
+        <v>19.2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>53.3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="G12" t="n">
-        <v>14.4</v>
+        <v>13.2</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="K12" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>19.2</v>
+        <v>18.7</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="G13" t="n">
-        <v>13.2</v>
+        <v>14.1</v>
       </c>
       <c r="H13" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="K13" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.4</v>
+        <v>20.7</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>1.4</v>
       </c>
       <c r="G14" t="n">
-        <v>13.6</v>
+        <v>14</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="15">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>20.6</v>
+        <v>22.4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="G15" t="n">
-        <v>15.4</v>
+        <v>13.6</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="I15" t="n">
         <v>1.2</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="16">
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>21</v>
+        <v>20.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>70.7</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G16" t="n">
-        <v>14</v>
+        <v>15.4</v>
       </c>
       <c r="H16" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="17">
@@ -6586,39 +6586,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>67.2</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G17" t="n">
-        <v>12.3</v>
+        <v>14.2</v>
       </c>
       <c r="H17" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
         <v>1.9</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="18">
@@ -6672,39 +6672,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.1</v>
+        <v>21.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="G19" t="n">
-        <v>11.5</v>
+        <v>14.7</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="20">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -6723,31 +6723,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="G20" t="n">
-        <v>14.8</v>
+        <v>11.4</v>
       </c>
       <c r="H20" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="K20" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="21">
@@ -6758,39 +6758,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="G21" t="n">
-        <v>15.9</v>
+        <v>14</v>
       </c>
       <c r="H21" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="K21" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="22">
@@ -6801,39 +6801,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21.2</v>
+        <v>21.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>58.4</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="G22" t="n">
-        <v>14</v>
+        <v>15.9</v>
       </c>
       <c r="H22" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -7020,11 +7020,11 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -7036,7 +7036,7 @@
         <v>1.7</v>
       </c>
       <c r="G27" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="H27" t="n">
         <v>4.7</v>
@@ -7149,16 +7149,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>57.2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -7174,7 +7174,7 @@
         <v>1.3</v>
       </c>
       <c r="J30" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="K30" t="n">
         <v>2.6</v>

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -505,31 +505,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="G2" t="n">
         <v>5.6</v>
       </c>
       <c r="H2" t="n">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J2" t="n">
         <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="3">
@@ -583,7 +583,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -591,31 +591,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="G4" t="n">
         <v>5.6</v>
       </c>
       <c r="H4" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="I4" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J4" t="n">
         <v>0.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="5">
@@ -712,39 +712,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21.4</v>
+        <v>23.5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>77.1</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G7" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>7.9</v>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="8">
@@ -755,39 +755,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23.5</v>
+        <v>21.5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G8" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="H8" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="9">
@@ -845,11 +845,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>42.5</t>
+          <t>42.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -864,7 +864,7 @@
         <v>6.5</v>
       </c>
       <c r="H10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I10" t="n">
         <v>1.9</v>
@@ -873,7 +873,7 @@
         <v>0.6</v>
       </c>
       <c r="K10" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="11">
@@ -888,16 +888,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>27.1</v>
+        <v>26.9</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -907,16 +907,16 @@
         <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J11" t="n">
         <v>0.4</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="12">
@@ -927,39 +927,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.1</v>
+        <v>25.4</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G12" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="H12" t="n">
-        <v>9.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J12" t="n">
         <v>0.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="13">
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>25.4</v>
+        <v>23.1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G13" t="n">
-        <v>6.7</v>
+        <v>5.9</v>
       </c>
       <c r="H13" t="n">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="I13" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J13" t="n">
         <v>0.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="14">
@@ -1013,33 +1013,33 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G14" t="n">
-        <v>6.7</v>
+        <v>5.9</v>
       </c>
       <c r="H14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J14" t="n">
         <v>0.5</v>
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="H15" t="n">
-        <v>8.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I15" t="n">
         <v>1.9</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K15" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="16">
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.4</v>
+        <v>24.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="G17" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="H17" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K17" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="18">
@@ -1185,39 +1185,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>24.2</v>
+        <v>23.8</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="H18" t="n">
         <v>8.5</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K18" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="19">
@@ -1228,27 +1228,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.1</v>
+        <v>23.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G19" t="n">
-        <v>6.1</v>
+        <v>5.4</v>
       </c>
       <c r="H19" t="n">
         <v>8</v>
@@ -1260,7 +1260,7 @@
         <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="20">
@@ -1271,39 +1271,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>23.6</v>
+        <v>24</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G20" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="H20" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="I20" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K20" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="21">
@@ -1314,39 +1314,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.1</v>
+        <v>23.7</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="H21" t="n">
-        <v>8.4</v>
+        <v>7.3</v>
       </c>
       <c r="I21" t="n">
         <v>1.9</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K21" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="22">
@@ -1357,39 +1357,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.7</v>
+        <v>24.3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="H22" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="I22" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J22" t="n">
         <v>0.5</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="23">
@@ -1408,19 +1408,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>3.4</v>
       </c>
       <c r="G23" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="H23" t="n">
         <v>8.300000000000001</v>
@@ -1432,7 +1432,7 @@
         <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="24">
@@ -1443,39 +1443,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="H24" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="I24" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="25">
@@ -1486,39 +1486,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25.8</v>
+        <v>24.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>83.9</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>5.8</v>
+        <v>6.5</v>
       </c>
       <c r="H25" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K25" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="26">
@@ -1529,39 +1529,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24.4</v>
+        <v>25.8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="F26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H26" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K26" t="n">
         <v>3.1</v>
-      </c>
-      <c r="G26" t="n">
-        <v>7</v>
-      </c>
-      <c r="H26" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.6</v>
       </c>
     </row>
     <row r="27">
@@ -1615,39 +1615,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>25.1</v>
+        <v>26</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="G28" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H28" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K28" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -1658,39 +1658,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>26.2</v>
+        <v>24.4</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="G29" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="H29" t="n">
         <v>8.9</v>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="30">
@@ -1705,11 +1705,11 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1724,7 +1724,7 @@
         <v>5.6</v>
       </c>
       <c r="H30" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I30" t="n">
         <v>2.1</v>
@@ -1733,7 +1733,7 @@
         <v>0.6</v>
       </c>
       <c r="K30" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="31">
@@ -1862,16 +1862,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.3</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -1884,7 +1884,7 @@
         <v>5.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J2" t="n">
         <v>0.5</v>
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.7</v>
+        <v>22.9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="G4" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="H4" t="n">
         <v>5.1</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="5">
@@ -1987,39 +1987,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.4</v>
+        <v>22</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>84.9</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G5" t="n">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
       <c r="H5" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J5" t="n">
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="6">
@@ -2030,39 +2030,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.9</v>
+        <v>22.3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>41.6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="H6" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J6" t="n">
         <v>0.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="7">
@@ -2073,39 +2073,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="G7" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
       <c r="H7" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="8">
@@ -2116,39 +2116,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>6.6</v>
+        <v>7.5</v>
       </c>
       <c r="H8" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J8" t="n">
         <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="9">
@@ -2159,30 +2159,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>44.6</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="G9" t="n">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="H9" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="I9" t="n">
         <v>1.5</v>
@@ -2191,7 +2191,7 @@
         <v>0.6</v>
       </c>
       <c r="K9" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="10">
@@ -2374,11 +2374,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.8</v>
+        <v>21.9</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2387,26 +2387,26 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="G14" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="H14" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="I14" t="n">
         <v>1.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="15">
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23.6</v>
+        <v>22.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="G15" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="H15" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="16">
@@ -2460,39 +2460,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.1</v>
+        <v>22.8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="G16" t="n">
-        <v>6.3</v>
+        <v>7.3</v>
       </c>
       <c r="H16" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="17">
@@ -2503,39 +2503,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.7</v>
+        <v>23.1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="G17" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="H17" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="I17" t="n">
         <v>1.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="18">
@@ -2550,16 +2550,16 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -2589,39 +2589,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>24.3</v>
+        <v>23.5</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>6.1</v>
+        <v>6.8</v>
       </c>
       <c r="H19" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K19" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="20">
@@ -2632,39 +2632,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.9</v>
+        <v>24.4</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>41.9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>3.6</v>
       </c>
       <c r="G20" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="H20" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="I20" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
         <v>0.7</v>
       </c>
       <c r="K20" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="21">
@@ -2675,39 +2675,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.7</v>
+        <v>24.3</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3.5</v>
       </c>
       <c r="G21" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="H21" t="n">
-        <v>6.1</v>
+        <v>4.7</v>
       </c>
       <c r="I21" t="n">
         <v>1.7</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="K21" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="22">
@@ -2718,39 +2718,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.4</v>
+        <v>23.7</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>41.9</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>83.6</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="G22" t="n">
-        <v>7.1</v>
+        <v>6.4</v>
       </c>
       <c r="H22" t="n">
-        <v>5.4</v>
+        <v>6.1</v>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="K22" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="23">
@@ -2761,39 +2761,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.6</v>
+        <v>23.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="G23" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="H23" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I23" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="24">
@@ -2804,39 +2804,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.9</v>
+        <v>25.1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="G24" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="25">
@@ -2847,39 +2847,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.4</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="G25" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="H25" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K25" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="26">
@@ -2890,39 +2890,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25</v>
+        <v>23.2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="G26" t="n">
         <v>6.7</v>
       </c>
       <c r="H26" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K26" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="27">
@@ -2933,39 +2933,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="G27" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="28">
@@ -2976,39 +2976,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.1</v>
+        <v>24.1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="G28" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H28" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K28" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="29">
@@ -3023,16 +3023,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -3042,10 +3042,10 @@
         <v>7.8</v>
       </c>
       <c r="H29" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0.7</v>
@@ -3070,12 +3070,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -3085,7 +3085,7 @@
         <v>6.7</v>
       </c>
       <c r="H30" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="I30" t="n">
         <v>1.8</v>
@@ -3094,7 +3094,7 @@
         <v>0.8</v>
       </c>
       <c r="K30" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="31">
@@ -3109,16 +3109,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.5</v>
+        <v>24.7</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -3128,13 +3128,13 @@
         <v>7.2</v>
       </c>
       <c r="H31" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I31" t="n">
         <v>1.9</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K31" t="n">
         <v>3.2</v>
@@ -3334,7 +3334,7 @@
         <v>1.2</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K4" t="n">
         <v>2.3</v>
@@ -3352,16 +3352,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -3374,7 +3374,7 @@
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J5" t="n">
         <v>0.6</v>
@@ -3477,39 +3477,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>20.6</v>
+        <v>21.4</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G8" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="9">
@@ -3524,23 +3524,23 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G9" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="H9" t="n">
         <v>3.5</v>
@@ -3552,7 +3552,7 @@
         <v>0.8</v>
       </c>
       <c r="K9" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="10">
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.4</v>
+        <v>20.6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G10" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="H10" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11">
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>22.6</v>
+        <v>21.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F11" t="n">
         <v>2.6</v>
       </c>
       <c r="G11" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="H11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K11" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="12">
@@ -3666,7 +3666,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="G12" t="n">
         <v>6.7</v>
@@ -3696,11 +3696,11 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>47.9</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3735,36 +3735,36 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.2</v>
+        <v>21.8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G14" t="n">
-        <v>8.5</v>
+        <v>6.8</v>
       </c>
       <c r="H14" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>2.4</v>
@@ -3778,39 +3778,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="G15" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="H15" t="n">
         <v>4.7</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="16">
@@ -3821,39 +3821,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>21.9</v>
+        <v>22.7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="G16" t="n">
-        <v>6.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="I16" t="n">
         <v>1.7</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="17">
@@ -3907,39 +3907,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.9</v>
+        <v>22.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="G18" t="n">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="K18" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="19">
@@ -3954,7 +3954,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3963,14 +3963,14 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>2.7</v>
       </c>
       <c r="G19" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="H19" t="n">
         <v>4.3</v>
@@ -3993,15 +3993,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.8</v>
+        <v>24</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4010,22 +4010,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="G20" t="n">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="H20" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="K20" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="21">
@@ -4040,20 +4040,20 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G21" t="n">
         <v>8</v>
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.6</v>
+        <v>23.3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>47.3</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G22" t="n">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="H22" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
         <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -4122,36 +4122,36 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.3</v>
+        <v>22.2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="G23" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="H23" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
         <v>2.7</v>
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>22.2</v>
+        <v>23.5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="H24" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K24" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="25">
@@ -4216,16 +4216,16 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G25" t="n">
         <v>7.8</v>
@@ -4251,36 +4251,36 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>26.3</v>
+        <v>23.8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="G26" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="I26" t="n">
         <v>1.8</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K26" t="n">
         <v>2.6</v>
@@ -4294,36 +4294,36 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.8</v>
+        <v>26.3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.8</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G27" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="H27" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
         <v>1.8</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
         <v>2.6</v>
@@ -4380,39 +4380,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.4</v>
+        <v>23.8</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>46.8</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G29" t="n">
-        <v>8.800000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J29" t="n">
         <v>0.8</v>
       </c>
       <c r="K29" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="30">
@@ -4423,15 +4423,15 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>23.9</v>
+        <v>24.3</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4440,13 +4440,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G30" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="I30" t="n">
         <v>1.8</v>
@@ -4470,16 +4470,16 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -4666,39 +4666,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.6</v>
+        <v>20.8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="G4" t="n">
-        <v>10.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="I4" t="n">
         <v>1.5</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="5">
@@ -4709,39 +4709,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>20.8</v>
+        <v>21.6</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="G5" t="n">
-        <v>8.800000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="I5" t="n">
         <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -4803,19 +4803,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="H7" t="n">
         <v>3.8</v>
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.9</v>
+        <v>23</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="G8" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J8" t="n">
         <v>1.4</v>
       </c>
-      <c r="J8" t="n">
-        <v>1.3</v>
-      </c>
       <c r="K8" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9">
@@ -4881,39 +4881,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="G9" t="n">
-        <v>10.8</v>
+        <v>9.6</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="10">
@@ -4924,39 +4924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="G10" t="n">
-        <v>9.6</v>
+        <v>10.1</v>
       </c>
       <c r="H10" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J10" t="n">
         <v>1.3</v>
       </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
       <c r="K10" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="11">
@@ -4967,39 +4967,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="G11" t="n">
-        <v>10.5</v>
+        <v>10.8</v>
       </c>
       <c r="H11" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="I11" t="n">
         <v>1.4</v>
       </c>
       <c r="J11" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="K11" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="12">
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.9</v>
+        <v>23.2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.6</v>
+        <v>2.7</v>
       </c>
       <c r="G12" t="n">
-        <v>10.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="13">
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.4</v>
+        <v>21.6</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="G13" t="n">
-        <v>9.699999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="H13" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1.1</v>
+        <v>1.8</v>
       </c>
       <c r="K13" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="14">
@@ -5096,39 +5096,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>22.3</v>
+        <v>22.9</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>47.2</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G14" t="n">
         <v>10.8</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="15">
@@ -5139,39 +5139,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>21.6</v>
+        <v>23.4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="G15" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="16">
@@ -5182,36 +5182,36 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23</v>
+        <v>21.6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="G16" t="n">
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="H16" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="K16" t="n">
         <v>2.8</v>
@@ -5225,39 +5225,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.3</v>
+        <v>22.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G17" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="H17" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="I17" t="n">
         <v>1.4</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="18">
@@ -5268,39 +5268,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>74.2</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="G18" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="H18" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K18" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="19">
@@ -5311,36 +5311,36 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="G19" t="n">
-        <v>11.3</v>
+        <v>9.4</v>
       </c>
       <c r="H19" t="n">
         <v>4.5</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="K19" t="n">
         <v>2.4</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -5362,28 +5362,28 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="G20" t="n">
-        <v>9.4</v>
+        <v>11.3</v>
       </c>
       <c r="H20" t="n">
         <v>4.5</v>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="K20" t="n">
         <v>2.4</v>
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.5</v>
+        <v>23.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="G21" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="H21" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
         <v>1.2</v>
       </c>
       <c r="K21" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="22">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>24.1</v>
+        <v>23</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>74.9</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>2.3</v>
       </c>
       <c r="G22" t="n">
-        <v>10</v>
+        <v>11.8</v>
       </c>
       <c r="H22" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="K22" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -5483,39 +5483,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>74.7</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="G23" t="n">
-        <v>11.7</v>
+        <v>10.4</v>
       </c>
       <c r="H23" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="24">
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.3</v>
+        <v>24</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>2.3</v>
       </c>
       <c r="G24" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="H24" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="I24" t="n">
         <v>1.6</v>
       </c>
       <c r="J24" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="K24" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="25">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -5577,31 +5577,31 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="G25" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H25" t="n">
         <v>4.4</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K25" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="26">
@@ -5612,39 +5612,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.1</v>
+        <v>23.9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="G26" t="n">
-        <v>9.5</v>
+        <v>10.1</v>
       </c>
       <c r="H26" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="K26" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="27">
@@ -5655,39 +5655,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.8</v>
+        <v>23.1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>50.7</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G27" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="H27" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J27" t="n">
         <v>1.6</v>
       </c>
-      <c r="J27" t="n">
-        <v>1.1</v>
-      </c>
       <c r="K27" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="28">
@@ -5698,39 +5698,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.7</v>
+        <v>27.2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G28" t="n">
-        <v>10.5</v>
+        <v>10.7</v>
       </c>
       <c r="H28" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I28" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="K28" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -5741,39 +5741,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>27.2</v>
+        <v>23.7</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G29" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K29" t="n">
         <v>2.6</v>
-      </c>
-      <c r="G29" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="H29" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K29" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -5788,20 +5788,20 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>25.7</v>
+        <v>25.9</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G30" t="n">
         <v>10.6</v>
@@ -5835,16 +5835,16 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="G31" t="n">
         <v>12.4</v>
@@ -5856,7 +5856,7 @@
         <v>1.8</v>
       </c>
       <c r="J31" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K31" t="n">
         <v>2.6</v>
@@ -5941,39 +5941,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>52.2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>73.1</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="G2" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="3">
@@ -5984,39 +5984,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.4</v>
+        <v>19.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="G3" t="n">
-        <v>15.7</v>
+        <v>13.5</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="4">
@@ -6027,39 +6027,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18.2</v>
+        <v>18.7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>51.9</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="G4" t="n">
-        <v>13.7</v>
+        <v>14.1</v>
       </c>
       <c r="H4" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="K4" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="5">
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>18.1</v>
+        <v>21.8</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="G5" t="n">
-        <v>13.2</v>
+        <v>14.8</v>
       </c>
       <c r="H5" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J5" t="n">
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="6">
@@ -6113,39 +6113,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G6" t="n">
-        <v>13.6</v>
+        <v>14.6</v>
       </c>
       <c r="H6" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="I6" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="K6" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="7">
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.7</v>
+        <v>19.7</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
         <v>1.2</v>
-      </c>
-      <c r="G7" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.4</v>
       </c>
       <c r="J7" t="n">
         <v>1.9</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8">
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20.8</v>
+        <v>19.4</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>54.9</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>74.4</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="G9" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="H9" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="I9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J9" t="n">
         <v>1.3</v>
       </c>
-      <c r="J9" t="n">
-        <v>1.9</v>
-      </c>
       <c r="K9" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="10">
@@ -6285,39 +6285,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.8</v>
+        <v>20.7</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>67.8</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>1.4</v>
       </c>
       <c r="G10" t="n">
-        <v>14.8</v>
+        <v>14</v>
       </c>
       <c r="H10" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="I10" t="n">
         <v>1.3</v>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="K10" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="11">
@@ -6328,39 +6328,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19.7</v>
+        <v>20.6</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="G11" t="n">
-        <v>14.4</v>
+        <v>15.3</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K11" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="12">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19.2</v>
+        <v>22.2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>53.3</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="G12" t="n">
-        <v>13.2</v>
+        <v>13.6</v>
       </c>
       <c r="H12" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J12" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>18.7</v>
+        <v>21.7</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I13" t="n">
         <v>1.3</v>
       </c>
-      <c r="G13" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1.1</v>
-      </c>
       <c r="J13" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="14">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20.7</v>
+        <v>21.1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>70.3</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G14" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="I14" t="n">
         <v>1.3</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="15">
@@ -6500,39 +6500,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.4</v>
+        <v>18.2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G15" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J15" t="n">
         <v>1.4</v>
       </c>
-      <c r="G15" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="H15" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.5</v>
-      </c>
       <c r="K15" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="16">
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>70.7</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="F16" t="n">
         <v>1.2</v>
       </c>
       <c r="G16" t="n">
-        <v>15.4</v>
+        <v>12.2</v>
       </c>
       <c r="H16" t="n">
         <v>4.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="17">
@@ -6586,39 +6586,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G17" t="n">
-        <v>14.2</v>
+        <v>14.7</v>
       </c>
       <c r="H17" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
         <v>1.9</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="18">
@@ -6629,36 +6629,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G18" t="n">
-        <v>13.6</v>
+        <v>15.7</v>
       </c>
       <c r="H18" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="K18" t="n">
         <v>2.6</v>
@@ -6672,39 +6672,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21.7</v>
+        <v>19.3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="G19" t="n">
         <v>14.7</v>
       </c>
       <c r="H19" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="K19" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -6715,39 +6715,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21.9</v>
+        <v>21.6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>11.4</v>
+        <v>15.8</v>
       </c>
       <c r="H20" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="K20" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -6758,39 +6758,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>21.3</v>
+        <v>22.1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0.9</v>
+        <v>2.1</v>
       </c>
       <c r="G21" t="n">
-        <v>14</v>
+        <v>11.6</v>
       </c>
       <c r="H21" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="I21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J21" t="n">
         <v>1.6</v>
       </c>
-      <c r="J21" t="n">
-        <v>2</v>
-      </c>
       <c r="K21" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="22">
@@ -6801,39 +6801,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="G22" t="n">
-        <v>15.9</v>
+        <v>14.3</v>
       </c>
       <c r="H22" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J22" t="n">
         <v>1.8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="23">
@@ -6844,36 +6844,36 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23</v>
+        <v>21.3</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="F23" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G23" t="n">
+        <v>14</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I23" t="n">
         <v>1.6</v>
       </c>
-      <c r="G23" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="H23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1.4</v>
-      </c>
       <c r="J23" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="K23" t="n">
         <v>2.2</v>
@@ -6930,39 +6930,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.8</v>
+        <v>22.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G25" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="H25" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="K25" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="26">
@@ -6973,39 +6973,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>21.2</v>
+        <v>23.8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>53.1</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>14.1</v>
+        <v>15.6</v>
       </c>
       <c r="H26" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="K26" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="27">
@@ -7016,39 +7016,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.2</v>
+        <v>24.2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="G27" t="n">
-        <v>14.3</v>
+        <v>15.6</v>
       </c>
       <c r="H27" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="K27" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="28">
@@ -7059,39 +7059,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>24</v>
+        <v>23.2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="G28" t="n">
-        <v>15.3</v>
+        <v>14.3</v>
       </c>
       <c r="H28" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I28" t="n">
         <v>1.6</v>
       </c>
       <c r="J28" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="K28" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="29">
@@ -7102,39 +7102,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>1.3</v>
       </c>
       <c r="G29" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="H29" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="30">
@@ -7149,23 +7149,23 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.9</v>
+        <v>25.2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>57.2</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>73.9</t>
+          <t>73.6</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="G30" t="n">
-        <v>16.1</v>
+        <v>16</v>
       </c>
       <c r="H30" t="n">
         <v>4.4</v>
@@ -7174,7 +7174,7 @@
         <v>1.3</v>
       </c>
       <c r="J30" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="K30" t="n">
         <v>2.6</v>
@@ -7192,35 +7192,35 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>25.4</v>
+        <v>25.2</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>59.6</t>
+          <t>59.1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>68.4</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G31" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="H31" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I31" t="n">
         <v>1.8</v>
       </c>
       <c r="J31" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="K31" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
   </sheetData>

--- a/backend/nba_defense_data.xlsx
+++ b/backend/nba_defense_data.xlsx
@@ -497,39 +497,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22.4</v>
+        <v>22.1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>41.5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="G2" t="n">
         <v>5.6</v>
       </c>
       <c r="H2" t="n">
-        <v>8.5</v>
+        <v>7.3</v>
       </c>
       <c r="I2" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J2" t="n">
         <v>0.5</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -544,32 +544,32 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>71.3</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G3" t="n">
         <v>6.5</v>
       </c>
       <c r="H3" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="I3" t="n">
         <v>1.8</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K3" t="n">
         <v>3.8</v>
@@ -583,7 +583,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -591,31 +591,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="G4" t="n">
         <v>5.6</v>
       </c>
       <c r="H4" t="n">
-        <v>7.3</v>
+        <v>8.5</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="J4" t="n">
         <v>0.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="5">
@@ -626,39 +626,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>22.7</v>
+        <v>22.4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>75.9</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K5" t="n">
         <v>3.1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="H5" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.6</v>
       </c>
     </row>
     <row r="6">
@@ -669,39 +669,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.2</v>
+        <v>22.7</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.2</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="H6" t="n">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="7">
@@ -712,39 +712,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23.5</v>
+        <v>21.5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>77.1</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="H7" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
@@ -755,39 +755,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.5</v>
+        <v>23.6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>5.8</v>
+        <v>6.3</v>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="9">
@@ -802,16 +802,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23</v>
+        <v>22.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.7</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>84.1</t>
+          <t>84.2</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -884,36 +884,36 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26.9</v>
+        <v>25.4</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
         <v>3.6</v>
@@ -927,39 +927,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>25.4</v>
+        <v>26.8</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="G12" t="n">
-        <v>6.6</v>
+        <v>6.1</v>
       </c>
       <c r="H12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="13">
@@ -970,39 +970,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>23.1</v>
+        <v>23.5</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>2.9</v>
       </c>
       <c r="G13" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="H13" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="14">
@@ -1056,39 +1056,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24.6</v>
+        <v>23.1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G15" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K15" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="16">
@@ -1099,39 +1099,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>23.7</v>
+        <v>24.8</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>83.6</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>5.3</v>
+        <v>6.1</v>
       </c>
       <c r="H16" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
         <v>0.4</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="17">
@@ -1142,39 +1142,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24.6</v>
+        <v>24</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="G17" t="n">
-        <v>6.7</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K17" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="18">
@@ -1185,39 +1185,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.8</v>
+        <v>24.5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="G18" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="H18" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J18" t="n">
         <v>0.6</v>
       </c>
       <c r="K18" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="19">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1279,31 +1279,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="G20" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="H20" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J20" t="n">
         <v>0.6</v>
       </c>
       <c r="K20" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="21">
@@ -1318,11 +1318,11 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1346,7 +1346,7 @@
         <v>0.5</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -1404,23 +1404,23 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G23" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="H23" t="n">
         <v>8.300000000000001</v>
@@ -1432,7 +1432,7 @@
         <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="24">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1451,31 +1451,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G24" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="H24" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="I24" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="25">
@@ -1486,39 +1486,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>24.9</v>
+        <v>25.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>83.9</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="H25" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K25" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="26">
@@ -1529,39 +1529,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>25.8</v>
+        <v>24.9</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>83.9</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="H26" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K26" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="27">
@@ -1576,26 +1576,26 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>46.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G27" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="I27" t="n">
         <v>2.6</v>
@@ -1662,16 +1662,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1681,16 +1681,16 @@
         <v>7</v>
       </c>
       <c r="H29" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0.7</v>
       </c>
       <c r="K29" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="30">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1733,7 +1733,7 @@
         <v>0.6</v>
       </c>
       <c r="K30" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="31">
@@ -1909,19 +1909,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>3.1</v>
       </c>
       <c r="G3" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H3" t="n">
         <v>4.9</v>
@@ -1948,26 +1948,26 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>2.7</v>
       </c>
       <c r="G4" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I4" t="n">
         <v>1.6</v>
@@ -1995,12 +1995,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>84.9</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -2010,7 +2010,7 @@
         <v>6.5</v>
       </c>
       <c r="H5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I5" t="n">
         <v>1.4</v>
@@ -2073,30 +2073,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="G7" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="H7" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="I7" t="n">
         <v>1.5</v>
@@ -2105,7 +2105,7 @@
         <v>0.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G8" t="n">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I8" t="n">
         <v>1.6</v>
@@ -2148,7 +2148,7 @@
         <v>0.6</v>
       </c>
       <c r="K8" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="9">
@@ -2159,39 +2159,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>23.1</v>
+        <v>23.9</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>81.7</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="G9" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="H9" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="I9" t="n">
         <v>1.5</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="10">
@@ -2202,39 +2202,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23.7</v>
+        <v>22.9</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>41.6</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>6.3</v>
+        <v>7.5</v>
       </c>
       <c r="H10" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I10" t="n">
         <v>1.6</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K10" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="11">
@@ -2249,11 +2249,11 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2265,10 +2265,10 @@
         <v>3.4</v>
       </c>
       <c r="G11" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="H11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I11" t="n">
         <v>1.4</v>
@@ -2292,26 +2292,26 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>3.2</v>
       </c>
       <c r="G12" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="H12" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I12" t="n">
         <v>1.4</v>
@@ -2331,39 +2331,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>22.9</v>
+        <v>21.9</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="G13" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="H13" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="I13" t="n">
         <v>1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K13" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="14">
@@ -2374,30 +2374,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.9</v>
+        <v>23.1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="G14" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="H14" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="I14" t="n">
         <v>1.8</v>
@@ -2406,7 +2406,7 @@
         <v>0.6</v>
       </c>
       <c r="K14" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="15">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2425,19 +2425,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>83.4</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G15" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H15" t="n">
         <v>5.2</v>
@@ -2449,7 +2449,7 @@
         <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="16">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2468,31 +2468,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="G16" t="n">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="17">
@@ -2503,39 +2503,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>23.1</v>
+        <v>22.8</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="G17" t="n">
-        <v>6.3</v>
+        <v>7.3</v>
       </c>
       <c r="H17" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K17" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="18">
@@ -2546,39 +2546,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="G18" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="H18" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K18" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="19">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2597,31 +2597,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G19" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="H19" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K19" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="20">
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24.4</v>
+        <v>24.2</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2645,14 +2645,14 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>3.6</v>
       </c>
       <c r="G20" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="H20" t="n">
         <v>5.4</v>
@@ -2661,7 +2661,7 @@
         <v>1.4</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="K20" t="n">
         <v>2.9</v>
@@ -2679,26 +2679,26 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>45.2</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3.5</v>
       </c>
       <c r="G21" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="H21" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I21" t="n">
         <v>1.7</v>
@@ -2722,26 +2722,26 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45.4</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>3.5</v>
       </c>
       <c r="G22" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="H22" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="I22" t="n">
         <v>1.7</v>
@@ -2750,7 +2750,7 @@
         <v>0.3</v>
       </c>
       <c r="K22" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="23">
@@ -2761,39 +2761,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.1</v>
+        <v>25</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="G23" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="H23" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
         <v>0.6</v>
       </c>
       <c r="K23" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -2804,39 +2804,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>25.1</v>
+        <v>23.5</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>45.9</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="G24" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="H24" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K24" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="25">
@@ -2847,39 +2847,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>82.4</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="G25" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="H25" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="I25" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K25" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="26">
@@ -2890,39 +2890,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>79.4</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="G26" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="J26" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="K26" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="27">
@@ -2933,39 +2933,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.8</v>
+        <v>23.1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>79.4</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="G27" t="n">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="H27" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="K27" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="28">
@@ -2984,12 +2984,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -3223,16 +3223,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -3248,7 +3248,7 @@
         <v>1.7</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
@@ -3266,7 +3266,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -3275,14 +3275,14 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
@@ -3395,16 +3395,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>41.3</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -3417,10 +3417,10 @@
         <v>4.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K6" t="n">
         <v>3.1</v>
@@ -3434,39 +3434,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>21.5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>79.9</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="G7" t="n">
         <v>7.6</v>
       </c>
       <c r="H7" t="n">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="I7" t="n">
         <v>1.6</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="K7" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="8">
@@ -3477,39 +3477,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.4</v>
+        <v>23</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="G8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K8" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -3520,39 +3520,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.5</v>
+        <v>20.6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="H9" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="I9" t="n">
         <v>1.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="10">
@@ -3563,39 +3563,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>DAL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20.6</v>
+        <v>21.2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G10" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="I10" t="n">
         <v>1.6</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K10" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="11">
@@ -3606,39 +3606,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DAL</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.2</v>
+        <v>22.8</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="H11" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="I11" t="n">
         <v>1.6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="12">
@@ -3653,26 +3653,26 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>44.6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="F12" t="n">
         <v>2.8</v>
       </c>
       <c r="G12" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I12" t="n">
         <v>1.7</v>
@@ -3692,7 +3692,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -3700,31 +3700,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>47.9</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="G13" t="n">
-        <v>7.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14">
@@ -3735,39 +3735,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.8</v>
+        <v>22.7</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="G14" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="I14" t="n">
         <v>1.7</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="15">
@@ -3778,39 +3778,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>22.7</v>
+        <v>21.8</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="G15" t="n">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="H15" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="I15" t="n">
         <v>1.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="16">
@@ -3821,39 +3821,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22.7</v>
+        <v>21.4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>44.8</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="G16" t="n">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="H16" t="n">
         <v>4.7</v>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J16" t="n">
         <v>0.7</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="17">
@@ -3868,16 +3868,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>83.4</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -3887,7 +3887,7 @@
         <v>6.9</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I17" t="n">
         <v>2.1</v>
@@ -3911,23 +3911,23 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>2.8</v>
       </c>
       <c r="G18" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H18" t="n">
         <v>4.2</v>
@@ -3950,39 +3950,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.9</v>
+        <v>23.8</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>78.1</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="G19" t="n">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
       <c r="H19" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K19" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -3993,39 +3993,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>22.9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>82.9</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G20" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
         <v>0.8</v>
       </c>
       <c r="K20" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="21">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -4044,31 +4044,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>82.9</t>
+          <t>78.1</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="G21" t="n">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="H21" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I21" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="22">
@@ -4079,39 +4079,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23.3</v>
+        <v>23.5</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>8.5</v>
+        <v>7.6</v>
       </c>
       <c r="H22" t="n">
         <v>5.4</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J22" t="n">
         <v>0.8</v>
       </c>
       <c r="K22" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="23">
@@ -4122,36 +4122,36 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>22.2</v>
+        <v>23.2</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>44.7</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="G23" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="H23" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="I23" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="K23" t="n">
         <v>2.7</v>
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>23.5</v>
+        <v>22.4</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="G24" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="H24" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="I24" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K24" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="25">
@@ -4208,39 +4208,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>47.6</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="G25" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J25" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K25" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="26">
@@ -4251,39 +4251,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.8</v>
+        <v>24.1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="G26" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="H26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I26" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="K26" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="27">
@@ -4298,16 +4298,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>26.3</v>
+        <v>26.4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -4317,7 +4317,7 @@
         <v>7.2</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I27" t="n">
         <v>1.8</v>
@@ -4345,12 +4345,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>49.1</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -4366,7 +4366,7 @@
         <v>1.9</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>1.9</v>
@@ -4380,39 +4380,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>23.8</v>
+        <v>24.3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>46.8</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>7.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I29" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J29" t="n">
         <v>0.8</v>
       </c>
       <c r="K29" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="30">
@@ -4423,15 +4423,15 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>24.3</v>
+        <v>24.1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4440,22 +4440,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="G30" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="H30" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I30" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J30" t="n">
         <v>0.8</v>
       </c>
       <c r="K30" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="31">
@@ -4584,16 +4584,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>44.7</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -4627,32 +4627,32 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>46.4</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="F3" t="n">
         <v>1.8</v>
       </c>
       <c r="G3" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="H3" t="n">
         <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K3" t="n">
         <v>3</v>
@@ -4666,39 +4666,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>20.8</v>
+        <v>21.6</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.9</t>
+          <t>46.6</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="G4" t="n">
-        <v>8.800000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="H4" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="I4" t="n">
         <v>1.5</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -4709,39 +4709,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.6</v>
+        <v>21</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>47.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>71.4</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="G5" t="n">
-        <v>10.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="I5" t="n">
         <v>1.5</v>
       </c>
       <c r="J5" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="6">
@@ -4756,23 +4756,23 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.4</v>
+        <v>22.7</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>73.7</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="H6" t="n">
         <v>4.4</v>
@@ -4799,11 +4799,11 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4815,7 +4815,7 @@
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H7" t="n">
         <v>3.8</v>
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>22.1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>48.6</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="G8" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J8" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="K8" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="9">
@@ -4885,23 +4885,23 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>2.5</v>
       </c>
       <c r="G9" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="H9" t="n">
         <v>4.5</v>
@@ -4913,7 +4913,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="10">
@@ -4924,39 +4924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>21.9</v>
+        <v>21.6</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>47.7</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>2.1</v>
       </c>
       <c r="G10" t="n">
-        <v>10.1</v>
+        <v>10.8</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I10" t="n">
         <v>1.4</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="K10" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="11">
@@ -4967,39 +4967,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>21.6</v>
+        <v>23.2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>47.7</t>
+          <t>47.5</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
         <v>2.1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="H11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>2.9</v>
       </c>
     </row>
     <row r="12">
@@ -5010,39 +5010,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23.2</v>
+        <v>21.6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="G12" t="n">
-        <v>9.699999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="H12" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="K12" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="13">
@@ -5053,39 +5053,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.6</v>
+        <v>23</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="G13" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="I13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J13" t="n">
         <v>1.4</v>
       </c>
-      <c r="J13" t="n">
-        <v>1.8</v>
-      </c>
       <c r="K13" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="14">
@@ -5182,39 +5182,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>21.6</v>
+        <v>22.7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>76.4</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="G16" t="n">
-        <v>9.9</v>
+        <v>10.6</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="17">
@@ -5225,39 +5225,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAL</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>76.4</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="G17" t="n">
-        <v>10.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="K17" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="18">
@@ -5268,36 +5268,36 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>23.5</v>
+        <v>22.9</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>53.0</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>74.2</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="G18" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="H18" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="K18" t="n">
         <v>2.7</v>
@@ -5311,39 +5311,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LAL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>22.6</v>
+        <v>21.7</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>45.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>72.8</t>
+          <t>79.1</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="G19" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="H19" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="K19" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="20">
@@ -5354,39 +5354,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>22.6</v>
+        <v>22.9</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="G20" t="n">
-        <v>11.3</v>
+        <v>10</v>
       </c>
       <c r="H20" t="n">
         <v>4.5</v>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="K20" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="21">
@@ -5397,39 +5397,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>23.1</v>
+        <v>23.5</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>52.9</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="G21" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="H21" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
         <v>1.2</v>
       </c>
       <c r="K21" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="22">
@@ -5440,39 +5440,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>23</v>
+        <v>22.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>47.0</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>74.9</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="G22" t="n">
-        <v>11.8</v>
+        <v>11.3</v>
       </c>
       <c r="H22" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J22" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="23">
@@ -5483,36 +5483,36 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23.3</v>
+        <v>24</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="G23" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="H23" t="n">
         <v>3.4</v>
       </c>
       <c r="I23" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="K23" t="n">
         <v>2.7</v>
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24</v>
+        <v>23.1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>47.3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>2.3</v>
       </c>
       <c r="G24" t="n">
-        <v>10.2</v>
+        <v>11.7</v>
       </c>
       <c r="H24" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="K24" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -5569,39 +5569,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>23.7</v>
+        <v>23.1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>50.8</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F25" t="n">
         <v>2.5</v>
       </c>
       <c r="G25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="H25" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J25" t="n">
         <v>1.6</v>
       </c>
-      <c r="J25" t="n">
-        <v>1.1</v>
-      </c>
       <c r="K25" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="26">
@@ -5612,39 +5612,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SAC</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>50.8</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="G26" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H26" t="n">
         <v>4.4</v>
       </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K26" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="27">
@@ -5655,39 +5655,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>SAC</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>23.1</v>
+        <v>24.1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>47.5</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="G27" t="n">
-        <v>9.5</v>
+        <v>10.2</v>
       </c>
       <c r="H27" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="I27" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="K27" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="28">
@@ -5698,39 +5698,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>27.2</v>
+        <v>23.7</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>46.5</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="F28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G28" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K28" t="n">
         <v>2.6</v>
-      </c>
-      <c r="G28" t="n">
-        <v>10.7</v>
-      </c>
-      <c r="H28" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="I28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="J28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K28" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -5741,39 +5741,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>23.7</v>
+        <v>27.3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>51.4</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="G29" t="n">
-        <v>10.6</v>
+        <v>10.8</v>
       </c>
       <c r="H29" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="K29" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -5784,39 +5784,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>WAS</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>25.9</v>
+        <v>24.6</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>72.4</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="G30" t="n">
-        <v>10.6</v>
+        <v>12.4</v>
       </c>
       <c r="H30" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="I30" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J30" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="31">
@@ -5827,39 +5827,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>WAS</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>24.6</v>
+        <v>25.9</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>72.4</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="G31" t="n">
-        <v>12.4</v>
+        <v>10.6</v>
       </c>
       <c r="H31" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="I31" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="K31" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
     </row>
   </sheetData>
@@ -5949,12 +5949,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>52.2</t>
+          <t>52.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -5964,7 +5964,7 @@
         <v>13.2</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="I2" t="n">
         <v>1.7</v>
@@ -5973,7 +5973,7 @@
         <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="3">
@@ -6027,39 +6027,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>PHO</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18.7</v>
+        <v>21.7</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>51.9</t>
+          <t>57.3</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="F4" t="n">
         <v>1.3</v>
       </c>
       <c r="G4" t="n">
-        <v>14.1</v>
+        <v>14.8</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="I4" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="5">
@@ -6070,39 +6070,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PHO</t>
+          <t>MEM</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.8</v>
+        <v>21.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>57.3</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="G5" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="H5" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I5" t="n">
         <v>1.3</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="K5" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="6">
@@ -6113,39 +6113,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MEM</t>
+          <t>OKC</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>21</v>
+        <v>19.2</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="G6" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="H6" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K6" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="7">
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>19.7</v>
+        <v>20.6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>52.4</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="G7" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="I7" t="n">
         <v>1.2</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="K7" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="8">
@@ -6199,39 +6199,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OKC</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>19.2</v>
+        <v>18.8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G8" t="n">
-        <v>14.5</v>
+        <v>13.9</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J8" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="9">
@@ -6242,39 +6242,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19.4</v>
+        <v>19.7</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>72.1</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="G9" t="n">
-        <v>13.2</v>
+        <v>14.4</v>
       </c>
       <c r="H9" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="10">
@@ -6285,39 +6285,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20.7</v>
+        <v>19.4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>67.8</t>
+          <t>72.1</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G10" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="H10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I10" t="n">
         <v>1.4</v>
       </c>
-      <c r="G10" t="n">
-        <v>14</v>
-      </c>
-      <c r="H10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>1.3</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>2.2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2.6</v>
       </c>
     </row>
     <row r="11">
@@ -6328,39 +6328,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>DEN</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20.6</v>
+        <v>22.3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>68.6</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I11" t="n">
         <v>1.2</v>
       </c>
-      <c r="G11" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1.3</v>
-      </c>
       <c r="J11" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="K11" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="12">
@@ -6371,39 +6371,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DEN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>22.2</v>
+        <v>20.6</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>53.6</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>67.5</t>
         </is>
       </c>
       <c r="F12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I12" t="n">
         <v>1.4</v>
       </c>
-      <c r="G12" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1.2</v>
-      </c>
       <c r="J12" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="K12" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="13">
@@ -6414,39 +6414,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>52.1</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>69.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="G13" t="n">
-        <v>13.5</v>
+        <v>14.7</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="14">
@@ -6457,39 +6457,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>GS</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>21.1</v>
+        <v>20.6</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>48.6</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>70.3</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G14" t="n">
-        <v>14.2</v>
+        <v>15.3</v>
       </c>
       <c r="H14" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I14" t="n">
         <v>1.3</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="K14" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="15">
@@ -6504,26 +6504,26 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.8</t>
         </is>
       </c>
       <c r="F15" t="n">
         <v>0.7</v>
       </c>
       <c r="G15" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="H15" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I15" t="n">
         <v>1.6</v>
@@ -6543,39 +6543,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20.7</v>
+        <v>21.7</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>69.3</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="G16" t="n">
-        <v>12.2</v>
+        <v>13.5</v>
       </c>
       <c r="H16" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="17">
@@ -6586,39 +6586,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.6</v>
+        <v>21.2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>70.9</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="G17" t="n">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="J17" t="n">
         <v>1.9</v>
       </c>
       <c r="K17" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="18">
@@ -6629,39 +6629,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>ORL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>21.6</v>
+        <v>19.3</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="G18" t="n">
-        <v>15.7</v>
+        <v>14.7</v>
       </c>
       <c r="H18" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="K18" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -6672,36 +6672,36 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ORL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>19.3</v>
+        <v>21.6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>52.0</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>14.7</v>
+        <v>15.8</v>
       </c>
       <c r="H19" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
         <v>3</v>
@@ -6715,39 +6715,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHA</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>54.2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="G20" t="n">
-        <v>15.8</v>
+        <v>11.6</v>
       </c>
       <c r="H20" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="21">
@@ -6758,39 +6758,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CHA</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>22.1</v>
+        <v>21.6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>54.2</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="G21" t="n">
-        <v>11.6</v>
+        <v>15.7</v>
       </c>
       <c r="H21" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="K21" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="22">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LAC</t>
+          <t>BKN</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -6809,31 +6809,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>58.5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="J22" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="23">
@@ -6844,36 +6844,36 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BKN</t>
+          <t>UTA</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>21.3</v>
+        <v>22.9</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>58.5</t>
+          <t>57.4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="G23" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="H23" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="K23" t="n">
         <v>2.2</v>
@@ -6887,39 +6887,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POR</t>
+          <t>LAC</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>24.6</v>
+        <v>21.4</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>53.0</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G24" t="n">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="H24" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="I24" t="n">
         <v>1.7</v>
       </c>
       <c r="J24" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="K24" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="25">
@@ -6930,39 +6930,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>UTA</t>
+          <t>POR</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>22.9</v>
+        <v>24.9</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>57.4</t>
+          <t>56.2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G25" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="H25" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="K25" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="26">
@@ -7016,39 +7016,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CHI</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24.2</v>
+        <v>23.4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>54.7</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>67.4</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="G27" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="H27" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="K27" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="28">
@@ -7059,39 +7059,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>23.2</v>
+        <v>23.9</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>54.9</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="G28" t="n">
-        <v>14.3</v>
+        <v>15.8</v>
       </c>
       <c r="H28" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J28" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="K28" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="29">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>59.2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>68.6</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -7214,7 +7214,7 @@
         <v>4.2</v>
       </c>
       <c r="I31" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>2.2</v>
